--- a/docs/Mech Data.xlsx
+++ b/docs/Mech Data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\FoundryData-Dev\Data\systems\mwd\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{961015C9-46B8-42CA-974E-71A6DF59CF20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8326161-EC90-4AEF-B148-CBFC075BCF42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="22440" yWindow="2175" windowWidth="24885" windowHeight="19275" xr2:uid="{8D44F242-D0B2-4B9E-94CF-33F11494976A}"/>
+    <workbookView xWindow="51480" yWindow="-4995" windowWidth="16440" windowHeight="28320" xr2:uid="{8D44F242-D0B2-4B9E-94CF-33F11494976A}"/>
   </bookViews>
   <sheets>
     <sheet name="Mechs" sheetId="1" r:id="rId1"/>
@@ -1618,9 +1618,15 @@
       <c r="N4" s="12">
         <v>4</v>
       </c>
-      <c r="O4" s="12"/>
-      <c r="P4" s="1"/>
-      <c r="Q4" s="12"/>
+      <c r="O4" s="12">
+        <v>3</v>
+      </c>
+      <c r="P4" s="1">
+        <v>3</v>
+      </c>
+      <c r="Q4" s="12">
+        <v>3</v>
+      </c>
       <c r="R4" s="3">
         <v>1728000</v>
       </c>

--- a/docs/Mech Data.xlsx
+++ b/docs/Mech Data.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\FoundryData-Dev\Data\systems\mwd\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8326161-EC90-4AEF-B148-CBFC075BCF42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10FBC4AF-F6F2-43DD-860F-6EEE9C0A8CED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="51480" yWindow="-4995" windowWidth="16440" windowHeight="28320" xr2:uid="{8D44F242-D0B2-4B9E-94CF-33F11494976A}"/>
   </bookViews>
   <sheets>
     <sheet name="Mechs" sheetId="1" r:id="rId1"/>
-    <sheet name="Asset Modules" sheetId="2" r:id="rId2"/>
-    <sheet name="Misc Tables" sheetId="3" r:id="rId3"/>
-    <sheet name="Sheet4" sheetId="4" r:id="rId4"/>
+    <sheet name="Vehicles" sheetId="5" r:id="rId2"/>
+    <sheet name="Asset Modules" sheetId="2" r:id="rId3"/>
+    <sheet name="Misc Tables" sheetId="3" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="530" uniqueCount="256">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="713" uniqueCount="437">
   <si>
     <t>Chassis</t>
   </si>
@@ -110,9 +110,6 @@
     <t>Stinger</t>
   </si>
   <si>
-    <t>Wasp</t>
-  </si>
-  <si>
     <t>COM-2D</t>
   </si>
   <si>
@@ -446,27 +443,6 @@
     <t>Raider</t>
   </si>
   <si>
-    <t>Mech</t>
-  </si>
-  <si>
-    <t>HND</t>
-  </si>
-  <si>
-    <t>SYS</t>
-  </si>
-  <si>
-    <t>REL</t>
-  </si>
-  <si>
-    <t>CHS</t>
-  </si>
-  <si>
-    <t>Struct</t>
-  </si>
-  <si>
-    <t>Diss</t>
-  </si>
-  <si>
     <t>Thermal Profile</t>
   </si>
   <si>
@@ -809,7 +785,2124 @@
     <t>EngRate X Tonnage X 267</t>
   </si>
   <si>
-    <t>Actuators</t>
+    <t>Fire Control Suite</t>
+  </si>
+  <si>
+    <t>Advanced Sensors</t>
+  </si>
+  <si>
+    <t>Reinforced Cockpit</t>
+  </si>
+  <si>
+    <t>Modules</t>
+  </si>
+  <si>
+    <t>Quirks</t>
+  </si>
+  <si>
+    <t>Low Profile</t>
+  </si>
+  <si>
+    <t>Oversized Frame</t>
+  </si>
+  <si>
+    <t>Cramp Cockpit</t>
+  </si>
+  <si>
+    <t>Hard to Pilot</t>
+  </si>
+  <si>
+    <t>Easy to Pilot</t>
+  </si>
+  <si>
+    <t>Equipment</t>
+  </si>
+  <si>
+    <t>Targeting Computer</t>
+  </si>
+  <si>
+    <t>Battle Computer - Cluster Optimizer</t>
+  </si>
+  <si>
+    <t>Network</t>
+  </si>
+  <si>
+    <t>C3 Unit</t>
+  </si>
+  <si>
+    <t>Bloodhound Active Probe</t>
+  </si>
+  <si>
+    <t>Beagle Active Probe</t>
+  </si>
+  <si>
+    <t>Watchdog CEWS</t>
+  </si>
+  <si>
+    <t>Protection Systems</t>
+  </si>
+  <si>
+    <t>CASE</t>
+  </si>
+  <si>
+    <t>Feed Stabilizer</t>
+  </si>
+  <si>
+    <t>Coolant Pod</t>
+  </si>
+  <si>
+    <t>Power Rerouter Bus</t>
+  </si>
+  <si>
+    <t>Mobility</t>
+  </si>
+  <si>
+    <t>Basic Jump Jet</t>
+  </si>
+  <si>
+    <t>Improved Jump Jet</t>
+  </si>
+  <si>
+    <t>Triple Strength Myomer</t>
+  </si>
+  <si>
+    <t>M.A.S.C.</t>
+  </si>
+  <si>
+    <t>Artemis IV FCS</t>
+  </si>
+  <si>
+    <t>TAG Designator</t>
+  </si>
+  <si>
+    <t>NARC Beacon Launcher</t>
+  </si>
+  <si>
+    <t>Guardian ECM</t>
+  </si>
+  <si>
+    <t>Advanced Targeting Computer</t>
+  </si>
+  <si>
+    <t>Combat  Electronics</t>
+  </si>
+  <si>
+    <t>Hardened Structure Components</t>
+  </si>
+  <si>
+    <t>Advanced Optics</t>
+  </si>
+  <si>
+    <t>IFF Jammer</t>
+  </si>
+  <si>
+    <t>Jump Booster</t>
+  </si>
+  <si>
+    <t>Thermal Bank</t>
+  </si>
+  <si>
+    <t>Stealth X system</t>
+  </si>
+  <si>
+    <t>Battle Computer - Ballistic Optimizer</t>
+  </si>
+  <si>
+    <t>Battle Computer - Energy Optimizer</t>
+  </si>
+  <si>
+    <t>Buffered VDNI Console</t>
+  </si>
+  <si>
+    <t>Encased Cybernetic Cockpit</t>
+  </si>
+  <si>
+    <t>Carried Combat Shield</t>
+  </si>
+  <si>
+    <t>SLIC Suite</t>
+  </si>
+  <si>
+    <t>AR14 Sheathed Beacon</t>
+  </si>
+  <si>
+    <t>Nova CEWS</t>
+  </si>
+  <si>
+    <t>Probeking QS</t>
+  </si>
+  <si>
+    <t>Electronic Protection Array</t>
+  </si>
+  <si>
+    <t>UAV Integration Compartment</t>
+  </si>
+  <si>
+    <t>Hardened Armor</t>
+  </si>
+  <si>
+    <t>Laser Heat Sink</t>
+  </si>
+  <si>
+    <t>Reactive Plating</t>
+  </si>
+  <si>
+    <t>Harjel II</t>
+  </si>
+  <si>
+    <t>Supercharger</t>
+  </si>
+  <si>
+    <t>Reflective Glazing</t>
+  </si>
+  <si>
+    <t>Effect</t>
+  </si>
+  <si>
+    <t>Requirement</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Overheat </t>
+  </si>
+  <si>
+    <t>+1 gunnery dice, +5 AR for penetrating attacks</t>
+  </si>
+  <si>
+    <t>+1 gunnery dice, +5 AR for energy attacks</t>
+  </si>
+  <si>
+    <t>Cluster Dice hit on 4+</t>
+  </si>
+  <si>
+    <t>Legs not Crippled/Disabled</t>
+  </si>
+  <si>
+    <t>Cost/Risk</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>Jump Move generates +1 heat</t>
+  </si>
+  <si>
+    <t>1 Jump Move Action; +1 TrackingPenalty; +3 AR</t>
+  </si>
+  <si>
+    <t>2 Jump Move Action; +1 TrackingPenalty; +3 AR</t>
+  </si>
+  <si>
+    <t>Sensor Lock; missile weapon</t>
+  </si>
+  <si>
+    <t>Sensor Lock; cluster weapon</t>
+  </si>
+  <si>
+    <t>Sensor Lock; ballistic weapon</t>
+  </si>
+  <si>
+    <t>Sensor Lock; energy weapon</t>
+  </si>
+  <si>
+    <r>
+      <t>+5 AR</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> with missile attacks; guided missile systems may use Lock/TAG/NARC benefits</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>+2 melee damage</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">; </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>+30m ground movement</t>
+    </r>
+  </si>
+  <si>
+    <t>+50m ground movement when engaged</t>
+  </si>
+  <si>
+    <r>
+      <t>+1 Piloting die</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">; </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>+5 AR</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> with melee attacks</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>+100m ground movement</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> when engaged</t>
+    </r>
+  </si>
+  <si>
+    <t>+1 heat per move action while active and +1 leg stress when used.</t>
+  </si>
+  <si>
+    <t>+1 leg stress when used.</t>
+  </si>
+  <si>
+    <t>none, but it only functions while heat remains in the required band.</t>
+  </si>
+  <si>
+    <t>Provider Hook</t>
+  </si>
+  <si>
+    <t>Attack</t>
+  </si>
+  <si>
+    <t>missile lockGated, fireControl</t>
+  </si>
+  <si>
+    <t>cluster, lockGated</t>
+  </si>
+  <si>
+    <t>ballistics, lockGated</t>
+  </si>
+  <si>
+    <t>laser, lockGated</t>
+  </si>
+  <si>
+    <t>jump, heat</t>
+  </si>
+  <si>
+    <t>speedBoost, legs</t>
+  </si>
+  <si>
+    <t>Attack, CQ provider</t>
+  </si>
+  <si>
+    <t>cluster damage provider</t>
+  </si>
+  <si>
+    <t>Attack provider</t>
+  </si>
+  <si>
+    <t>Mobility provider</t>
+  </si>
+  <si>
+    <t>speedBoost, melee</t>
+  </si>
+  <si>
+    <t>Mobility, melee attack provider</t>
+  </si>
+  <si>
+    <t>speedBoost, legs, heat</t>
+  </si>
+  <si>
+    <t>-1 trackingPenalty</t>
+  </si>
+  <si>
+    <t>Generates +1 heat when used</t>
+  </si>
+  <si>
+    <t>Sensor provider</t>
+  </si>
+  <si>
+    <t>EW Provider</t>
+  </si>
+  <si>
+    <t>sensors, passive, optics</t>
+  </si>
+  <si>
+    <t>Active sensors available</t>
+  </si>
+  <si>
+    <t>sensors, activeProbe, quickScan</t>
+  </si>
+  <si>
+    <t>Arms or Legs not Disabled, no actuator failure</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Line of sight; not </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>sensorBlind</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>sensors</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>activeProbe</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>ecm</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>epm</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>beacon</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Ignore obscuredLight; </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>+1 die</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> to visual identification</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>sensors</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>activeProbe</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>antiStealth</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>mineDetection</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>sensors</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>activeProbe</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>mineDetection</t>
+    </r>
+  </si>
+  <si>
+    <t>+2 dice acquireTarget / Sensor Sweep/generateTargetingData; +2 Piloting dice to avoid mines; acquire blind → contact as freeAction. Ignore ecmShrouded.</t>
+  </si>
+  <si>
+    <t>+1 die acquireTarget / Sensor Sweep, +2 Piloting dice to avoid mines; upgrade blind → contact, contact → track as freeAction. Ignore obscuredLight</t>
+  </si>
+  <si>
+    <t>acquireTarget attempt each activation may be made as a Free Action</t>
+  </si>
+  <si>
+    <t>acquireTarget action generates 1 heat</t>
+  </si>
+  <si>
+    <r>
+      <t>ecm</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>epm</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>sensors</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>cews</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>ecm</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>epm</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>sensors</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>cews</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>advanced</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>ecm</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>defensiveJammer</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>epm</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>counterEW</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Applies </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>ecmShrouded</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> to the carrier. Grants </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>+1 die</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> to </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>acquireTarget</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">. Grants </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>+1 die</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> to </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>epmFilter</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>. Flexible compact EW package.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Applies </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>ecmShrouded</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> and </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>epmBoosted</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> to the carrier. Grants </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>+1 die</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> to </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>acquireTarget</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">. Grants </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>+1 die</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> to </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>ecmSpike</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>breakLock</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, and </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>epmFilter</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>. Active mode applies ecmShrouded to allies within 90m.</t>
+    </r>
+  </si>
+  <si>
+    <t>Active mode generates 1 heat</t>
+  </si>
+  <si>
+    <t>Applies ecmShrouded to the carrier. Grants +3 dice to ecmSpike and breakLock.; Active mode applies ecmShrouded to allies within 180m.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Applies </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>epmBoosted</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> to the carrier. Grants </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>+2 dice</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> to </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>epmFilter</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> and </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>holdLink</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">. While </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>epmBoosted</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, the carrier may ignore </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>ecmJamming</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">’s targetingData reduction and may attempt to acquire </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>lock</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> despite </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>ecmJamming</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Suppresses shared targetingData, C3 sharing, IFF-assisted fire, TAG/NARC/beacon sharing, and allied contact-sharing on affected tracked targets. Does not apply generic </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>ecmJamming</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> unless used with an ECM Spike action.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>stealth</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>signatureControl</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>heat</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>ecm</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>networkDisruption</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>iff</t>
+    </r>
+  </si>
+  <si>
+    <t>+2 trackingPenalty when attacking the carrier; +1 DN for enemy acquireTarget tests when in use</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Applies </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>ecmShrouded</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> to the carrier while active. Grants </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>+1 die</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> to </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>acquireTarget</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">. Grants </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>+1 die</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> to </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>epmFilter</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> or </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>holdLink</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>. Applies epmBoosted to allies within 180m</t>
+    </r>
+  </si>
+  <si>
+    <t>Suite active</t>
+  </si>
+  <si>
+    <t>ECM active</t>
+  </si>
+  <si>
+    <t>EPM active</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Target must be at least </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>track status</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>, or part of a network/link</t>
+    </r>
+  </si>
+  <si>
+    <t>Stealth system active</t>
+  </si>
+  <si>
+    <t>Armored Cockpit Cowl</t>
+  </si>
+  <si>
+    <t>Pilot has neural interface; cockpit not disabled</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">If </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>sensorBlind</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, shutdown, or neural-interface crit occurs, pilot suffers </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>+1 Fatigue</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> from feedback. </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>cockpit</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>pilotProtection</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>neuralInterface</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>sealedCockpit</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>cockpit</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>pilotProtection</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>armor</t>
+    </r>
+  </si>
+  <si>
+    <t>Cockpit/head not disabled</t>
+  </si>
+  <si>
+    <t>Reduces pilot Physical damage from Head/Cockpit crits by 1</t>
+  </si>
+  <si>
+    <t>Reduces pilot Physical damage from Head/Cockpit crits by 1. Grants +1 die to Piloting checks made to resist cockpit shock, fall impact, or control feedback.</t>
+  </si>
+  <si>
+    <r>
+      <t>targeting</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>range</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>tracking</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>precision</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>cockpit</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>vdni</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>neuralInterface</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>initiative</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>stability</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>multiAction</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>targeting</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>stabilization</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>recoilCompensation</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>movementFire</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Target at </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>track</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> or </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>lock</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>; ranged attack</t>
+    </r>
+  </si>
+  <si>
+    <t>Pilot has VDNI/neural interface; console Ready</t>
+  </si>
+  <si>
+    <t>Ares Target Projection Suite</t>
+  </si>
+  <si>
+    <t>Ignore 1 point of penalty from Attack movement. At lock, grants +1 gunnery die or +5 AR with ranged attacks</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Disabled by </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>sensorBlind or sensorDegraded.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Disabled while </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>sensorBlind</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> or </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>sensorDegraded</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">On head crit, neural feedback, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>sensorBlind</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>, or head degradation, pilot suffers 1 Fatigue. If the console is disabled while active, pilot immediately suffers 3 fatigue from feedback.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Reduces attack trackingPenalty by 1 against targets at </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>track</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> or better. At </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>lock</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, grants </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>+5 AR</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> for attacks at Far/Extreme range.</t>
+    </r>
+  </si>
+  <si>
+    <t>+1 initiative; +1 die to Piloting; first additional reaction or extra SA in an activation generates 1 less Burn. Grant +1 die to breakLock and holdLink.</t>
+  </si>
+  <si>
+    <t>Cockpit/Harm Provider</t>
+  </si>
+  <si>
+    <t>Targeting/Attack Provider</t>
+  </si>
+  <si>
+    <t>Targeting/Attack; Mobility Provider</t>
+  </si>
+  <si>
+    <t>Improved Actuators Mechanics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Packrat </t>
+  </si>
+  <si>
+    <t>H-7</t>
+  </si>
+  <si>
+    <t>Warrior</t>
+  </si>
+  <si>
+    <t>VTOL</t>
+  </si>
+  <si>
+    <t>Scorpion</t>
+  </si>
+  <si>
+    <t>Tracked</t>
+  </si>
+  <si>
+    <t>Hetzer</t>
+  </si>
+  <si>
+    <t>Ambush</t>
+  </si>
+  <si>
+    <t>Wheeled</t>
+  </si>
+  <si>
+    <t>Condor</t>
+  </si>
+  <si>
+    <t>Hover</t>
+  </si>
+  <si>
+    <t>Vedette</t>
+  </si>
+  <si>
+    <t>Patton</t>
+  </si>
+  <si>
+    <t>Demolisher</t>
+  </si>
+  <si>
+    <t>TR-7</t>
+  </si>
+  <si>
+    <t>Thrush</t>
+  </si>
+  <si>
+    <t>Interceptor</t>
+  </si>
+  <si>
+    <t>Jet</t>
+  </si>
+  <si>
+    <t>Corsair</t>
+  </si>
+  <si>
+    <t>Aerospace</t>
+  </si>
+  <si>
+    <t>F-90</t>
+  </si>
+  <si>
+    <t>Stingray</t>
+  </si>
+  <si>
+    <t>SL-17</t>
+  </si>
+  <si>
+    <t>Shilone</t>
+  </si>
+  <si>
+    <t>Multi-role</t>
+  </si>
+  <si>
+    <t>CHP-WS</t>
+  </si>
+  <si>
+    <t>Chippewa</t>
+  </si>
+  <si>
+    <t>Bomber</t>
+  </si>
+  <si>
+    <t>Slipper</t>
+  </si>
+  <si>
+    <t>Cargo</t>
+  </si>
+  <si>
+    <t>LX-series</t>
+  </si>
+  <si>
+    <t>Bulldog</t>
+  </si>
+  <si>
+    <t>Mao-Heng</t>
+  </si>
+  <si>
+    <t>Cruiser</t>
   </si>
 </sst>
 </file>
@@ -820,7 +2913,7 @@
     <numFmt numFmtId="164" formatCode="_([$€-2]\ * #,##0_);_([$€-2]\ * \(#,##0\);_([$€-2]\ * &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="165" formatCode="_([$€-2]\ * #,##0_);_([$€-2]\ * \(#,##0\);_([$€-2]\ * &quot;-&quot;????_);_(@_)"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -837,14 +2930,26 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color theme="0"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="8"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial Unicode MS"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -857,8 +2962,20 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="1"/>
+        <bgColor theme="1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.34998626667073579"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -875,12 +2992,20 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="0"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -908,19 +3033,7 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -940,17 +3053,45 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="49" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
   <dxfs count="15">
     <dxf>
-      <alignment horizontal="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <numFmt numFmtId="165" formatCode="_([$€-2]\ * #,##0_);_([$€-2]\ * \(#,##0\);_([$€-2]\ * &quot;-&quot;????_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="164" formatCode="_([$€-2]\ * #,##0_);_([$€-2]\ * \(#,##0\);_([$€-2]\ * &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <alignment horizontal="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -960,15 +3101,6 @@
     </dxf>
     <dxf>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="_([$€-2]\ * #,##0_);_([$€-2]\ * \(#,##0\);_([$€-2]\ * &quot;-&quot;????_);_(@_)"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -981,6 +3113,9 @@
     </dxf>
     <dxf>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -1005,7 +3140,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{6E1CAF6D-0208-4038-886B-5074FE9AD89F}" name="Table2" displayName="Table2" ref="A1:U54" totalsRowShown="0" headerRowDxfId="5">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{6E1CAF6D-0208-4038-886B-5074FE9AD89F}" name="Table2" displayName="Table2" ref="A1:U54" totalsRowShown="0" headerRowDxfId="14">
   <autoFilter ref="A1:U54" xr:uid="{6E1CAF6D-0208-4038-886B-5074FE9AD89F}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -1033,24 +3168,24 @@
     <tableColumn id="1" xr3:uid="{99E7DF86-D7C0-49CC-8D73-AC2552E8FD6F}" name="Model"/>
     <tableColumn id="2" xr3:uid="{A0E8F771-705A-4F3C-B718-EE583E5DEEFD}" name="Designation"/>
     <tableColumn id="3" xr3:uid="{60B1183E-274E-4A08-AAB2-D385B8C660BC}" name="Weight Class"/>
-    <tableColumn id="4" xr3:uid="{6DBF2415-F2A3-4C19-A8D4-E685B05EEAA3}" name="Tonnage" dataDxfId="14"/>
+    <tableColumn id="4" xr3:uid="{6DBF2415-F2A3-4C19-A8D4-E685B05EEAA3}" name="Tonnage" dataDxfId="13"/>
     <tableColumn id="5" xr3:uid="{1CB9D459-A39C-4402-B45A-DDADFA5D22EF}" name="Role"/>
-    <tableColumn id="6" xr3:uid="{6FB569F8-DE48-400D-972E-32AA4638F32E}" name="Movement" dataDxfId="13"/>
-    <tableColumn id="7" xr3:uid="{060221F4-9CD2-493C-A589-5AFA79F22A9D}" name="Jump" dataDxfId="12"/>
-    <tableColumn id="8" xr3:uid="{984550C1-15E2-48D3-B147-91E7C7986015}" name="Armor" dataDxfId="11"/>
-    <tableColumn id="9" xr3:uid="{B72349A2-1DA5-49F2-B1BC-0A3328934E65}" name="Structure" dataDxfId="10"/>
-    <tableColumn id="10" xr3:uid="{BDA830D9-B1BA-416B-B84D-9440BD00C757}" name="Heat Dissipation" dataDxfId="9"/>
-    <tableColumn id="11" xr3:uid="{1882AD50-E1A1-4729-839F-58DAA4CFAE55}" name="Thermal Profile" dataDxfId="8"/>
+    <tableColumn id="6" xr3:uid="{6FB569F8-DE48-400D-972E-32AA4638F32E}" name="Movement" dataDxfId="12"/>
+    <tableColumn id="7" xr3:uid="{060221F4-9CD2-493C-A589-5AFA79F22A9D}" name="Jump" dataDxfId="11"/>
+    <tableColumn id="8" xr3:uid="{984550C1-15E2-48D3-B147-91E7C7986015}" name="Armor" dataDxfId="10"/>
+    <tableColumn id="9" xr3:uid="{B72349A2-1DA5-49F2-B1BC-0A3328934E65}" name="Structure" dataDxfId="9"/>
+    <tableColumn id="10" xr3:uid="{BDA830D9-B1BA-416B-B84D-9440BD00C757}" name="Heat Dissipation" dataDxfId="8"/>
+    <tableColumn id="11" xr3:uid="{1882AD50-E1A1-4729-839F-58DAA4CFAE55}" name="Thermal Profile" dataDxfId="7"/>
     <tableColumn id="12" xr3:uid="{269284FF-C57C-4360-8BF9-4EE874395A7A}" name="Weapon Groups"/>
     <tableColumn id="13" xr3:uid="{01B03644-9157-421F-9613-BFC910F63E24}" name="Quirk"/>
-    <tableColumn id="14" xr3:uid="{C1C33636-A054-41D9-8E1F-947C146ABE39}" name="Handling" dataDxfId="4"/>
-    <tableColumn id="15" xr3:uid="{54BCA419-F4D3-45CA-A25D-8CC6D4A82955}" name="System" dataDxfId="3"/>
-    <tableColumn id="16" xr3:uid="{D81E916F-7F83-4E24-A792-A34498F134BD}" name="Chassis" dataDxfId="2"/>
-    <tableColumn id="17" xr3:uid="{A01C96FC-347B-4D67-8B70-97F7B0DCC1CC}" name="Reliability" dataDxfId="0"/>
-    <tableColumn id="18" xr3:uid="{A34999C4-6145-4324-9CD5-ECA43D0A40DA}" name="C-Bills" dataDxfId="1"/>
-    <tableColumn id="19" xr3:uid="{E58EE8B7-3527-416F-89C7-C168D93114AA}" name="Point Cost" dataDxfId="7"/>
+    <tableColumn id="14" xr3:uid="{C1C33636-A054-41D9-8E1F-947C146ABE39}" name="Handling" dataDxfId="6"/>
+    <tableColumn id="15" xr3:uid="{54BCA419-F4D3-45CA-A25D-8CC6D4A82955}" name="System" dataDxfId="5"/>
+    <tableColumn id="16" xr3:uid="{D81E916F-7F83-4E24-A792-A34498F134BD}" name="Chassis" dataDxfId="4"/>
+    <tableColumn id="17" xr3:uid="{A01C96FC-347B-4D67-8B70-97F7B0DCC1CC}" name="Reliability" dataDxfId="3"/>
+    <tableColumn id="18" xr3:uid="{A34999C4-6145-4324-9CD5-ECA43D0A40DA}" name="C-Bills" dataDxfId="2"/>
+    <tableColumn id="19" xr3:uid="{E58EE8B7-3527-416F-89C7-C168D93114AA}" name="Point Cost" dataDxfId="1"/>
     <tableColumn id="20" xr3:uid="{71094815-E36D-4A55-B5AD-3C9E4B6BC59C}" name="Tags"/>
-    <tableColumn id="21" xr3:uid="{4026F33E-50AD-4E08-B447-19387B8F9997}" name="Deploy Cost" dataDxfId="6">
+    <tableColumn id="21" xr3:uid="{4026F33E-50AD-4E08-B447-19387B8F9997}" name="Deploy Cost" dataDxfId="0">
       <calculatedColumnFormula>R2*0.0025</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -1376,7 +3511,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FAFFFFD4-FB15-4BD8-910B-EE32BF634ADE}">
   <dimension ref="A1:V113"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="15.28515625" customWidth="1"/>
@@ -1401,7 +3536,7 @@
     <col min="21" max="21" width="13.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:22">
       <c r="A1" s="1" t="s">
         <v>8</v>
       </c>
@@ -1415,13 +3550,13 @@
         <v>2</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>3</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>4</v>
@@ -1433,7 +3568,7 @@
         <v>6</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
       <c r="L1" s="1" t="s">
         <v>7</v>
@@ -1463,11 +3598,11 @@
         <v>16</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>190</v>
+        <v>182</v>
       </c>
       <c r="V1" s="1"/>
     </row>
-    <row r="2" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:22">
       <c r="A2" t="s">
         <v>10</v>
       </c>
@@ -1481,13 +3616,13 @@
         <v>20</v>
       </c>
       <c r="E2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F2" s="1">
         <v>240</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>144</v>
+        <v>136</v>
       </c>
       <c r="H2" s="12">
         <v>14</v>
@@ -1499,7 +3634,7 @@
         <v>2</v>
       </c>
       <c r="K2" s="12" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="N2" s="12">
         <v>6</v>
@@ -1524,7 +3659,7 @@
         <v>3778</v>
       </c>
     </row>
-    <row r="3" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:22">
       <c r="A3" t="s">
         <v>20</v>
       </c>
@@ -1538,13 +3673,13 @@
         <v>20</v>
       </c>
       <c r="E3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F3" s="1">
         <v>180</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="H3" s="12">
         <v>15</v>
@@ -1556,7 +3691,7 @@
         <v>3</v>
       </c>
       <c r="K3" s="12" t="s">
-        <v>155</v>
+        <v>147</v>
       </c>
       <c r="N3" s="12">
         <v>5</v>
@@ -1581,12 +3716,12 @@
         <v>4035.6</v>
       </c>
     </row>
-    <row r="4" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:22">
       <c r="A4" t="s">
-        <v>237</v>
+        <v>229</v>
       </c>
       <c r="B4" t="s">
-        <v>238</v>
+        <v>230</v>
       </c>
       <c r="C4" t="s">
         <v>12</v>
@@ -1595,13 +3730,13 @@
         <v>20</v>
       </c>
       <c r="E4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F4" s="1">
         <v>180</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>144</v>
+        <v>136</v>
       </c>
       <c r="H4" s="12">
         <v>17</v>
@@ -1613,7 +3748,7 @@
         <v>2</v>
       </c>
       <c r="K4" s="12" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="N4" s="12">
         <v>4</v>
@@ -1628,22 +3763,22 @@
         <v>3</v>
       </c>
       <c r="R4" s="3">
-        <v>1728000</v>
+        <v>499</v>
       </c>
       <c r="S4" s="4">
         <v>23</v>
       </c>
       <c r="U4" s="5">
         <f>R4*0.0025</f>
-        <v>4320</v>
-      </c>
-    </row>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.25">
+        <v>1.2475000000000001</v>
+      </c>
+    </row>
+    <row r="5" spans="1:22">
       <c r="A5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B5" t="s">
         <v>23</v>
-      </c>
-      <c r="B5" t="s">
-        <v>24</v>
       </c>
       <c r="C5" t="s">
         <v>12</v>
@@ -1652,13 +3787,13 @@
         <v>25</v>
       </c>
       <c r="E5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F5" s="1">
         <v>180</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>144</v>
+        <v>136</v>
       </c>
       <c r="H5" s="12">
         <v>19</v>
@@ -1670,7 +3805,7 @@
         <v>3</v>
       </c>
       <c r="K5" s="12" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="N5" s="12">
         <v>5</v>
@@ -1695,12 +3830,12 @@
         <v>4559.375</v>
       </c>
     </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:22">
       <c r="A6" t="s">
+        <v>49</v>
+      </c>
+      <c r="B6" t="s">
         <v>50</v>
-      </c>
-      <c r="B6" t="s">
-        <v>51</v>
       </c>
       <c r="C6" t="s">
         <v>12</v>
@@ -1709,13 +3844,13 @@
         <v>25</v>
       </c>
       <c r="E6" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F6" s="1">
         <v>270</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>144</v>
+        <v>136</v>
       </c>
       <c r="H6" s="12">
         <v>16</v>
@@ -1727,7 +3862,7 @@
         <v>3</v>
       </c>
       <c r="K6" s="12" t="s">
-        <v>168</v>
+        <v>160</v>
       </c>
       <c r="N6" s="12">
         <v>6</v>
@@ -1752,12 +3887,12 @@
         <v>5573.6975000000002</v>
       </c>
     </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:22">
       <c r="A7" t="s">
-        <v>235</v>
+        <v>227</v>
       </c>
       <c r="B7" t="s">
-        <v>236</v>
+        <v>228</v>
       </c>
       <c r="C7" t="s">
         <v>12</v>
@@ -1766,13 +3901,13 @@
         <v>30</v>
       </c>
       <c r="E7" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F7" s="1">
         <v>180</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="H7" s="12">
         <v>17</v>
@@ -1784,7 +3919,7 @@
         <v>3</v>
       </c>
       <c r="K7" s="12" t="s">
-        <v>155</v>
+        <v>147</v>
       </c>
       <c r="N7" s="12">
         <v>5</v>
@@ -1809,12 +3944,12 @@
         <v>8660.9249999999993</v>
       </c>
     </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:22">
       <c r="A8" t="s">
+        <v>24</v>
+      </c>
+      <c r="B8" t="s">
         <v>25</v>
-      </c>
-      <c r="B8" t="s">
-        <v>26</v>
       </c>
       <c r="C8" t="s">
         <v>12</v>
@@ -1823,13 +3958,13 @@
         <v>30</v>
       </c>
       <c r="E8" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F8" s="1">
         <v>150</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="H8" s="12">
         <v>21</v>
@@ -1841,7 +3976,7 @@
         <v>3</v>
       </c>
       <c r="K8" s="12" t="s">
-        <v>168</v>
+        <v>160</v>
       </c>
       <c r="N8" s="12">
         <v>4</v>
@@ -1866,12 +4001,12 @@
         <v>5415.8</v>
       </c>
     </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:22">
       <c r="A9" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B9" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C9" t="s">
         <v>12</v>
@@ -1880,13 +4015,13 @@
         <v>30</v>
       </c>
       <c r="E9" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F9" s="1">
         <v>240</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>144</v>
+        <v>136</v>
       </c>
       <c r="H9" s="12">
         <v>14</v>
@@ -1898,7 +4033,7 @@
         <v>3</v>
       </c>
       <c r="K9" s="12" t="s">
-        <v>155</v>
+        <v>147</v>
       </c>
       <c r="N9" s="12">
         <v>6</v>
@@ -1923,12 +4058,12 @@
         <v>6753.1750000000002</v>
       </c>
     </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:22">
       <c r="A10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B10" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C10" t="s">
         <v>12</v>
@@ -1937,13 +4072,13 @@
         <v>30</v>
       </c>
       <c r="E10" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F10" s="1">
         <v>180</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="H10" s="12">
         <v>18</v>
@@ -1955,7 +4090,7 @@
         <v>2</v>
       </c>
       <c r="K10" s="12" t="s">
-        <v>193</v>
+        <v>185</v>
       </c>
       <c r="N10" s="12">
         <v>5</v>
@@ -1980,12 +4115,12 @@
         <v>5664.1</v>
       </c>
     </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:22">
       <c r="A11" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B11" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C11" t="s">
         <v>12</v>
@@ -1994,13 +4129,13 @@
         <v>30</v>
       </c>
       <c r="E11" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F11" s="1">
         <v>240</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="H11" s="12">
         <v>15</v>
@@ -2012,7 +4147,7 @@
         <v>3</v>
       </c>
       <c r="K11" s="12" t="s">
-        <v>168</v>
+        <v>160</v>
       </c>
       <c r="N11" s="12">
         <v>6</v>
@@ -2037,12 +4172,12 @@
         <v>7355.7250000000004</v>
       </c>
     </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:22">
       <c r="A12" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B12" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C12" t="s">
         <v>12</v>
@@ -2051,13 +4186,13 @@
         <v>35</v>
       </c>
       <c r="E12" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F12" s="1">
         <v>120</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="H12" s="12">
         <v>22</v>
@@ -2069,7 +4204,7 @@
         <v>4</v>
       </c>
       <c r="K12" s="12" t="s">
-        <v>168</v>
+        <v>160</v>
       </c>
       <c r="N12" s="12">
         <v>3</v>
@@ -2094,12 +4229,12 @@
         <v>6123.1500000000005</v>
       </c>
     </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:22">
       <c r="A13" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B13" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C13" t="s">
         <v>12</v>
@@ -2108,13 +4243,13 @@
         <v>35</v>
       </c>
       <c r="E13" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F13" s="1">
         <v>150</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>144</v>
+        <v>136</v>
       </c>
       <c r="H13" s="12">
         <v>20</v>
@@ -2126,7 +4261,7 @@
         <v>3</v>
       </c>
       <c r="K13" s="12" t="s">
-        <v>168</v>
+        <v>160</v>
       </c>
       <c r="N13" s="12">
         <v>4</v>
@@ -2151,12 +4286,12 @@
         <v>6287.0625</v>
       </c>
     </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:22">
       <c r="A14" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B14" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C14" t="s">
         <v>12</v>
@@ -2165,13 +4300,13 @@
         <v>35</v>
       </c>
       <c r="E14" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F14" s="1">
         <v>180</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>144</v>
+        <v>136</v>
       </c>
       <c r="H14" s="12">
         <v>24</v>
@@ -2183,7 +4318,7 @@
         <v>4</v>
       </c>
       <c r="K14" s="12" t="s">
-        <v>172</v>
+        <v>164</v>
       </c>
       <c r="N14" s="12">
         <v>4</v>
@@ -2209,53 +4344,53 @@
         <v>7312.95</v>
       </c>
     </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A15" s="22"/>
-      <c r="B15" s="22"/>
-      <c r="C15" s="22"/>
-      <c r="D15" s="23"/>
-      <c r="E15" s="22"/>
-      <c r="F15" s="23"/>
-      <c r="G15" s="23"/>
-      <c r="H15" s="23"/>
-      <c r="I15" s="23"/>
-      <c r="J15" s="22"/>
-      <c r="K15" s="23"/>
-      <c r="L15" s="22"/>
-      <c r="M15" s="22"/>
-      <c r="N15" s="23"/>
-      <c r="O15" s="23"/>
-      <c r="P15" s="23"/>
-      <c r="Q15" s="23"/>
-      <c r="R15" s="24"/>
-      <c r="S15" s="25"/>
-      <c r="T15" s="22"/>
-      <c r="U15" s="26">
+    <row r="15" spans="1:22">
+      <c r="A15" s="16"/>
+      <c r="B15" s="16"/>
+      <c r="C15" s="16"/>
+      <c r="D15" s="17"/>
+      <c r="E15" s="16"/>
+      <c r="F15" s="17"/>
+      <c r="G15" s="17"/>
+      <c r="H15" s="17"/>
+      <c r="I15" s="17"/>
+      <c r="J15" s="16"/>
+      <c r="K15" s="17"/>
+      <c r="L15" s="16"/>
+      <c r="M15" s="16"/>
+      <c r="N15" s="17"/>
+      <c r="O15" s="17"/>
+      <c r="P15" s="17"/>
+      <c r="Q15" s="17"/>
+      <c r="R15" s="18"/>
+      <c r="S15" s="19"/>
+      <c r="T15" s="16"/>
+      <c r="U15" s="20">
         <f>AVERAGE(R2:R14)</f>
-        <v>2333524.923076923</v>
-      </c>
-    </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.25">
+        <v>2200640.230769231</v>
+      </c>
+    </row>
+    <row r="16" spans="1:22">
       <c r="A16" t="s">
+        <v>51</v>
+      </c>
+      <c r="B16" t="s">
         <v>52</v>
       </c>
-      <c r="B16" t="s">
-        <v>53</v>
-      </c>
       <c r="C16" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D16" s="1">
         <v>40</v>
       </c>
       <c r="E16" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F16" s="1">
         <v>240</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>144</v>
+        <v>136</v>
       </c>
       <c r="H16" s="12">
         <v>15</v>
@@ -2267,7 +4402,7 @@
         <v>3</v>
       </c>
       <c r="K16" s="12" t="s">
-        <v>163</v>
+        <v>147</v>
       </c>
       <c r="N16" s="12">
         <v>6</v>
@@ -2292,27 +4427,27 @@
         <v>9232.4174999999996</v>
       </c>
     </row>
-    <row r="17" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:21">
       <c r="A17" t="s">
+        <v>53</v>
+      </c>
+      <c r="B17" t="s">
         <v>54</v>
       </c>
-      <c r="B17" t="s">
-        <v>55</v>
-      </c>
       <c r="C17" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D17" s="1">
         <v>40</v>
       </c>
       <c r="E17" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F17" s="1">
         <v>180</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="H17" s="12">
         <v>20</v>
@@ -2324,7 +4459,7 @@
         <v>3</v>
       </c>
       <c r="K17" s="12" t="s">
-        <v>168</v>
+        <v>160</v>
       </c>
       <c r="N17" s="12">
         <v>5</v>
@@ -2349,27 +4484,27 @@
         <v>17837.75</v>
       </c>
     </row>
-    <row r="18" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:21">
       <c r="A18" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B18" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C18" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D18" s="1">
         <v>45</v>
       </c>
       <c r="E18" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F18" s="1">
         <v>120</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>144</v>
+        <v>136</v>
       </c>
       <c r="H18" s="12">
         <v>25</v>
@@ -2381,7 +4516,7 @@
         <v>2</v>
       </c>
       <c r="K18" s="12" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="N18" s="12">
         <v>3</v>
@@ -2406,27 +4541,27 @@
         <v>7864.4375</v>
       </c>
     </row>
-    <row r="19" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:21">
       <c r="A19" t="s">
+        <v>26</v>
+      </c>
+      <c r="B19" t="s">
         <v>27</v>
       </c>
-      <c r="B19" t="s">
+      <c r="C19" t="s">
         <v>28</v>
-      </c>
-      <c r="C19" t="s">
-        <v>29</v>
       </c>
       <c r="D19" s="1">
         <v>45</v>
       </c>
       <c r="E19" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F19" s="1">
         <v>180</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="H19" s="12">
         <v>25</v>
@@ -2438,7 +4573,7 @@
         <v>4</v>
       </c>
       <c r="K19" s="12" t="s">
-        <v>172</v>
+        <v>160</v>
       </c>
       <c r="N19" s="12">
         <v>6</v>
@@ -2463,27 +4598,27 @@
         <v>10165.225</v>
       </c>
     </row>
-    <row r="20" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:21">
       <c r="A20" t="s">
+        <v>57</v>
+      </c>
+      <c r="B20" t="s">
         <v>58</v>
       </c>
-      <c r="B20" t="s">
-        <v>59</v>
-      </c>
       <c r="C20" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D20" s="1">
         <v>45</v>
       </c>
       <c r="E20" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F20" s="1">
         <v>120</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>174</v>
+        <v>166</v>
       </c>
       <c r="H20" s="12">
         <v>28</v>
@@ -2495,7 +4630,7 @@
         <v>5</v>
       </c>
       <c r="K20" s="12" t="s">
-        <v>168</v>
+        <v>160</v>
       </c>
       <c r="N20" s="12">
         <v>4</v>
@@ -2520,27 +4655,27 @@
         <v>7843.9575000000004</v>
       </c>
     </row>
-    <row r="21" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:21">
       <c r="A21" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B21" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C21" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D21" s="1">
         <v>50</v>
       </c>
       <c r="E21" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F21" s="1">
         <v>120</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>144</v>
+        <v>136</v>
       </c>
       <c r="H21" s="12">
         <v>33</v>
@@ -2552,7 +4687,7 @@
         <v>3</v>
       </c>
       <c r="K21" s="12" t="s">
-        <v>168</v>
+        <v>160</v>
       </c>
       <c r="N21" s="12">
         <v>4</v>
@@ -2577,27 +4712,27 @@
         <v>23621.25</v>
       </c>
     </row>
-    <row r="22" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:21">
       <c r="A22" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B22" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C22" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D22" s="1">
         <v>50</v>
       </c>
       <c r="E22" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F22" s="1">
         <v>120</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>144</v>
+        <v>136</v>
       </c>
       <c r="H22" s="12">
         <v>38</v>
@@ -2609,7 +4744,7 @@
         <v>3</v>
       </c>
       <c r="K22" s="12" t="s">
-        <v>163</v>
+        <v>155</v>
       </c>
       <c r="N22" s="12">
         <v>3</v>
@@ -2634,27 +4769,27 @@
         <v>8594.6875</v>
       </c>
     </row>
-    <row r="23" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:21">
       <c r="A23" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B23" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C23" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D23" s="1">
         <v>50</v>
       </c>
       <c r="E23" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F23" s="1">
         <v>150</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="H23" s="12">
         <v>27</v>
@@ -2666,7 +4801,7 @@
         <v>4</v>
       </c>
       <c r="K23" s="12" t="s">
-        <v>172</v>
+        <v>164</v>
       </c>
       <c r="N23" s="12">
         <v>5</v>
@@ -2691,27 +4826,27 @@
         <v>12270.3125</v>
       </c>
     </row>
-    <row r="24" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:21">
       <c r="A24" t="s">
+        <v>75</v>
+      </c>
+      <c r="B24" t="s">
         <v>76</v>
       </c>
-      <c r="B24" t="s">
-        <v>77</v>
-      </c>
       <c r="C24" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D24" s="1">
         <v>50</v>
       </c>
       <c r="E24" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F24" s="1">
         <v>180</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="H24" s="12">
         <v>29</v>
@@ -2723,7 +4858,7 @@
         <v>5</v>
       </c>
       <c r="K24" s="12" t="s">
-        <v>172</v>
+        <v>164</v>
       </c>
       <c r="N24" s="12">
         <v>5</v>
@@ -2748,27 +4883,27 @@
         <v>24350.625</v>
       </c>
     </row>
-    <row r="25" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:21">
       <c r="A25" t="s">
+        <v>29</v>
+      </c>
+      <c r="B25" t="s">
         <v>30</v>
       </c>
-      <c r="B25" t="s">
-        <v>31</v>
-      </c>
       <c r="C25" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D25" s="1">
         <v>55</v>
       </c>
       <c r="E25" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F25" s="1">
         <v>150</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="H25" s="12">
         <v>29</v>
@@ -2780,7 +4915,7 @@
         <v>4</v>
       </c>
       <c r="K25" s="12" t="s">
-        <v>168</v>
+        <v>160</v>
       </c>
       <c r="N25" s="12">
         <v>4</v>
@@ -2805,27 +4940,27 @@
         <v>12160.2675</v>
       </c>
     </row>
-    <row r="26" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:21">
       <c r="A26" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B26" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C26" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D26" s="1">
         <v>55</v>
       </c>
       <c r="E26" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F26" s="1">
         <v>150</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="H26" s="12">
         <v>31</v>
@@ -2837,7 +4972,7 @@
         <v>3</v>
       </c>
       <c r="K26" s="12" t="s">
-        <v>168</v>
+        <v>160</v>
       </c>
       <c r="N26" s="12">
         <v>5</v>
@@ -2862,27 +4997,27 @@
         <v>11125.6425</v>
       </c>
     </row>
-    <row r="27" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:21">
       <c r="A27" t="s">
+        <v>32</v>
+      </c>
+      <c r="B27" t="s">
         <v>33</v>
       </c>
-      <c r="B27" t="s">
-        <v>34</v>
-      </c>
       <c r="C27" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D27" s="1">
         <v>55</v>
       </c>
       <c r="E27" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F27" s="1">
         <v>150</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="H27" s="12">
         <v>30</v>
@@ -2894,7 +5029,7 @@
         <v>5</v>
       </c>
       <c r="K27" s="12" t="s">
-        <v>172</v>
+        <v>164</v>
       </c>
       <c r="N27" s="12">
         <v>5</v>
@@ -2920,45 +5055,45 @@
         <v>11947.1425</v>
       </c>
     </row>
-    <row r="28" spans="1:21" s="22" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="D28" s="23"/>
-      <c r="F28" s="23"/>
-      <c r="G28" s="23"/>
-      <c r="H28" s="23"/>
-      <c r="I28" s="23"/>
-      <c r="K28" s="23"/>
-      <c r="N28" s="23"/>
-      <c r="O28" s="23"/>
-      <c r="P28" s="23"/>
-      <c r="Q28" s="23"/>
-      <c r="R28" s="24"/>
-      <c r="S28" s="25"/>
-      <c r="U28" s="26">
+    <row r="28" spans="1:21" s="16" customFormat="1">
+      <c r="D28" s="17"/>
+      <c r="F28" s="17"/>
+      <c r="G28" s="17"/>
+      <c r="H28" s="17"/>
+      <c r="I28" s="17"/>
+      <c r="K28" s="17"/>
+      <c r="N28" s="17"/>
+      <c r="O28" s="17"/>
+      <c r="P28" s="17"/>
+      <c r="Q28" s="17"/>
+      <c r="R28" s="18"/>
+      <c r="S28" s="19"/>
+      <c r="U28" s="20">
         <f>AVERAGE(R16:R27)</f>
         <v>5233790.5</v>
       </c>
     </row>
-    <row r="29" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:21">
       <c r="A29" t="s">
+        <v>97</v>
+      </c>
+      <c r="B29" t="s">
         <v>98</v>
       </c>
-      <c r="B29" t="s">
-        <v>99</v>
-      </c>
       <c r="C29" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D29" s="1">
         <v>60</v>
       </c>
       <c r="E29" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F29" s="1">
         <v>120</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="H29" s="12">
         <v>36</v>
@@ -2970,7 +5105,7 @@
         <v>3</v>
       </c>
       <c r="K29" s="12" t="s">
-        <v>155</v>
+        <v>147</v>
       </c>
       <c r="N29" s="12">
         <v>3</v>
@@ -2995,27 +5130,27 @@
         <v>14215.025</v>
       </c>
     </row>
-    <row r="30" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:21">
       <c r="A30" t="s">
+        <v>77</v>
+      </c>
+      <c r="B30" t="s">
         <v>78</v>
       </c>
-      <c r="B30" t="s">
-        <v>79</v>
-      </c>
       <c r="C30" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D30" s="1">
         <v>60</v>
       </c>
       <c r="E30" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F30" s="1">
         <v>150</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>144</v>
+        <v>136</v>
       </c>
       <c r="H30" s="12">
         <v>35</v>
@@ -3027,7 +5162,7 @@
         <v>3</v>
       </c>
       <c r="K30" s="12" t="s">
-        <v>168</v>
+        <v>160</v>
       </c>
       <c r="N30" s="12">
         <v>5</v>
@@ -3052,27 +5187,27 @@
         <v>12335.2</v>
       </c>
     </row>
-    <row r="31" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:21">
       <c r="A31" t="s">
+        <v>79</v>
+      </c>
+      <c r="B31" t="s">
         <v>80</v>
       </c>
-      <c r="B31" t="s">
-        <v>81</v>
-      </c>
       <c r="C31" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D31" s="1">
         <v>60</v>
       </c>
       <c r="E31" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F31" s="1">
         <v>120</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>144</v>
+        <v>136</v>
       </c>
       <c r="H31" s="12">
         <v>30</v>
@@ -3084,7 +5219,7 @@
         <v>3</v>
       </c>
       <c r="K31" s="12" t="s">
-        <v>193</v>
+        <v>185</v>
       </c>
       <c r="N31" s="12">
         <v>3</v>
@@ -3109,27 +5244,27 @@
         <v>12132</v>
       </c>
     </row>
-    <row r="32" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:21">
       <c r="A32" t="s">
-        <v>239</v>
+        <v>231</v>
       </c>
       <c r="B32" t="s">
-        <v>240</v>
+        <v>232</v>
       </c>
       <c r="C32" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D32" s="1">
         <v>60</v>
       </c>
       <c r="E32" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F32" s="1">
         <v>150</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="H32" s="12">
         <v>30</v>
@@ -3141,7 +5276,7 @@
         <v>3</v>
       </c>
       <c r="K32" s="12" t="s">
-        <v>172</v>
+        <v>164</v>
       </c>
       <c r="N32" s="12">
         <v>4</v>
@@ -3166,27 +5301,27 @@
         <v>14474.4</v>
       </c>
     </row>
-    <row r="33" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:21">
       <c r="A33" t="s">
+        <v>125</v>
+      </c>
+      <c r="B33" t="s">
         <v>126</v>
       </c>
-      <c r="B33" t="s">
-        <v>127</v>
-      </c>
       <c r="C33" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D33" s="1">
         <v>65</v>
       </c>
       <c r="E33" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F33" s="1">
         <v>120</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="H33" s="12">
         <v>41</v>
@@ -3198,7 +5333,7 @@
         <v>3</v>
       </c>
       <c r="K33" s="12" t="s">
-        <v>163</v>
+        <v>155</v>
       </c>
       <c r="N33" s="12">
         <v>4</v>
@@ -3223,27 +5358,27 @@
         <v>29601.275000000001</v>
       </c>
     </row>
-    <row r="34" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:21">
       <c r="A34" t="s">
+        <v>81</v>
+      </c>
+      <c r="B34" t="s">
         <v>82</v>
       </c>
-      <c r="B34" t="s">
-        <v>83</v>
-      </c>
       <c r="C34" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D34" s="1">
         <v>65</v>
       </c>
       <c r="E34" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F34" s="1">
         <v>120</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>144</v>
+        <v>136</v>
       </c>
       <c r="H34" s="12">
         <v>44</v>
@@ -3255,7 +5390,7 @@
         <v>4</v>
       </c>
       <c r="K34" s="12" t="s">
-        <v>172</v>
+        <v>164</v>
       </c>
       <c r="N34" s="12">
         <v>3</v>
@@ -3280,27 +5415,27 @@
         <v>13171.4</v>
       </c>
     </row>
-    <row r="35" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:21">
       <c r="A35" t="s">
+        <v>83</v>
+      </c>
+      <c r="B35" t="s">
         <v>84</v>
       </c>
-      <c r="B35" t="s">
-        <v>85</v>
-      </c>
       <c r="C35" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D35" s="1">
         <v>65</v>
       </c>
       <c r="E35" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F35" s="1">
         <v>120</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="H35" s="12">
         <v>36</v>
@@ -3312,7 +5447,7 @@
         <v>4</v>
       </c>
       <c r="K35" s="12" t="s">
-        <v>168</v>
+        <v>160</v>
       </c>
       <c r="N35" s="12">
         <v>3</v>
@@ -3337,27 +5472,27 @@
         <v>14227.8125</v>
       </c>
     </row>
-    <row r="36" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:21">
       <c r="A36" t="s">
+        <v>85</v>
+      </c>
+      <c r="B36" t="s">
         <v>86</v>
       </c>
-      <c r="B36" t="s">
-        <v>87</v>
-      </c>
       <c r="C36" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D36" s="1">
         <v>70</v>
       </c>
       <c r="E36" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F36" s="1">
         <v>120</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>144</v>
+        <v>136</v>
       </c>
       <c r="H36" s="12">
         <v>41</v>
@@ -3369,7 +5504,7 @@
         <v>4</v>
       </c>
       <c r="K36" s="12" t="s">
-        <v>168</v>
+        <v>160</v>
       </c>
       <c r="N36" s="12">
         <v>3</v>
@@ -3394,27 +5529,27 @@
         <v>15452.432500000001</v>
       </c>
     </row>
-    <row r="37" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:21">
       <c r="A37" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B37" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C37" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D37" s="1">
         <v>70</v>
       </c>
       <c r="E37" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F37" s="1">
         <v>120</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="H37" s="12">
         <v>42</v>
@@ -3423,10 +5558,10 @@
         <v>24</v>
       </c>
       <c r="J37" s="12">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K37" s="12" t="s">
-        <v>174</v>
+        <v>166</v>
       </c>
       <c r="N37" s="12">
         <v>5</v>
@@ -3451,27 +5586,27 @@
         <v>15061.432500000001</v>
       </c>
     </row>
-    <row r="38" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:21">
       <c r="A38" t="s">
+        <v>87</v>
+      </c>
+      <c r="B38" t="s">
         <v>88</v>
       </c>
-      <c r="B38" t="s">
-        <v>89</v>
-      </c>
       <c r="C38" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D38" s="1">
         <v>70</v>
       </c>
       <c r="E38" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F38" s="1">
         <v>120</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>144</v>
+        <v>136</v>
       </c>
       <c r="H38" s="12">
         <v>44</v>
@@ -3483,7 +5618,7 @@
         <v>5</v>
       </c>
       <c r="K38" s="12" t="s">
-        <v>179</v>
+        <v>160</v>
       </c>
       <c r="N38" s="12">
         <v>3</v>
@@ -3495,7 +5630,7 @@
         <v>5</v>
       </c>
       <c r="Q38" s="12">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R38" s="3">
         <v>6070983</v>
@@ -3508,27 +5643,27 @@
         <v>15177.4575</v>
       </c>
     </row>
-    <row r="39" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:21">
       <c r="A39" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B39" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C39" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D39" s="1">
         <v>75</v>
       </c>
       <c r="E39" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F39" s="1">
         <v>120</v>
       </c>
       <c r="G39" s="1" t="s">
-        <v>144</v>
+        <v>136</v>
       </c>
       <c r="H39" s="12">
         <v>49</v>
@@ -3540,19 +5675,19 @@
         <v>5</v>
       </c>
       <c r="K39" s="12" t="s">
-        <v>174</v>
+        <v>160</v>
       </c>
       <c r="N39" s="12">
         <v>3</v>
       </c>
       <c r="O39" s="12">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P39" s="1">
         <v>5</v>
       </c>
       <c r="Q39" s="12">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="R39" s="3">
         <v>7136938</v>
@@ -3565,27 +5700,27 @@
         <v>17842.345000000001</v>
       </c>
     </row>
-    <row r="40" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:21">
       <c r="A40" t="s">
+        <v>89</v>
+      </c>
+      <c r="B40" t="s">
         <v>90</v>
       </c>
-      <c r="B40" t="s">
-        <v>91</v>
-      </c>
       <c r="C40" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D40" s="1">
         <v>75</v>
       </c>
       <c r="E40" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F40" s="1">
         <v>120</v>
       </c>
       <c r="G40" s="1" t="s">
-        <v>144</v>
+        <v>136</v>
       </c>
       <c r="H40" s="12">
         <v>41</v>
@@ -3597,7 +5732,7 @@
         <v>4</v>
       </c>
       <c r="K40" s="12" t="s">
-        <v>172</v>
+        <v>164</v>
       </c>
       <c r="N40" s="12">
         <v>4</v>
@@ -3622,27 +5757,27 @@
         <v>15058.4575</v>
       </c>
     </row>
-    <row r="41" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:21">
       <c r="A41" t="s">
+        <v>103</v>
+      </c>
+      <c r="B41" t="s">
         <v>104</v>
       </c>
-      <c r="B41" t="s">
-        <v>105</v>
-      </c>
       <c r="C41" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D41" s="1">
         <v>75</v>
       </c>
       <c r="E41" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F41" s="1">
         <v>120</v>
       </c>
       <c r="G41" s="1" t="s">
-        <v>144</v>
+        <v>136</v>
       </c>
       <c r="H41" s="12">
         <v>42</v>
@@ -3654,7 +5789,7 @@
         <v>4</v>
       </c>
       <c r="K41" s="12" t="s">
-        <v>168</v>
+        <v>160</v>
       </c>
       <c r="N41" s="12">
         <v>3</v>
@@ -3680,45 +5815,45 @@
         <v>16568.125</v>
       </c>
     </row>
-    <row r="42" spans="1:21" s="22" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="D42" s="23"/>
-      <c r="F42" s="23"/>
-      <c r="G42" s="23"/>
-      <c r="H42" s="23"/>
-      <c r="I42" s="23"/>
-      <c r="K42" s="23"/>
-      <c r="N42" s="23"/>
-      <c r="O42" s="23"/>
-      <c r="P42" s="23"/>
-      <c r="Q42" s="23"/>
-      <c r="R42" s="24"/>
-      <c r="S42" s="25"/>
-      <c r="U42" s="26">
+    <row r="42" spans="1:21" s="16" customFormat="1">
+      <c r="D42" s="17"/>
+      <c r="F42" s="17"/>
+      <c r="G42" s="17"/>
+      <c r="H42" s="17"/>
+      <c r="I42" s="17"/>
+      <c r="K42" s="17"/>
+      <c r="N42" s="17"/>
+      <c r="O42" s="17"/>
+      <c r="P42" s="17"/>
+      <c r="Q42" s="17"/>
+      <c r="R42" s="18"/>
+      <c r="S42" s="19"/>
+      <c r="U42" s="20">
         <f>AVERAGE(R29:R41)</f>
         <v>6317457.307692308</v>
       </c>
     </row>
-    <row r="43" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:21">
       <c r="A43" t="s">
+        <v>91</v>
+      </c>
+      <c r="B43" t="s">
         <v>92</v>
       </c>
-      <c r="B43" t="s">
-        <v>93</v>
-      </c>
       <c r="C43" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D43" s="1">
         <v>80</v>
       </c>
       <c r="E43" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F43" s="1">
         <v>90</v>
       </c>
       <c r="G43" s="1" t="s">
-        <v>144</v>
+        <v>136</v>
       </c>
       <c r="H43" s="12">
         <v>51</v>
@@ -3730,7 +5865,7 @@
         <v>5</v>
       </c>
       <c r="K43" s="12" t="s">
-        <v>185</v>
+        <v>171</v>
       </c>
       <c r="N43" s="12">
         <v>2</v>
@@ -3755,27 +5890,27 @@
         <v>16495.424999999999</v>
       </c>
     </row>
-    <row r="44" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:21">
       <c r="A44" t="s">
+        <v>107</v>
+      </c>
+      <c r="B44" t="s">
         <v>108</v>
       </c>
-      <c r="B44" t="s">
-        <v>109</v>
-      </c>
       <c r="C44" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D44" s="1">
         <v>80</v>
       </c>
       <c r="E44" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F44" s="1">
         <v>120</v>
       </c>
       <c r="G44" s="1" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="H44" s="12">
         <v>42</v>
@@ -3787,7 +5922,7 @@
         <v>4</v>
       </c>
       <c r="K44" s="12" t="s">
-        <v>168</v>
+        <v>160</v>
       </c>
       <c r="N44" s="12">
         <v>3</v>
@@ -3812,27 +5947,27 @@
         <v>19128</v>
       </c>
     </row>
-    <row r="45" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:21">
       <c r="A45" t="s">
+        <v>119</v>
+      </c>
+      <c r="B45" t="s">
         <v>120</v>
       </c>
-      <c r="B45" t="s">
-        <v>121</v>
-      </c>
       <c r="C45" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D45" s="1">
         <v>80</v>
       </c>
       <c r="E45" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F45" s="1">
         <v>120</v>
       </c>
       <c r="G45" s="1" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="H45" s="12">
         <v>36</v>
@@ -3844,7 +5979,7 @@
         <v>4</v>
       </c>
       <c r="K45" s="12" t="s">
-        <v>168</v>
+        <v>160</v>
       </c>
       <c r="N45" s="12">
         <v>5</v>
@@ -3869,27 +6004,27 @@
         <v>21280.799999999999</v>
       </c>
     </row>
-    <row r="46" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:21">
       <c r="A46" t="s">
+        <v>93</v>
+      </c>
+      <c r="B46" t="s">
         <v>94</v>
       </c>
-      <c r="B46" t="s">
-        <v>95</v>
-      </c>
       <c r="C46" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D46" s="1">
         <v>85</v>
       </c>
       <c r="E46" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F46" s="1">
         <v>120</v>
       </c>
       <c r="G46" s="1" t="s">
-        <v>144</v>
+        <v>136</v>
       </c>
       <c r="H46" s="12">
         <v>47</v>
@@ -3901,7 +6036,7 @@
         <v>4</v>
       </c>
       <c r="K46" s="12" t="s">
-        <v>179</v>
+        <v>166</v>
       </c>
       <c r="N46" s="12">
         <v>4</v>
@@ -3926,27 +6061,27 @@
         <v>21253.107500000002</v>
       </c>
     </row>
-    <row r="47" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:21">
       <c r="A47" t="s">
+        <v>105</v>
+      </c>
+      <c r="B47" t="s">
         <v>106</v>
       </c>
-      <c r="B47" t="s">
-        <v>107</v>
-      </c>
       <c r="C47" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D47" s="1">
         <v>85</v>
       </c>
       <c r="E47" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F47" s="1">
         <v>90</v>
       </c>
       <c r="G47" s="1" t="s">
-        <v>144</v>
+        <v>136</v>
       </c>
       <c r="H47" s="12">
         <v>54</v>
@@ -3958,7 +6093,7 @@
         <v>4</v>
       </c>
       <c r="K47" s="12" t="s">
-        <v>168</v>
+        <v>160</v>
       </c>
       <c r="N47" s="12">
         <v>2</v>
@@ -3983,27 +6118,27 @@
         <v>18659.5625</v>
       </c>
     </row>
-    <row r="48" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:21">
       <c r="A48" t="s">
+        <v>109</v>
+      </c>
+      <c r="B48" t="s">
         <v>110</v>
       </c>
-      <c r="B48" t="s">
-        <v>111</v>
-      </c>
       <c r="C48" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D48" s="1">
         <v>90</v>
       </c>
       <c r="E48" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F48" s="1">
         <v>90</v>
       </c>
       <c r="G48" s="1" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="H48" s="12">
         <v>50</v>
@@ -4015,7 +6150,7 @@
         <v>5</v>
       </c>
       <c r="K48" s="12" t="s">
-        <v>174</v>
+        <v>164</v>
       </c>
       <c r="N48" s="12">
         <v>4</v>
@@ -4040,27 +6175,27 @@
         <v>22340.2</v>
       </c>
     </row>
-    <row r="49" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:21">
       <c r="A49" t="s">
+        <v>121</v>
+      </c>
+      <c r="B49" t="s">
         <v>122</v>
       </c>
-      <c r="B49" t="s">
-        <v>123</v>
-      </c>
       <c r="C49" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D49" s="1">
         <v>90</v>
       </c>
       <c r="E49" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F49" s="1">
         <v>90</v>
       </c>
       <c r="G49" s="1" t="s">
-        <v>144</v>
+        <v>136</v>
       </c>
       <c r="H49" s="12">
         <v>45</v>
@@ -4072,7 +6207,7 @@
         <v>3</v>
       </c>
       <c r="K49" s="12" t="s">
-        <v>193</v>
+        <v>185</v>
       </c>
       <c r="N49" s="12">
         <v>2</v>
@@ -4097,27 +6232,27 @@
         <v>45999</v>
       </c>
     </row>
-    <row r="50" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:21">
       <c r="A50" t="s">
+        <v>111</v>
+      </c>
+      <c r="B50" t="s">
         <v>112</v>
       </c>
-      <c r="B50" t="s">
-        <v>113</v>
-      </c>
       <c r="C50" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D50" s="1">
         <v>95</v>
       </c>
       <c r="E50" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F50" s="1">
         <v>120</v>
       </c>
       <c r="G50" s="1" t="s">
-        <v>144</v>
+        <v>136</v>
       </c>
       <c r="H50" s="12">
         <v>40</v>
@@ -4129,7 +6264,7 @@
         <v>3</v>
       </c>
       <c r="K50" s="12" t="s">
-        <v>172</v>
+        <v>164</v>
       </c>
       <c r="N50" s="12">
         <v>4</v>
@@ -4154,27 +6289,27 @@
         <v>24560.817500000001</v>
       </c>
     </row>
-    <row r="51" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:21">
       <c r="A51" t="s">
+        <v>113</v>
+      </c>
+      <c r="B51" t="s">
         <v>114</v>
       </c>
-      <c r="B51" t="s">
-        <v>115</v>
-      </c>
       <c r="C51" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D51" s="1">
         <v>100</v>
       </c>
       <c r="E51" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F51" s="1">
         <v>60</v>
       </c>
       <c r="G51" s="1" t="s">
-        <v>144</v>
+        <v>136</v>
       </c>
       <c r="H51" s="12">
         <v>55</v>
@@ -4186,7 +6321,7 @@
         <v>3</v>
       </c>
       <c r="K51" s="12" t="s">
-        <v>168</v>
+        <v>160</v>
       </c>
       <c r="N51" s="12">
         <v>1</v>
@@ -4211,27 +6346,27 @@
         <v>19241.6675</v>
       </c>
     </row>
-    <row r="52" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:21">
       <c r="A52" t="s">
+        <v>115</v>
+      </c>
+      <c r="B52" t="s">
         <v>116</v>
       </c>
-      <c r="B52" t="s">
-        <v>117</v>
-      </c>
       <c r="C52" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D52" s="1">
         <v>100</v>
       </c>
       <c r="E52" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F52" s="1">
         <v>90</v>
       </c>
       <c r="G52" s="1" t="s">
-        <v>144</v>
+        <v>136</v>
       </c>
       <c r="H52" s="12">
         <v>64</v>
@@ -4243,7 +6378,7 @@
         <v>4</v>
       </c>
       <c r="K52" s="12" t="s">
-        <v>179</v>
+        <v>164</v>
       </c>
       <c r="N52" s="12">
         <v>3</v>
@@ -4268,27 +6403,27 @@
         <v>24065</v>
       </c>
     </row>
-    <row r="53" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:21">
       <c r="A53" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B53" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C53" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D53" s="1">
         <v>100</v>
       </c>
       <c r="E53" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F53" s="1">
         <v>90</v>
       </c>
       <c r="G53" s="1" t="s">
-        <v>144</v>
+        <v>136</v>
       </c>
       <c r="H53" s="1">
         <v>63</v>
@@ -4300,7 +6435,7 @@
         <v>4</v>
       </c>
       <c r="K53" s="12" t="s">
-        <v>174</v>
+        <v>166</v>
       </c>
       <c r="N53" s="12">
         <v>1</v>
@@ -4325,27 +6460,27 @@
         <v>55995</v>
       </c>
     </row>
-    <row r="54" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:21">
       <c r="A54" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B54" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C54" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D54" s="1">
         <v>100</v>
       </c>
       <c r="E54" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F54" s="1">
         <v>90</v>
       </c>
       <c r="G54" s="1" t="s">
-        <v>144</v>
+        <v>136</v>
       </c>
       <c r="H54" s="1">
         <v>66</v>
@@ -4357,7 +6492,7 @@
         <v>4</v>
       </c>
       <c r="K54" s="12" t="s">
-        <v>163</v>
+        <v>155</v>
       </c>
       <c r="N54" s="12">
         <v>2</v>
@@ -4383,200 +6518,200 @@
         <v>25305</v>
       </c>
     </row>
-    <row r="55" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:21">
       <c r="U55" s="10"/>
     </row>
-    <row r="61" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:21">
       <c r="J61" s="13"/>
     </row>
-    <row r="62" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:21">
       <c r="J62" s="1"/>
       <c r="K62" s="1"/>
     </row>
-    <row r="63" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="K63" s="16"/>
-    </row>
-    <row r="64" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="K64" s="16"/>
-    </row>
-    <row r="65" spans="3:11" x14ac:dyDescent="0.25">
-      <c r="K65" s="16"/>
-    </row>
-    <row r="66" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:21">
+      <c r="K63" s="14"/>
+    </row>
+    <row r="64" spans="1:21">
+      <c r="K64" s="14"/>
+    </row>
+    <row r="65" spans="3:11">
+      <c r="K65" s="14"/>
+    </row>
+    <row r="66" spans="3:11">
       <c r="C66" s="13"/>
       <c r="D66" s="13"/>
       <c r="E66" s="13"/>
-      <c r="K66" s="16"/>
-    </row>
-    <row r="67" spans="3:11" x14ac:dyDescent="0.25">
-      <c r="C67" s="16"/>
-      <c r="D67" s="16"/>
-      <c r="E67" s="16"/>
-      <c r="K67" s="16"/>
-    </row>
-    <row r="68" spans="3:11" x14ac:dyDescent="0.25">
-      <c r="C68" s="16"/>
-      <c r="D68" s="16"/>
-      <c r="E68" s="16"/>
-      <c r="K68" s="16"/>
-    </row>
-    <row r="69" spans="3:11" x14ac:dyDescent="0.25">
-      <c r="C69" s="16"/>
-      <c r="D69" s="16"/>
-      <c r="E69" s="16"/>
-      <c r="K69" s="16"/>
-    </row>
-    <row r="70" spans="3:11" x14ac:dyDescent="0.25">
-      <c r="C70" s="16"/>
-      <c r="D70" s="16"/>
-      <c r="E70" s="16"/>
-      <c r="K70" s="16"/>
-    </row>
-    <row r="71" spans="3:11" x14ac:dyDescent="0.25">
-      <c r="C71" s="16"/>
-      <c r="D71" s="16"/>
-      <c r="E71" s="16"/>
-      <c r="K71" s="16"/>
-    </row>
-    <row r="72" spans="3:11" x14ac:dyDescent="0.25">
-      <c r="C72" s="16"/>
-      <c r="D72" s="16"/>
-      <c r="E72" s="16"/>
-      <c r="K72" s="16"/>
-    </row>
-    <row r="73" spans="3:11" x14ac:dyDescent="0.25">
-      <c r="C73" s="16"/>
-      <c r="D73" s="16"/>
-      <c r="E73" s="16"/>
-      <c r="K73" s="16"/>
-    </row>
-    <row r="74" spans="3:11" x14ac:dyDescent="0.25">
-      <c r="C74" s="16"/>
-      <c r="D74" s="16"/>
-      <c r="E74" s="16"/>
-      <c r="K74" s="16"/>
-    </row>
-    <row r="75" spans="3:11" x14ac:dyDescent="0.25">
-      <c r="C75" s="16"/>
-      <c r="D75" s="16"/>
-      <c r="E75" s="16"/>
-    </row>
-    <row r="76" spans="3:11" x14ac:dyDescent="0.25">
-      <c r="C76" s="16"/>
-      <c r="D76" s="16"/>
-      <c r="E76" s="16"/>
-      <c r="K76" s="16"/>
-    </row>
-    <row r="77" spans="3:11" x14ac:dyDescent="0.25">
-      <c r="C77" s="16"/>
-      <c r="D77" s="16"/>
-      <c r="E77" s="16"/>
-      <c r="K77" s="16"/>
-    </row>
-    <row r="78" spans="3:11" x14ac:dyDescent="0.25">
-      <c r="C78" s="16"/>
-      <c r="D78" s="16"/>
-      <c r="E78" s="16"/>
-      <c r="K78" s="16"/>
-    </row>
-    <row r="79" spans="3:11" x14ac:dyDescent="0.25">
-      <c r="K79" s="16"/>
-    </row>
-    <row r="80" spans="3:11" x14ac:dyDescent="0.25">
-      <c r="K80" s="16"/>
-    </row>
-    <row r="81" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K81" s="16"/>
-    </row>
-    <row r="82" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K82" s="16"/>
-    </row>
-    <row r="83" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K83" s="16"/>
-    </row>
-    <row r="84" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K84" s="16"/>
-    </row>
-    <row r="85" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K85" s="16"/>
-    </row>
-    <row r="86" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K86" s="16"/>
-    </row>
-    <row r="87" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K87" s="16"/>
-    </row>
-    <row r="89" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K89" s="16"/>
-    </row>
-    <row r="90" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K90" s="16"/>
-    </row>
-    <row r="91" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K91" s="16"/>
-    </row>
-    <row r="92" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K92" s="16"/>
-    </row>
-    <row r="93" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K93" s="16"/>
-    </row>
-    <row r="94" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K94" s="16"/>
-    </row>
-    <row r="95" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K95" s="16"/>
-    </row>
-    <row r="96" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K96" s="16"/>
-    </row>
-    <row r="97" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K97" s="16"/>
-    </row>
-    <row r="98" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K98" s="16"/>
-    </row>
-    <row r="99" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K99" s="16"/>
-    </row>
-    <row r="100" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K100" s="16"/>
-    </row>
-    <row r="102" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K102" s="16"/>
-    </row>
-    <row r="103" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K103" s="16"/>
-    </row>
-    <row r="104" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K104" s="16"/>
-    </row>
-    <row r="105" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K105" s="16"/>
-    </row>
-    <row r="106" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K106" s="16"/>
-    </row>
-    <row r="107" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K107" s="16"/>
-    </row>
-    <row r="108" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K108" s="16"/>
-    </row>
-    <row r="109" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K109" s="16"/>
-    </row>
-    <row r="110" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K110" s="16"/>
-    </row>
-    <row r="111" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K111" s="16"/>
-    </row>
-    <row r="112" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K112" s="16"/>
-    </row>
-    <row r="113" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K113" s="16"/>
+      <c r="K66" s="14"/>
+    </row>
+    <row r="67" spans="3:11">
+      <c r="C67" s="14"/>
+      <c r="D67" s="14"/>
+      <c r="E67" s="14"/>
+      <c r="K67" s="14"/>
+    </row>
+    <row r="68" spans="3:11">
+      <c r="C68" s="14"/>
+      <c r="D68" s="14"/>
+      <c r="E68" s="14"/>
+      <c r="K68" s="14"/>
+    </row>
+    <row r="69" spans="3:11">
+      <c r="C69" s="14"/>
+      <c r="D69" s="14"/>
+      <c r="E69" s="14"/>
+      <c r="K69" s="14"/>
+    </row>
+    <row r="70" spans="3:11">
+      <c r="C70" s="14"/>
+      <c r="D70" s="14"/>
+      <c r="E70" s="14"/>
+      <c r="K70" s="14"/>
+    </row>
+    <row r="71" spans="3:11">
+      <c r="C71" s="14"/>
+      <c r="D71" s="14"/>
+      <c r="E71" s="14"/>
+      <c r="K71" s="14"/>
+    </row>
+    <row r="72" spans="3:11">
+      <c r="C72" s="14"/>
+      <c r="D72" s="14"/>
+      <c r="E72" s="14"/>
+      <c r="K72" s="14"/>
+    </row>
+    <row r="73" spans="3:11">
+      <c r="C73" s="14"/>
+      <c r="D73" s="14"/>
+      <c r="E73" s="14"/>
+      <c r="K73" s="14"/>
+    </row>
+    <row r="74" spans="3:11">
+      <c r="C74" s="14"/>
+      <c r="D74" s="14"/>
+      <c r="E74" s="14"/>
+      <c r="K74" s="14"/>
+    </row>
+    <row r="75" spans="3:11">
+      <c r="C75" s="14"/>
+      <c r="D75" s="14"/>
+      <c r="E75" s="14"/>
+    </row>
+    <row r="76" spans="3:11">
+      <c r="C76" s="14"/>
+      <c r="D76" s="14"/>
+      <c r="E76" s="14"/>
+      <c r="K76" s="14"/>
+    </row>
+    <row r="77" spans="3:11">
+      <c r="C77" s="14"/>
+      <c r="D77" s="14"/>
+      <c r="E77" s="14"/>
+      <c r="K77" s="14"/>
+    </row>
+    <row r="78" spans="3:11">
+      <c r="C78" s="14"/>
+      <c r="D78" s="14"/>
+      <c r="E78" s="14"/>
+      <c r="K78" s="14"/>
+    </row>
+    <row r="79" spans="3:11">
+      <c r="K79" s="14"/>
+    </row>
+    <row r="80" spans="3:11">
+      <c r="K80" s="14"/>
+    </row>
+    <row r="81" spans="11:11">
+      <c r="K81" s="14"/>
+    </row>
+    <row r="82" spans="11:11">
+      <c r="K82" s="14"/>
+    </row>
+    <row r="83" spans="11:11">
+      <c r="K83" s="14"/>
+    </row>
+    <row r="84" spans="11:11">
+      <c r="K84" s="14"/>
+    </row>
+    <row r="85" spans="11:11">
+      <c r="K85" s="14"/>
+    </row>
+    <row r="86" spans="11:11">
+      <c r="K86" s="14"/>
+    </row>
+    <row r="87" spans="11:11">
+      <c r="K87" s="14"/>
+    </row>
+    <row r="89" spans="11:11">
+      <c r="K89" s="14"/>
+    </row>
+    <row r="90" spans="11:11">
+      <c r="K90" s="14"/>
+    </row>
+    <row r="91" spans="11:11">
+      <c r="K91" s="14"/>
+    </row>
+    <row r="92" spans="11:11">
+      <c r="K92" s="14"/>
+    </row>
+    <row r="93" spans="11:11">
+      <c r="K93" s="14"/>
+    </row>
+    <row r="94" spans="11:11">
+      <c r="K94" s="14"/>
+    </row>
+    <row r="95" spans="11:11">
+      <c r="K95" s="14"/>
+    </row>
+    <row r="96" spans="11:11">
+      <c r="K96" s="14"/>
+    </row>
+    <row r="97" spans="11:11">
+      <c r="K97" s="14"/>
+    </row>
+    <row r="98" spans="11:11">
+      <c r="K98" s="14"/>
+    </row>
+    <row r="99" spans="11:11">
+      <c r="K99" s="14"/>
+    </row>
+    <row r="100" spans="11:11">
+      <c r="K100" s="14"/>
+    </row>
+    <row r="102" spans="11:11">
+      <c r="K102" s="14"/>
+    </row>
+    <row r="103" spans="11:11">
+      <c r="K103" s="14"/>
+    </row>
+    <row r="104" spans="11:11">
+      <c r="K104" s="14"/>
+    </row>
+    <row r="105" spans="11:11">
+      <c r="K105" s="14"/>
+    </row>
+    <row r="106" spans="11:11">
+      <c r="K106" s="14"/>
+    </row>
+    <row r="107" spans="11:11">
+      <c r="K107" s="14"/>
+    </row>
+    <row r="108" spans="11:11">
+      <c r="K108" s="14"/>
+    </row>
+    <row r="109" spans="11:11">
+      <c r="K109" s="14"/>
+    </row>
+    <row r="110" spans="11:11">
+      <c r="K110" s="14"/>
+    </row>
+    <row r="111" spans="11:11">
+      <c r="K111" s="14"/>
+    </row>
+    <row r="112" spans="11:11">
+      <c r="K112" s="14"/>
+    </row>
+    <row r="113" spans="11:11">
+      <c r="K113" s="14"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4605,18 +6740,1136 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B4614B8F-CA9A-402E-B293-C8FF103E111E}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E4958DB6-0C29-4AF4-BF5F-5783B9139A50}">
+  <dimension ref="A1:P17"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.5703125" customWidth="1"/>
+    <col min="6" max="6" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.5703125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="9.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:16" ht="15.75" thickBot="1">
+      <c r="A1" s="31" t="s">
+        <v>8</v>
+      </c>
+      <c r="B1" s="31" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1" s="31" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="31" t="s">
+        <v>72</v>
+      </c>
+      <c r="E1" s="31" t="s">
+        <v>270</v>
+      </c>
+      <c r="F1" s="31" t="s">
+        <v>3</v>
+      </c>
+      <c r="G1" s="31" t="s">
+        <v>4</v>
+      </c>
+      <c r="H1" s="31" t="s">
+        <v>5</v>
+      </c>
+      <c r="I1" s="31" t="s">
+        <v>7</v>
+      </c>
+      <c r="J1" s="31" t="s">
+        <v>13</v>
+      </c>
+      <c r="K1" s="31" t="s">
+        <v>17</v>
+      </c>
+      <c r="L1" s="31" t="s">
+        <v>18</v>
+      </c>
+      <c r="M1" s="31" t="s">
+        <v>0</v>
+      </c>
+      <c r="N1" s="31" t="s">
+        <v>19</v>
+      </c>
+      <c r="O1" s="32" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="33" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16">
+      <c r="B2" t="s">
+        <v>403</v>
+      </c>
+      <c r="C2">
+        <v>20</v>
+      </c>
+      <c r="D2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E2" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16">
+      <c r="A3" t="s">
+        <v>404</v>
+      </c>
+      <c r="B3" t="s">
+        <v>405</v>
+      </c>
+      <c r="C3">
+        <v>21</v>
+      </c>
+      <c r="D3" t="s">
+        <v>329</v>
+      </c>
+      <c r="E3" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16">
+      <c r="B4" t="s">
+        <v>407</v>
+      </c>
+      <c r="C4">
+        <v>25</v>
+      </c>
+      <c r="D4" t="s">
+        <v>130</v>
+      </c>
+      <c r="E4" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16">
+      <c r="B5" t="s">
+        <v>409</v>
+      </c>
+      <c r="C5">
+        <v>40</v>
+      </c>
+      <c r="D5" t="s">
+        <v>410</v>
+      </c>
+      <c r="E5" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16">
+      <c r="B6" t="s">
+        <v>412</v>
+      </c>
+      <c r="C6">
+        <v>50</v>
+      </c>
+      <c r="D6" t="s">
+        <v>132</v>
+      </c>
+      <c r="E6" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16">
+      <c r="B7" t="s">
+        <v>414</v>
+      </c>
+      <c r="C7">
+        <v>50</v>
+      </c>
+      <c r="D7" t="s">
+        <v>329</v>
+      </c>
+      <c r="E7" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16">
+      <c r="B8" t="s">
+        <v>415</v>
+      </c>
+      <c r="C8">
+        <v>65</v>
+      </c>
+      <c r="D8" t="s">
+        <v>131</v>
+      </c>
+      <c r="E8" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16">
+      <c r="B9" t="s">
+        <v>416</v>
+      </c>
+      <c r="C9">
+        <v>80</v>
+      </c>
+      <c r="D9" t="s">
+        <v>131</v>
+      </c>
+      <c r="E9" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16">
+      <c r="A10" t="s">
+        <v>417</v>
+      </c>
+      <c r="B10" t="s">
+        <v>418</v>
+      </c>
+      <c r="C10">
+        <v>25</v>
+      </c>
+      <c r="D10" t="s">
+        <v>419</v>
+      </c>
+      <c r="E10" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16">
+      <c r="B11" t="s">
+        <v>421</v>
+      </c>
+      <c r="C11">
+        <v>50</v>
+      </c>
+      <c r="D11" t="s">
+        <v>329</v>
+      </c>
+      <c r="E11" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16">
+      <c r="A12" t="s">
+        <v>423</v>
+      </c>
+      <c r="B12" t="s">
+        <v>424</v>
+      </c>
+      <c r="C12">
+        <v>60</v>
+      </c>
+      <c r="D12" t="s">
+        <v>130</v>
+      </c>
+      <c r="E12" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16">
+      <c r="A13" t="s">
+        <v>425</v>
+      </c>
+      <c r="B13" t="s">
+        <v>426</v>
+      </c>
+      <c r="C13">
+        <v>65</v>
+      </c>
+      <c r="D13" t="s">
+        <v>427</v>
+      </c>
+      <c r="E13" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16">
+      <c r="A14" t="s">
+        <v>428</v>
+      </c>
+      <c r="B14" t="s">
+        <v>429</v>
+      </c>
+      <c r="C14">
+        <v>90</v>
+      </c>
+      <c r="D14" t="s">
+        <v>430</v>
+      </c>
+      <c r="E14" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16">
+      <c r="A15" t="s">
+        <v>433</v>
+      </c>
+      <c r="B15" t="s">
+        <v>431</v>
+      </c>
+      <c r="C15">
+        <v>1.5</v>
+      </c>
+      <c r="D15" t="s">
+        <v>432</v>
+      </c>
+      <c r="E15" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16">
+      <c r="B16" t="s">
+        <v>434</v>
+      </c>
+      <c r="C16">
+        <v>3</v>
+      </c>
+      <c r="D16" t="s">
+        <v>432</v>
+      </c>
+      <c r="E16" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="17" spans="2:5">
+      <c r="B17" t="s">
+        <v>435</v>
+      </c>
+      <c r="C17">
+        <v>10</v>
+      </c>
+      <c r="D17" t="s">
+        <v>436</v>
+      </c>
+      <c r="E17" t="s">
+        <v>411</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B4614B8F-CA9A-402E-B293-C8FF103E111E}">
+  <dimension ref="A1:G69"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="20" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="32.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="32.42578125" customWidth="1"/>
+    <col min="4" max="4" width="50.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="54.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="108.42578125" style="25" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="61.28515625" style="25" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7">
+      <c r="A1" s="21" t="s">
+        <v>250</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E1" t="s">
+        <v>305</v>
+      </c>
+      <c r="F1" s="26" t="s">
+        <v>304</v>
+      </c>
+      <c r="G1" s="26" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
+      <c r="A2" s="28" t="s">
+        <v>247</v>
+      </c>
+      <c r="B2" s="28"/>
+      <c r="C2" s="28"/>
+      <c r="D2" s="28"/>
+      <c r="E2" s="29"/>
+      <c r="F2" s="29"/>
+      <c r="G2" s="29"/>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="B3" t="s">
+        <v>275</v>
+      </c>
+      <c r="C3" t="s">
+        <v>336</v>
+      </c>
+      <c r="D3" t="s">
+        <v>330</v>
+      </c>
+      <c r="E3" s="25" t="s">
+        <v>316</v>
+      </c>
+      <c r="F3" s="27" t="s">
+        <v>320</v>
+      </c>
+      <c r="G3" s="25" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="B4" t="s">
+        <v>259</v>
+      </c>
+      <c r="C4" t="s">
+        <v>337</v>
+      </c>
+      <c r="D4" t="s">
+        <v>331</v>
+      </c>
+      <c r="E4" s="25" t="s">
+        <v>317</v>
+      </c>
+      <c r="F4" s="25" t="s">
+        <v>309</v>
+      </c>
+      <c r="G4" s="25" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="B5" t="s">
+        <v>287</v>
+      </c>
+      <c r="C5" t="s">
+        <v>338</v>
+      </c>
+      <c r="D5" t="s">
+        <v>332</v>
+      </c>
+      <c r="E5" s="25" t="s">
+        <v>318</v>
+      </c>
+      <c r="F5" s="25" t="s">
+        <v>307</v>
+      </c>
+      <c r="G5" s="25" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="B6" t="s">
+        <v>288</v>
+      </c>
+      <c r="C6" t="s">
+        <v>338</v>
+      </c>
+      <c r="D6" t="s">
+        <v>333</v>
+      </c>
+      <c r="E6" s="25" t="s">
+        <v>319</v>
+      </c>
+      <c r="F6" s="25" t="s">
+        <v>308</v>
+      </c>
+      <c r="G6" s="25" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7" s="28" t="s">
+        <v>270</v>
+      </c>
+      <c r="B7" s="28"/>
+      <c r="C7" s="28"/>
+      <c r="D7" s="28"/>
+      <c r="E7" s="29"/>
+      <c r="F7" s="29"/>
+      <c r="G7" s="29"/>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="B8" t="s">
+        <v>271</v>
+      </c>
+      <c r="C8" t="s">
+        <v>339</v>
+      </c>
+      <c r="D8" t="s">
+        <v>334</v>
+      </c>
+      <c r="E8" s="25" t="s">
+        <v>312</v>
+      </c>
+      <c r="F8" s="25" t="s">
+        <v>314</v>
+      </c>
+      <c r="G8" s="25" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="B9" t="s">
+        <v>272</v>
+      </c>
+      <c r="C9" t="s">
+        <v>339</v>
+      </c>
+      <c r="D9" t="s">
+        <v>334</v>
+      </c>
+      <c r="E9" s="25" t="s">
+        <v>312</v>
+      </c>
+      <c r="F9" s="25" t="s">
+        <v>315</v>
+      </c>
+      <c r="G9" s="25" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="B10" t="s">
+        <v>273</v>
+      </c>
+      <c r="C10" t="s">
+        <v>341</v>
+      </c>
+      <c r="D10" t="s">
+        <v>340</v>
+      </c>
+      <c r="E10" s="25" t="s">
+        <v>306</v>
+      </c>
+      <c r="F10" s="30" t="s">
+        <v>321</v>
+      </c>
+      <c r="G10" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="B11" t="s">
+        <v>274</v>
+      </c>
+      <c r="C11" t="s">
+        <v>339</v>
+      </c>
+      <c r="D11" t="s">
+        <v>335</v>
+      </c>
+      <c r="E11" s="25" t="s">
+        <v>310</v>
+      </c>
+      <c r="F11" s="25" t="s">
+        <v>322</v>
+      </c>
+      <c r="G11" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="B12" t="s">
+        <v>402</v>
+      </c>
+      <c r="C12" t="s">
+        <v>339</v>
+      </c>
+      <c r="E12" s="25" t="s">
+        <v>350</v>
+      </c>
+      <c r="F12" s="30" t="s">
+        <v>323</v>
+      </c>
+      <c r="G12" s="25" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="B13" t="s">
+        <v>302</v>
+      </c>
+      <c r="C13" t="s">
+        <v>339</v>
+      </c>
+      <c r="D13" t="s">
+        <v>342</v>
+      </c>
+      <c r="E13" s="25" t="s">
+        <v>310</v>
+      </c>
+      <c r="F13" s="30" t="s">
+        <v>324</v>
+      </c>
+      <c r="G13" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14" s="28" t="s">
+        <v>248</v>
+      </c>
+      <c r="B14" s="28"/>
+      <c r="C14" s="28"/>
+      <c r="D14" s="28"/>
+      <c r="E14" s="29"/>
+      <c r="F14" s="29"/>
+      <c r="G14" s="29"/>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="B15" t="s">
+        <v>262</v>
+      </c>
+      <c r="C15" t="s">
+        <v>345</v>
+      </c>
+      <c r="D15" s="27" t="s">
+        <v>354</v>
+      </c>
+      <c r="E15" s="25" t="s">
+        <v>348</v>
+      </c>
+      <c r="F15" s="25" t="s">
+        <v>356</v>
+      </c>
+      <c r="G15" s="25" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="B16" t="s">
+        <v>263</v>
+      </c>
+      <c r="C16" t="s">
+        <v>345</v>
+      </c>
+      <c r="D16" s="27" t="s">
+        <v>355</v>
+      </c>
+      <c r="E16" s="25" t="s">
+        <v>348</v>
+      </c>
+      <c r="F16" s="25" t="s">
+        <v>357</v>
+      </c>
+      <c r="G16" s="25" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="B17" t="s">
+        <v>282</v>
+      </c>
+      <c r="C17" t="s">
+        <v>345</v>
+      </c>
+      <c r="D17" t="s">
+        <v>347</v>
+      </c>
+      <c r="E17" t="s">
+        <v>351</v>
+      </c>
+      <c r="F17" s="25" t="s">
+        <v>353</v>
+      </c>
+      <c r="G17" s="25" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="B18" t="s">
+        <v>293</v>
+      </c>
+      <c r="C18" t="s">
+        <v>345</v>
+      </c>
+      <c r="D18" s="27" t="s">
+        <v>352</v>
+      </c>
+      <c r="E18" s="25" t="s">
+        <v>348</v>
+      </c>
+      <c r="F18" s="25" t="s">
+        <v>373</v>
+      </c>
+      <c r="G18" s="25" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="B19" t="s">
+        <v>295</v>
+      </c>
+      <c r="C19" t="s">
+        <v>345</v>
+      </c>
+      <c r="D19" t="s">
+        <v>349</v>
+      </c>
+      <c r="E19" s="25" t="s">
+        <v>348</v>
+      </c>
+      <c r="F19" s="25" t="s">
+        <v>358</v>
+      </c>
+      <c r="G19" s="25" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20" s="28" t="s">
+        <v>280</v>
+      </c>
+      <c r="B20" s="28"/>
+      <c r="C20" s="28"/>
+      <c r="D20" s="28"/>
+      <c r="E20" s="29"/>
+      <c r="F20" s="29"/>
+      <c r="G20" s="29"/>
+    </row>
+    <row r="21" spans="1:7">
+      <c r="B21" t="s">
+        <v>264</v>
+      </c>
+      <c r="C21" t="s">
+        <v>346</v>
+      </c>
+      <c r="D21" s="27" t="s">
+        <v>360</v>
+      </c>
+      <c r="E21" s="25" t="s">
+        <v>374</v>
+      </c>
+      <c r="F21" s="25" t="s">
+        <v>364</v>
+      </c>
+      <c r="G21" s="25" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7">
+      <c r="B22" t="s">
+        <v>294</v>
+      </c>
+      <c r="C22" t="s">
+        <v>346</v>
+      </c>
+      <c r="D22" s="27" t="s">
+        <v>361</v>
+      </c>
+      <c r="E22" s="25" t="s">
+        <v>374</v>
+      </c>
+      <c r="F22" s="25" t="s">
+        <v>365</v>
+      </c>
+      <c r="G22" s="25" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7">
+      <c r="B23" t="s">
+        <v>278</v>
+      </c>
+      <c r="C23" t="s">
+        <v>346</v>
+      </c>
+      <c r="D23" s="27" t="s">
+        <v>362</v>
+      </c>
+      <c r="E23" s="25" t="s">
+        <v>375</v>
+      </c>
+      <c r="F23" s="25" t="s">
+        <v>367</v>
+      </c>
+      <c r="G23" s="25" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7">
+      <c r="B24" t="s">
+        <v>296</v>
+      </c>
+      <c r="C24" t="s">
+        <v>346</v>
+      </c>
+      <c r="D24" s="27" t="s">
+        <v>363</v>
+      </c>
+      <c r="E24" s="25" t="s">
+        <v>376</v>
+      </c>
+      <c r="F24" s="25" t="s">
+        <v>368</v>
+      </c>
+      <c r="G24" s="25" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7">
+      <c r="B25" t="s">
+        <v>283</v>
+      </c>
+      <c r="C25" t="s">
+        <v>346</v>
+      </c>
+      <c r="D25" s="27" t="s">
+        <v>371</v>
+      </c>
+      <c r="E25" t="s">
+        <v>377</v>
+      </c>
+      <c r="F25" s="25" t="s">
+        <v>369</v>
+      </c>
+      <c r="G25" s="25" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7">
+      <c r="B26" t="s">
+        <v>286</v>
+      </c>
+      <c r="C26" t="s">
+        <v>346</v>
+      </c>
+      <c r="D26" s="27" t="s">
+        <v>370</v>
+      </c>
+      <c r="E26" s="25" t="s">
+        <v>378</v>
+      </c>
+      <c r="F26" s="25" t="s">
+        <v>372</v>
+      </c>
+      <c r="G26" s="25" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7">
+      <c r="A27" s="28" t="s">
+        <v>249</v>
+      </c>
+      <c r="B27" s="28"/>
+      <c r="C27" s="28"/>
+      <c r="D27" s="28"/>
+      <c r="E27" s="29"/>
+      <c r="F27" s="29"/>
+      <c r="G27" s="29"/>
+    </row>
+    <row r="28" spans="1:7">
+      <c r="B28" t="s">
+        <v>290</v>
+      </c>
+      <c r="C28" t="s">
+        <v>399</v>
+      </c>
+      <c r="D28" s="27" t="s">
+        <v>382</v>
+      </c>
+      <c r="E28" t="s">
+        <v>380</v>
+      </c>
+      <c r="F28" s="25" t="s">
+        <v>386</v>
+      </c>
+      <c r="G28" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7">
+      <c r="B29" t="s">
+        <v>379</v>
+      </c>
+      <c r="C29" t="s">
+        <v>399</v>
+      </c>
+      <c r="D29" s="27" t="s">
+        <v>383</v>
+      </c>
+      <c r="E29" t="s">
+        <v>384</v>
+      </c>
+      <c r="F29" s="25" t="s">
+        <v>385</v>
+      </c>
+      <c r="G29" s="25" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7">
+      <c r="A30" s="28" t="s">
+        <v>258</v>
+      </c>
+      <c r="B30" s="28"/>
+      <c r="C30" s="28"/>
+      <c r="D30" s="28"/>
+      <c r="E30" s="29"/>
+      <c r="F30" s="29"/>
+      <c r="G30" s="29"/>
+    </row>
+    <row r="31" spans="1:7">
+      <c r="B31" t="s">
+        <v>392</v>
+      </c>
+      <c r="C31" t="s">
+        <v>400</v>
+      </c>
+      <c r="D31" s="27" t="s">
+        <v>387</v>
+      </c>
+      <c r="E31" t="s">
+        <v>390</v>
+      </c>
+      <c r="F31" s="25" t="s">
+        <v>397</v>
+      </c>
+      <c r="G31" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7">
+      <c r="B32" t="s">
+        <v>279</v>
+      </c>
+      <c r="C32" t="s">
+        <v>400</v>
+      </c>
+      <c r="D32" s="27" t="s">
+        <v>389</v>
+      </c>
+      <c r="E32" t="s">
+        <v>390</v>
+      </c>
+      <c r="F32" s="25" t="s">
+        <v>393</v>
+      </c>
+      <c r="G32" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7">
+      <c r="B33" t="s">
+        <v>289</v>
+      </c>
+      <c r="C33" t="s">
+        <v>401</v>
+      </c>
+      <c r="D33" s="27" t="s">
+        <v>388</v>
+      </c>
+      <c r="E33" t="s">
+        <v>391</v>
+      </c>
+      <c r="F33" s="30" t="s">
+        <v>398</v>
+      </c>
+      <c r="G33" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7">
+      <c r="A34" s="28" t="s">
+        <v>260</v>
+      </c>
+      <c r="B34" s="28"/>
+      <c r="C34" s="28"/>
+      <c r="D34" s="28"/>
+      <c r="E34" s="29"/>
+      <c r="F34" s="29"/>
+      <c r="G34" s="29"/>
+    </row>
+    <row r="35" spans="1:7">
+      <c r="B35" t="s">
+        <v>261</v>
+      </c>
+      <c r="E35" s="25"/>
+    </row>
+    <row r="36" spans="1:7">
+      <c r="B36" t="s">
+        <v>297</v>
+      </c>
+      <c r="E36" s="25"/>
+    </row>
+    <row r="37" spans="1:7">
+      <c r="B37" t="s">
+        <v>292</v>
+      </c>
+      <c r="E37" s="25"/>
+    </row>
+    <row r="38" spans="1:7">
+      <c r="A38" s="28" t="s">
+        <v>265</v>
+      </c>
+      <c r="B38" s="28"/>
+      <c r="C38" s="28"/>
+      <c r="D38" s="28"/>
+      <c r="E38" s="29"/>
+      <c r="F38" s="29"/>
+      <c r="G38" s="29"/>
+    </row>
+    <row r="39" spans="1:7">
+      <c r="B39" t="s">
+        <v>266</v>
+      </c>
+      <c r="E39" s="25"/>
+    </row>
+    <row r="40" spans="1:7">
+      <c r="B40" t="s">
+        <v>267</v>
+      </c>
+      <c r="E40" s="25"/>
+    </row>
+    <row r="41" spans="1:7">
+      <c r="B41" t="s">
+        <v>269</v>
+      </c>
+      <c r="E41" s="25"/>
+    </row>
+    <row r="42" spans="1:7">
+      <c r="B42" t="s">
+        <v>281</v>
+      </c>
+      <c r="E42" s="25"/>
+    </row>
+    <row r="43" spans="1:7">
+      <c r="B43" t="s">
+        <v>285</v>
+      </c>
+      <c r="E43" s="25"/>
+    </row>
+    <row r="44" spans="1:7">
+      <c r="B44" t="s">
+        <v>300</v>
+      </c>
+      <c r="E44" s="25"/>
+    </row>
+    <row r="45" spans="1:7">
+      <c r="B45" t="s">
+        <v>303</v>
+      </c>
+      <c r="E45" s="25"/>
+    </row>
+    <row r="46" spans="1:7">
+      <c r="B46" t="s">
+        <v>298</v>
+      </c>
+      <c r="E46" s="25"/>
+    </row>
+    <row r="47" spans="1:7">
+      <c r="B47" t="s">
+        <v>299</v>
+      </c>
+      <c r="E47" s="25"/>
+    </row>
+    <row r="48" spans="1:7">
+      <c r="E48" s="25"/>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="21" t="s">
+        <v>251</v>
+      </c>
+      <c r="E49" s="25"/>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" t="s">
+        <v>252</v>
+      </c>
+      <c r="E50" s="25"/>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" t="s">
+        <v>253</v>
+      </c>
+      <c r="E51" s="25"/>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" t="s">
+        <v>254</v>
+      </c>
+      <c r="E52" s="25"/>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" t="s">
+        <v>255</v>
+      </c>
+      <c r="E53" s="25"/>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" t="s">
+        <v>256</v>
+      </c>
+      <c r="E54" s="25"/>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="E55" s="25"/>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="E56" s="25"/>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="E57" s="25"/>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="E58" s="25"/>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="E59" s="25"/>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="E60" s="25"/>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="E61" s="25"/>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="E62" s="25"/>
+    </row>
+    <row r="63" spans="1:5">
+      <c r="A63" s="24" t="s">
+        <v>257</v>
+      </c>
+      <c r="E63" s="25"/>
+    </row>
+    <row r="64" spans="1:5">
+      <c r="A64" t="s">
+        <v>276</v>
+      </c>
+      <c r="E64" s="25"/>
+    </row>
+    <row r="65" spans="1:5">
+      <c r="A65" t="s">
+        <v>277</v>
+      </c>
+      <c r="E65" s="25"/>
+    </row>
+    <row r="66" spans="1:5">
+      <c r="A66" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5">
+      <c r="A67" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5">
+      <c r="A68" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5">
+      <c r="A69" t="s">
+        <v>301</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2A5B5038-2C90-49A5-9352-EB0CF599BD6B}">
   <dimension ref="A1:M52"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="11.85546875" bestFit="1" customWidth="1"/>
@@ -4624,470 +7877,470 @@
     <col min="11" max="11" width="46.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" ht="30">
       <c r="A1" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="B1" s="11" t="s">
+        <v>127</v>
+      </c>
+      <c r="D1" s="13" t="s">
+        <v>137</v>
+      </c>
+      <c r="E1" s="13" t="s">
+        <v>138</v>
+      </c>
+      <c r="F1" s="13" t="s">
+        <v>139</v>
+      </c>
+      <c r="G1" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="H1" s="13" t="s">
+        <v>141</v>
+      </c>
+      <c r="I1" s="13" t="s">
+        <v>142</v>
+      </c>
+      <c r="J1" s="13" t="s">
+        <v>226</v>
+      </c>
+      <c r="K1" s="13" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12">
+      <c r="A2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B2" t="s">
+        <v>128</v>
+      </c>
+      <c r="D2" s="14" t="s">
+        <v>184</v>
+      </c>
+      <c r="E2" s="14" t="s">
+        <v>185</v>
+      </c>
+      <c r="F2" s="14" t="s">
+        <v>144</v>
+      </c>
+      <c r="G2" s="14" t="s">
+        <v>186</v>
+      </c>
+      <c r="H2" s="14" t="s">
+        <v>154</v>
+      </c>
+      <c r="I2" s="14" t="s">
+        <v>187</v>
+      </c>
+      <c r="J2" s="14">
+        <v>8</v>
+      </c>
+      <c r="K2" s="14" t="s">
+        <v>188</v>
+      </c>
+      <c r="L2" s="15"/>
+    </row>
+    <row r="3" spans="1:12">
+      <c r="A3" t="s">
+        <v>63</v>
+      </c>
+      <c r="B3" t="s">
+        <v>129</v>
+      </c>
+      <c r="D3" s="14" t="s">
+        <v>189</v>
+      </c>
+      <c r="E3" s="14" t="s">
+        <v>143</v>
+      </c>
+      <c r="F3" s="14" t="s">
+        <v>148</v>
+      </c>
+      <c r="G3" s="14" t="s">
+        <v>149</v>
+      </c>
+      <c r="H3" s="14" t="s">
+        <v>145</v>
+      </c>
+      <c r="I3" s="14" t="s">
+        <v>146</v>
+      </c>
+      <c r="J3" s="14">
+        <v>10</v>
+      </c>
+      <c r="K3" s="14" t="s">
+        <v>190</v>
+      </c>
+      <c r="L3" s="15"/>
+    </row>
+    <row r="4" spans="1:12">
+      <c r="A4" t="s">
+        <v>67</v>
+      </c>
+      <c r="B4" t="s">
+        <v>65</v>
+      </c>
+      <c r="D4" s="14" t="s">
+        <v>191</v>
+      </c>
+      <c r="E4" s="14" t="s">
+        <v>147</v>
+      </c>
+      <c r="F4" s="14" t="s">
+        <v>148</v>
+      </c>
+      <c r="G4" s="14" t="s">
+        <v>150</v>
+      </c>
+      <c r="H4" s="14" t="s">
+        <v>151</v>
+      </c>
+      <c r="I4" s="14" t="s">
+        <v>152</v>
+      </c>
+      <c r="J4" s="14">
+        <v>12</v>
+      </c>
+      <c r="K4" s="14" t="s">
+        <v>192</v>
+      </c>
+      <c r="L4" s="15"/>
+    </row>
+    <row r="5" spans="1:12">
+      <c r="A5" t="s">
+        <v>65</v>
+      </c>
+      <c r="B5" t="s">
+        <v>130</v>
+      </c>
+      <c r="D5" s="14" t="s">
+        <v>193</v>
+      </c>
+      <c r="E5" s="14" t="s">
+        <v>155</v>
+      </c>
+      <c r="F5" s="14" t="s">
+        <v>153</v>
+      </c>
+      <c r="G5" s="14" t="s">
+        <v>156</v>
+      </c>
+      <c r="H5" s="14" t="s">
+        <v>157</v>
+      </c>
+      <c r="I5" s="14" t="s">
+        <v>158</v>
+      </c>
+      <c r="J5" s="14">
+        <v>12</v>
+      </c>
+      <c r="K5" s="14" t="s">
+        <v>194</v>
+      </c>
+      <c r="L5" s="15"/>
+    </row>
+    <row r="6" spans="1:12">
+      <c r="A6" t="s">
+        <v>71</v>
+      </c>
+      <c r="B6" t="s">
+        <v>131</v>
+      </c>
+      <c r="D6" s="14" t="s">
+        <v>195</v>
+      </c>
+      <c r="E6" s="14" t="s">
+        <v>160</v>
+      </c>
+      <c r="F6" s="14" t="s">
+        <v>161</v>
+      </c>
+      <c r="G6" s="14" t="s">
+        <v>162</v>
+      </c>
+      <c r="H6" s="14" t="s">
+        <v>163</v>
+      </c>
+      <c r="I6" s="14" t="s">
+        <v>159</v>
+      </c>
+      <c r="J6" s="14">
+        <v>13</v>
+      </c>
+      <c r="K6" s="14" t="s">
+        <v>196</v>
+      </c>
+      <c r="L6" s="15"/>
+    </row>
+    <row r="7" spans="1:12">
+      <c r="A7" t="s">
         <v>62</v>
       </c>
-      <c r="B1" s="11" t="s">
-        <v>128</v>
-      </c>
-      <c r="D1" s="13" t="s">
-        <v>145</v>
-      </c>
-      <c r="E1" s="13" t="s">
-        <v>146</v>
-      </c>
-      <c r="F1" s="13" t="s">
-        <v>147</v>
-      </c>
-      <c r="G1" s="13" t="s">
-        <v>148</v>
-      </c>
-      <c r="H1" s="13" t="s">
-        <v>149</v>
-      </c>
-      <c r="I1" s="13" t="s">
-        <v>150</v>
-      </c>
-      <c r="J1" s="13" t="s">
+      <c r="B7" t="s">
+        <v>67</v>
+      </c>
+      <c r="D7" s="14" t="s">
+        <v>197</v>
+      </c>
+      <c r="E7" s="14" t="s">
+        <v>164</v>
+      </c>
+      <c r="F7" s="14" t="s">
+        <v>161</v>
+      </c>
+      <c r="G7" s="14" t="s">
+        <v>175</v>
+      </c>
+      <c r="H7" s="14" t="s">
+        <v>198</v>
+      </c>
+      <c r="I7" s="14" t="s">
+        <v>165</v>
+      </c>
+      <c r="J7" s="14">
+        <v>14</v>
+      </c>
+      <c r="K7" s="14" t="s">
+        <v>201</v>
+      </c>
+      <c r="L7" s="15"/>
+    </row>
+    <row r="8" spans="1:12">
+      <c r="A8" t="s">
+        <v>64</v>
+      </c>
+      <c r="B8" t="s">
+        <v>132</v>
+      </c>
+      <c r="D8" s="14" t="s">
+        <v>200</v>
+      </c>
+      <c r="E8" s="14" t="s">
+        <v>166</v>
+      </c>
+      <c r="F8" s="14" t="s">
+        <v>167</v>
+      </c>
+      <c r="G8" s="14" t="s">
+        <v>168</v>
+      </c>
+      <c r="H8" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="I8" s="14" t="s">
+        <v>170</v>
+      </c>
+      <c r="J8" s="14">
+        <v>15</v>
+      </c>
+      <c r="K8" s="14" t="s">
+        <v>199</v>
+      </c>
+      <c r="L8" s="15"/>
+    </row>
+    <row r="9" spans="1:12">
+      <c r="A9" t="s">
+        <v>66</v>
+      </c>
+      <c r="D9" s="14" t="s">
+        <v>202</v>
+      </c>
+      <c r="E9" s="14" t="s">
+        <v>171</v>
+      </c>
+      <c r="F9" s="14" t="s">
+        <v>167</v>
+      </c>
+      <c r="G9" s="14" t="s">
+        <v>172</v>
+      </c>
+      <c r="H9" s="14" t="s">
+        <v>173</v>
+      </c>
+      <c r="I9" s="14" t="s">
+        <v>174</v>
+      </c>
+      <c r="J9" s="14">
+        <v>16</v>
+      </c>
+      <c r="K9" s="14" t="s">
+        <v>203</v>
+      </c>
+      <c r="L9" s="15"/>
+    </row>
+    <row r="10" spans="1:12">
+      <c r="A10" t="s">
+        <v>69</v>
+      </c>
+      <c r="D10" s="14" t="s">
+        <v>204</v>
+      </c>
+      <c r="E10" s="14" t="s">
+        <v>177</v>
+      </c>
+      <c r="F10" s="14" t="s">
+        <v>178</v>
+      </c>
+      <c r="G10" s="14" t="s">
+        <v>179</v>
+      </c>
+      <c r="H10" s="14" t="s">
+        <v>180</v>
+      </c>
+      <c r="I10" s="14" t="s">
+        <v>181</v>
+      </c>
+      <c r="J10" s="14">
+        <v>18</v>
+      </c>
+      <c r="K10" s="14" t="s">
+        <v>205</v>
+      </c>
+      <c r="L10" s="15"/>
+    </row>
+    <row r="11" spans="1:12">
+      <c r="A11" t="s">
+        <v>70</v>
+      </c>
+      <c r="D11" s="14" t="s">
+        <v>206</v>
+      </c>
+      <c r="E11" s="14" t="s">
+        <v>207</v>
+      </c>
+      <c r="F11" s="14" t="s">
+        <v>208</v>
+      </c>
+      <c r="G11" s="14" t="s">
+        <v>209</v>
+      </c>
+      <c r="H11" s="14" t="s">
+        <v>210</v>
+      </c>
+      <c r="I11" s="14" t="s">
+        <v>211</v>
+      </c>
+      <c r="J11" s="14">
+        <v>20</v>
+      </c>
+      <c r="K11" s="14" t="s">
+        <v>212</v>
+      </c>
+      <c r="L11" s="15"/>
+    </row>
+    <row r="12" spans="1:12">
+      <c r="D12" s="14" t="s">
+        <v>213</v>
+      </c>
+      <c r="E12" s="14" t="s">
+        <v>214</v>
+      </c>
+      <c r="F12" s="14" t="s">
+        <v>215</v>
+      </c>
+      <c r="G12" s="14" t="s">
+        <v>176</v>
+      </c>
+      <c r="H12" s="14" t="s">
+        <v>216</v>
+      </c>
+      <c r="I12" s="14" t="s">
+        <v>217</v>
+      </c>
+      <c r="J12" s="14">
+        <v>20</v>
+      </c>
+      <c r="K12" s="14" t="s">
+        <v>218</v>
+      </c>
+      <c r="L12" s="15"/>
+    </row>
+    <row r="13" spans="1:12">
+      <c r="D13" s="14" t="s">
+        <v>219</v>
+      </c>
+      <c r="E13" s="14" t="s">
+        <v>220</v>
+      </c>
+      <c r="F13" s="14" t="s">
+        <v>221</v>
+      </c>
+      <c r="G13" s="14" t="s">
+        <v>222</v>
+      </c>
+      <c r="H13" s="14" t="s">
+        <v>223</v>
+      </c>
+      <c r="I13" s="14" t="s">
+        <v>224</v>
+      </c>
+      <c r="J13" s="14">
+        <v>24</v>
+      </c>
+      <c r="K13" s="14" t="s">
+        <v>225</v>
+      </c>
+      <c r="L13" s="15"/>
+    </row>
+    <row r="15" spans="1:12">
+      <c r="A15" s="23" t="s">
+        <v>233</v>
+      </c>
+      <c r="B15" s="23"/>
+      <c r="C15" s="23"/>
+    </row>
+    <row r="16" spans="1:12">
+      <c r="A16" s="22" t="s">
         <v>234</v>
       </c>
-      <c r="K1" s="13" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>69</v>
-      </c>
-      <c r="B2" t="s">
-        <v>129</v>
-      </c>
-      <c r="D2" s="16" t="s">
-        <v>192</v>
-      </c>
-      <c r="E2" s="16" t="s">
-        <v>193</v>
-      </c>
-      <c r="F2" s="16" t="s">
-        <v>152</v>
-      </c>
-      <c r="G2" s="16" t="s">
-        <v>194</v>
-      </c>
-      <c r="H2" s="16" t="s">
-        <v>162</v>
-      </c>
-      <c r="I2" s="16" t="s">
-        <v>195</v>
-      </c>
-      <c r="J2" s="16">
-        <v>8</v>
-      </c>
-      <c r="K2" s="16" t="s">
-        <v>196</v>
-      </c>
-      <c r="L2" s="21"/>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>64</v>
-      </c>
-      <c r="B3" t="s">
-        <v>130</v>
-      </c>
-      <c r="D3" s="16" t="s">
-        <v>197</v>
-      </c>
-      <c r="E3" s="16" t="s">
-        <v>151</v>
-      </c>
-      <c r="F3" s="16" t="s">
-        <v>156</v>
-      </c>
-      <c r="G3" s="16" t="s">
-        <v>157</v>
-      </c>
-      <c r="H3" s="16" t="s">
-        <v>153</v>
-      </c>
-      <c r="I3" s="16" t="s">
-        <v>154</v>
-      </c>
-      <c r="J3" s="16">
-        <v>10</v>
-      </c>
-      <c r="K3" s="16" t="s">
-        <v>198</v>
-      </c>
-      <c r="L3" s="21"/>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>68</v>
-      </c>
-      <c r="B4" t="s">
-        <v>66</v>
-      </c>
-      <c r="D4" s="16" t="s">
-        <v>199</v>
-      </c>
-      <c r="E4" s="16" t="s">
-        <v>155</v>
-      </c>
-      <c r="F4" s="16" t="s">
-        <v>156</v>
-      </c>
-      <c r="G4" s="16" t="s">
-        <v>158</v>
-      </c>
-      <c r="H4" s="16" t="s">
-        <v>159</v>
-      </c>
-      <c r="I4" s="16" t="s">
-        <v>160</v>
-      </c>
-      <c r="J4" s="16">
-        <v>12</v>
-      </c>
-      <c r="K4" s="16" t="s">
-        <v>200</v>
-      </c>
-      <c r="L4" s="21"/>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>66</v>
-      </c>
-      <c r="B5" t="s">
-        <v>131</v>
-      </c>
-      <c r="D5" s="16" t="s">
-        <v>201</v>
-      </c>
-      <c r="E5" s="16" t="s">
-        <v>163</v>
-      </c>
-      <c r="F5" s="16" t="s">
-        <v>161</v>
-      </c>
-      <c r="G5" s="16" t="s">
-        <v>164</v>
-      </c>
-      <c r="H5" s="16" t="s">
-        <v>165</v>
-      </c>
-      <c r="I5" s="16" t="s">
-        <v>166</v>
-      </c>
-      <c r="J5" s="16">
-        <v>12</v>
-      </c>
-      <c r="K5" s="16" t="s">
-        <v>202</v>
-      </c>
-      <c r="L5" s="21"/>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>72</v>
-      </c>
-      <c r="B6" t="s">
-        <v>132</v>
-      </c>
-      <c r="D6" s="16" t="s">
-        <v>203</v>
-      </c>
-      <c r="E6" s="16" t="s">
-        <v>168</v>
-      </c>
-      <c r="F6" s="16" t="s">
-        <v>169</v>
-      </c>
-      <c r="G6" s="16" t="s">
-        <v>170</v>
-      </c>
-      <c r="H6" s="16" t="s">
-        <v>171</v>
-      </c>
-      <c r="I6" s="16" t="s">
-        <v>167</v>
-      </c>
-      <c r="J6" s="16">
-        <v>13</v>
-      </c>
-      <c r="K6" s="16" t="s">
-        <v>204</v>
-      </c>
-      <c r="L6" s="21"/>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>63</v>
-      </c>
-      <c r="B7" t="s">
-        <v>68</v>
-      </c>
-      <c r="D7" s="16" t="s">
-        <v>205</v>
-      </c>
-      <c r="E7" s="16" t="s">
-        <v>172</v>
-      </c>
-      <c r="F7" s="16" t="s">
-        <v>169</v>
-      </c>
-      <c r="G7" s="16" t="s">
-        <v>183</v>
-      </c>
-      <c r="H7" s="16" t="s">
-        <v>206</v>
-      </c>
-      <c r="I7" s="16" t="s">
-        <v>173</v>
-      </c>
-      <c r="J7" s="16">
-        <v>14</v>
-      </c>
-      <c r="K7" s="16" t="s">
-        <v>207</v>
-      </c>
-      <c r="L7" s="21"/>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>65</v>
-      </c>
-      <c r="B8" t="s">
-        <v>133</v>
-      </c>
-      <c r="D8" s="16" t="s">
-        <v>208</v>
-      </c>
-      <c r="E8" s="16" t="s">
-        <v>174</v>
-      </c>
-      <c r="F8" s="16" t="s">
-        <v>175</v>
-      </c>
-      <c r="G8" s="16" t="s">
-        <v>176</v>
-      </c>
-      <c r="H8" s="16" t="s">
-        <v>177</v>
-      </c>
-      <c r="I8" s="16" t="s">
-        <v>178</v>
-      </c>
-      <c r="J8" s="16">
-        <v>15</v>
-      </c>
-      <c r="K8" s="16" t="s">
-        <v>209</v>
-      </c>
-      <c r="L8" s="21"/>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>67</v>
-      </c>
-      <c r="D9" s="16" t="s">
-        <v>210</v>
-      </c>
-      <c r="E9" s="16" t="s">
-        <v>179</v>
-      </c>
-      <c r="F9" s="16" t="s">
-        <v>175</v>
-      </c>
-      <c r="G9" s="16" t="s">
-        <v>180</v>
-      </c>
-      <c r="H9" s="16" t="s">
-        <v>181</v>
-      </c>
-      <c r="I9" s="16" t="s">
-        <v>182</v>
-      </c>
-      <c r="J9" s="16">
-        <v>16</v>
-      </c>
-      <c r="K9" s="16" t="s">
-        <v>211</v>
-      </c>
-      <c r="L9" s="21"/>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>70</v>
-      </c>
-      <c r="D10" s="16" t="s">
-        <v>212</v>
-      </c>
-      <c r="E10" s="16" t="s">
-        <v>185</v>
-      </c>
-      <c r="F10" s="16" t="s">
-        <v>186</v>
-      </c>
-      <c r="G10" s="16" t="s">
-        <v>187</v>
-      </c>
-      <c r="H10" s="16" t="s">
-        <v>188</v>
-      </c>
-      <c r="I10" s="16" t="s">
-        <v>189</v>
-      </c>
-      <c r="J10" s="16">
-        <v>18</v>
-      </c>
-      <c r="K10" s="16" t="s">
-        <v>213</v>
-      </c>
-      <c r="L10" s="21"/>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>71</v>
-      </c>
-      <c r="D11" s="16" t="s">
-        <v>214</v>
-      </c>
-      <c r="E11" s="16" t="s">
-        <v>215</v>
-      </c>
-      <c r="F11" s="16" t="s">
-        <v>216</v>
-      </c>
-      <c r="G11" s="16" t="s">
-        <v>217</v>
-      </c>
-      <c r="H11" s="16" t="s">
-        <v>218</v>
-      </c>
-      <c r="I11" s="16" t="s">
-        <v>219</v>
-      </c>
-      <c r="J11" s="16">
-        <v>20</v>
-      </c>
-      <c r="K11" s="16" t="s">
-        <v>220</v>
-      </c>
-      <c r="L11" s="21"/>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="D12" s="16" t="s">
-        <v>221</v>
-      </c>
-      <c r="E12" s="16" t="s">
-        <v>222</v>
-      </c>
-      <c r="F12" s="16" t="s">
-        <v>223</v>
-      </c>
-      <c r="G12" s="16" t="s">
-        <v>184</v>
-      </c>
-      <c r="H12" s="16" t="s">
-        <v>224</v>
-      </c>
-      <c r="I12" s="16" t="s">
-        <v>225</v>
-      </c>
-      <c r="J12" s="16">
-        <v>20</v>
-      </c>
-      <c r="K12" s="16" t="s">
-        <v>226</v>
-      </c>
-      <c r="L12" s="21"/>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="D13" s="16" t="s">
-        <v>227</v>
-      </c>
-      <c r="E13" s="16" t="s">
-        <v>228</v>
-      </c>
-      <c r="F13" s="16" t="s">
-        <v>229</v>
-      </c>
-      <c r="G13" s="16" t="s">
-        <v>230</v>
-      </c>
-      <c r="H13" s="16" t="s">
-        <v>231</v>
-      </c>
-      <c r="I13" s="16" t="s">
-        <v>232</v>
-      </c>
-      <c r="J13" s="16">
-        <v>24</v>
-      </c>
-      <c r="K13" s="16" t="s">
-        <v>233</v>
-      </c>
-      <c r="L13" s="21"/>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A15" s="27" t="s">
+      <c r="B16" s="22" t="s">
+        <v>238</v>
+      </c>
+      <c r="C16" s="22" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11">
+      <c r="A17" t="s">
+        <v>236</v>
+      </c>
+      <c r="B17" t="s">
+        <v>239</v>
+      </c>
+      <c r="C17" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11">
+      <c r="A18" t="s">
+        <v>237</v>
+      </c>
+      <c r="B18" t="s">
+        <v>239</v>
+      </c>
+      <c r="C18" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11">
+      <c r="B19" t="s">
         <v>241</v>
       </c>
-      <c r="B15" s="27"/>
-      <c r="C15" s="27"/>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A16" s="28" t="s">
-        <v>242</v>
-      </c>
-      <c r="B16" s="28" t="s">
+      <c r="C19" t="s">
         <v>246</v>
       </c>
-      <c r="C16" s="28" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
+    </row>
+    <row r="20" spans="1:11">
+      <c r="A20" t="s">
+        <v>240</v>
+      </c>
+      <c r="B20" t="s">
+        <v>239</v>
+      </c>
+      <c r="C20" t="s">
         <v>244</v>
-      </c>
-      <c r="B17" t="s">
-        <v>247</v>
-      </c>
-      <c r="C17" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>245</v>
-      </c>
-      <c r="B18" t="s">
-        <v>247</v>
-      </c>
-      <c r="C18" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="B19" t="s">
-        <v>249</v>
-      </c>
-      <c r="C19" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>248</v>
-      </c>
-      <c r="B20" t="s">
-        <v>247</v>
-      </c>
-      <c r="C20" t="s">
-        <v>252</v>
       </c>
       <c r="D20" s="13"/>
       <c r="E20" s="13"/>
@@ -5098,136 +8351,133 @@
       <c r="J20" s="13"/>
       <c r="K20" s="13"/>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:11">
       <c r="B21" t="s">
-        <v>249</v>
+        <v>241</v>
       </c>
       <c r="C21" t="s">
-        <v>250</v>
-      </c>
-      <c r="D21" s="21"/>
-      <c r="E21" s="21"/>
-      <c r="F21" s="16"/>
-      <c r="G21" s="16"/>
-      <c r="H21" s="16"/>
-      <c r="I21" s="16"/>
-      <c r="J21" s="16"/>
-      <c r="K21" s="16"/>
-    </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>255</v>
-      </c>
-      <c r="D22" s="21"/>
-      <c r="E22" s="21"/>
-      <c r="F22" s="16"/>
-      <c r="G22" s="16"/>
-      <c r="H22" s="16"/>
-      <c r="I22" s="16"/>
-      <c r="J22" s="16"/>
-      <c r="K22" s="16"/>
-    </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="D23" s="21"/>
-      <c r="E23" s="21"/>
-      <c r="F23" s="16"/>
-      <c r="G23" s="16"/>
-      <c r="H23" s="16"/>
-      <c r="I23" s="16"/>
-      <c r="J23" s="16"/>
-      <c r="K23" s="16"/>
-    </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="D24" s="21"/>
-      <c r="E24" s="21"/>
-      <c r="F24" s="16"/>
-      <c r="G24" s="16"/>
-      <c r="H24" s="16"/>
-      <c r="I24" s="16"/>
-      <c r="J24" s="16"/>
-      <c r="K24" s="16"/>
-    </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="D25" s="21"/>
-      <c r="E25" s="21"/>
-      <c r="F25" s="16"/>
-      <c r="G25" s="16"/>
-      <c r="H25" s="16"/>
-      <c r="I25" s="16"/>
-      <c r="J25" s="16"/>
-      <c r="K25" s="16"/>
-    </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="D26" s="21"/>
-      <c r="E26" s="21"/>
-      <c r="F26" s="16"/>
-      <c r="G26" s="16"/>
-      <c r="H26" s="16"/>
-      <c r="I26" s="16"/>
-      <c r="J26" s="16"/>
-      <c r="K26" s="16"/>
-    </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="D27" s="21"/>
-      <c r="E27" s="21"/>
-      <c r="F27" s="16"/>
-      <c r="G27" s="16"/>
-      <c r="H27" s="16"/>
-      <c r="I27" s="16"/>
-      <c r="J27" s="16"/>
-      <c r="K27" s="16"/>
-    </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="D28" s="21"/>
-      <c r="E28" s="21"/>
-      <c r="F28" s="16"/>
-      <c r="G28" s="16"/>
-      <c r="H28" s="16"/>
-      <c r="I28" s="16"/>
-      <c r="J28" s="16"/>
-      <c r="K28" s="16"/>
-    </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="D29" s="21"/>
-      <c r="E29" s="21"/>
-      <c r="F29" s="16"/>
-      <c r="G29" s="16"/>
-      <c r="H29" s="16"/>
-      <c r="I29" s="16"/>
-      <c r="J29" s="16"/>
-      <c r="K29" s="16"/>
-    </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="D30" s="21"/>
-      <c r="E30" s="21"/>
-      <c r="F30" s="16"/>
-      <c r="G30" s="16"/>
-      <c r="H30" s="16"/>
-      <c r="I30" s="16"/>
-      <c r="J30" s="16"/>
-      <c r="K30" s="16"/>
-    </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="D31" s="21"/>
-      <c r="E31" s="21"/>
-      <c r="F31" s="16"/>
-      <c r="G31" s="16"/>
-      <c r="H31" s="16"/>
-      <c r="I31" s="16"/>
-      <c r="J31" s="16"/>
-      <c r="K31" s="16"/>
-    </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="D32" s="21"/>
-      <c r="E32" s="21"/>
-      <c r="F32" s="16"/>
-      <c r="G32" s="16"/>
-      <c r="H32" s="16"/>
-      <c r="I32" s="16"/>
-      <c r="J32" s="16"/>
-      <c r="K32" s="16"/>
-    </row>
-    <row r="40" spans="6:13" x14ac:dyDescent="0.25">
+        <v>242</v>
+      </c>
+      <c r="D21" s="15"/>
+      <c r="E21" s="15"/>
+      <c r="F21" s="14"/>
+      <c r="G21" s="14"/>
+      <c r="H21" s="14"/>
+      <c r="I21" s="14"/>
+      <c r="J21" s="14"/>
+      <c r="K21" s="14"/>
+    </row>
+    <row r="22" spans="1:11">
+      <c r="D22" s="15"/>
+      <c r="E22" s="15"/>
+      <c r="F22" s="14"/>
+      <c r="G22" s="14"/>
+      <c r="H22" s="14"/>
+      <c r="I22" s="14"/>
+      <c r="J22" s="14"/>
+      <c r="K22" s="14"/>
+    </row>
+    <row r="23" spans="1:11">
+      <c r="D23" s="15"/>
+      <c r="E23" s="15"/>
+      <c r="F23" s="14"/>
+      <c r="G23" s="14"/>
+      <c r="H23" s="14"/>
+      <c r="I23" s="14"/>
+      <c r="J23" s="14"/>
+      <c r="K23" s="14"/>
+    </row>
+    <row r="24" spans="1:11">
+      <c r="D24" s="15"/>
+      <c r="E24" s="15"/>
+      <c r="F24" s="14"/>
+      <c r="G24" s="14"/>
+      <c r="H24" s="14"/>
+      <c r="I24" s="14"/>
+      <c r="J24" s="14"/>
+      <c r="K24" s="14"/>
+    </row>
+    <row r="25" spans="1:11">
+      <c r="D25" s="15"/>
+      <c r="E25" s="15"/>
+      <c r="F25" s="14"/>
+      <c r="G25" s="14"/>
+      <c r="H25" s="14"/>
+      <c r="I25" s="14"/>
+      <c r="J25" s="14"/>
+      <c r="K25" s="14"/>
+    </row>
+    <row r="26" spans="1:11">
+      <c r="D26" s="15"/>
+      <c r="E26" s="15"/>
+      <c r="F26" s="14"/>
+      <c r="G26" s="14"/>
+      <c r="H26" s="14"/>
+      <c r="I26" s="14"/>
+      <c r="J26" s="14"/>
+      <c r="K26" s="14"/>
+    </row>
+    <row r="27" spans="1:11">
+      <c r="D27" s="15"/>
+      <c r="E27" s="15"/>
+      <c r="F27" s="14"/>
+      <c r="G27" s="14"/>
+      <c r="H27" s="14"/>
+      <c r="I27" s="14"/>
+      <c r="J27" s="14"/>
+      <c r="K27" s="14"/>
+    </row>
+    <row r="28" spans="1:11">
+      <c r="D28" s="15"/>
+      <c r="E28" s="15"/>
+      <c r="F28" s="14"/>
+      <c r="G28" s="14"/>
+      <c r="H28" s="14"/>
+      <c r="I28" s="14"/>
+      <c r="J28" s="14"/>
+      <c r="K28" s="14"/>
+    </row>
+    <row r="29" spans="1:11">
+      <c r="D29" s="15"/>
+      <c r="E29" s="15"/>
+      <c r="F29" s="14"/>
+      <c r="G29" s="14"/>
+      <c r="H29" s="14"/>
+      <c r="I29" s="14"/>
+      <c r="J29" s="14"/>
+      <c r="K29" s="14"/>
+    </row>
+    <row r="30" spans="1:11">
+      <c r="D30" s="15"/>
+      <c r="E30" s="15"/>
+      <c r="F30" s="14"/>
+      <c r="G30" s="14"/>
+      <c r="H30" s="14"/>
+      <c r="I30" s="14"/>
+      <c r="J30" s="14"/>
+      <c r="K30" s="14"/>
+    </row>
+    <row r="31" spans="1:11">
+      <c r="D31" s="15"/>
+      <c r="E31" s="15"/>
+      <c r="F31" s="14"/>
+      <c r="G31" s="14"/>
+      <c r="H31" s="14"/>
+      <c r="I31" s="14"/>
+      <c r="J31" s="14"/>
+      <c r="K31" s="14"/>
+    </row>
+    <row r="32" spans="1:11">
+      <c r="D32" s="15"/>
+      <c r="E32" s="15"/>
+      <c r="F32" s="14"/>
+      <c r="G32" s="14"/>
+      <c r="H32" s="14"/>
+      <c r="I32" s="14"/>
+      <c r="J32" s="14"/>
+      <c r="K32" s="14"/>
+    </row>
+    <row r="40" spans="6:13">
       <c r="F40" s="13"/>
       <c r="G40" s="13"/>
       <c r="H40" s="13"/>
@@ -5237,125 +8487,125 @@
       <c r="L40" s="13"/>
       <c r="M40" s="13"/>
     </row>
-    <row r="41" spans="6:13" x14ac:dyDescent="0.25">
-      <c r="F41" s="21"/>
-      <c r="G41" s="21"/>
-      <c r="H41" s="16"/>
-      <c r="I41" s="16"/>
-      <c r="J41" s="16"/>
-      <c r="K41" s="16"/>
-      <c r="L41" s="16"/>
-      <c r="M41" s="16"/>
-    </row>
-    <row r="42" spans="6:13" x14ac:dyDescent="0.25">
-      <c r="F42" s="21"/>
-      <c r="G42" s="21"/>
-      <c r="H42" s="16"/>
-      <c r="I42" s="16"/>
-      <c r="J42" s="16"/>
-      <c r="K42" s="16"/>
-      <c r="L42" s="16"/>
-      <c r="M42" s="16"/>
-    </row>
-    <row r="43" spans="6:13" x14ac:dyDescent="0.25">
-      <c r="F43" s="21"/>
-      <c r="G43" s="21"/>
-      <c r="H43" s="16"/>
-      <c r="I43" s="16"/>
-      <c r="J43" s="16"/>
-      <c r="K43" s="16"/>
-      <c r="L43" s="16"/>
-      <c r="M43" s="16"/>
-    </row>
-    <row r="44" spans="6:13" x14ac:dyDescent="0.25">
-      <c r="F44" s="21"/>
-      <c r="G44" s="21"/>
-      <c r="H44" s="16"/>
-      <c r="I44" s="16"/>
-      <c r="J44" s="16"/>
-      <c r="K44" s="16"/>
-      <c r="L44" s="16"/>
-      <c r="M44" s="16"/>
-    </row>
-    <row r="45" spans="6:13" x14ac:dyDescent="0.25">
-      <c r="F45" s="21"/>
-      <c r="G45" s="21"/>
-      <c r="H45" s="16"/>
-      <c r="I45" s="16"/>
-      <c r="J45" s="16"/>
-      <c r="K45" s="16"/>
-      <c r="L45" s="16"/>
-      <c r="M45" s="16"/>
-    </row>
-    <row r="46" spans="6:13" x14ac:dyDescent="0.25">
-      <c r="F46" s="21"/>
-      <c r="G46" s="21"/>
-      <c r="H46" s="16"/>
-      <c r="I46" s="16"/>
-      <c r="J46" s="16"/>
-      <c r="K46" s="16"/>
-      <c r="L46" s="16"/>
-      <c r="M46" s="16"/>
-    </row>
-    <row r="47" spans="6:13" x14ac:dyDescent="0.25">
-      <c r="F47" s="21"/>
-      <c r="G47" s="21"/>
-      <c r="H47" s="16"/>
-      <c r="I47" s="16"/>
-      <c r="J47" s="16"/>
-      <c r="K47" s="16"/>
-      <c r="L47" s="16"/>
-      <c r="M47" s="16"/>
-    </row>
-    <row r="48" spans="6:13" x14ac:dyDescent="0.25">
-      <c r="F48" s="21"/>
-      <c r="G48" s="21"/>
-      <c r="H48" s="16"/>
-      <c r="I48" s="16"/>
-      <c r="J48" s="16"/>
-      <c r="K48" s="16"/>
-      <c r="L48" s="16"/>
-      <c r="M48" s="16"/>
-    </row>
-    <row r="49" spans="6:13" x14ac:dyDescent="0.25">
-      <c r="F49" s="21"/>
-      <c r="G49" s="21"/>
-      <c r="H49" s="16"/>
-      <c r="I49" s="16"/>
-      <c r="J49" s="16"/>
-      <c r="K49" s="16"/>
-      <c r="L49" s="16"/>
-      <c r="M49" s="16"/>
-    </row>
-    <row r="50" spans="6:13" x14ac:dyDescent="0.25">
-      <c r="F50" s="21"/>
-      <c r="G50" s="21"/>
-      <c r="H50" s="16"/>
-      <c r="I50" s="16"/>
-      <c r="J50" s="16"/>
-      <c r="K50" s="16"/>
-      <c r="L50" s="16"/>
-      <c r="M50" s="16"/>
-    </row>
-    <row r="51" spans="6:13" x14ac:dyDescent="0.25">
-      <c r="F51" s="21"/>
-      <c r="G51" s="21"/>
-      <c r="H51" s="16"/>
-      <c r="I51" s="16"/>
-      <c r="J51" s="16"/>
-      <c r="K51" s="16"/>
-      <c r="L51" s="16"/>
-      <c r="M51" s="16"/>
-    </row>
-    <row r="52" spans="6:13" x14ac:dyDescent="0.25">
-      <c r="F52" s="21"/>
-      <c r="G52" s="21"/>
-      <c r="H52" s="16"/>
-      <c r="I52" s="16"/>
-      <c r="J52" s="16"/>
-      <c r="K52" s="16"/>
-      <c r="L52" s="16"/>
-      <c r="M52" s="16"/>
+    <row r="41" spans="6:13">
+      <c r="F41" s="15"/>
+      <c r="G41" s="15"/>
+      <c r="H41" s="14"/>
+      <c r="I41" s="14"/>
+      <c r="J41" s="14"/>
+      <c r="K41" s="14"/>
+      <c r="L41" s="14"/>
+      <c r="M41" s="14"/>
+    </row>
+    <row r="42" spans="6:13">
+      <c r="F42" s="15"/>
+      <c r="G42" s="15"/>
+      <c r="H42" s="14"/>
+      <c r="I42" s="14"/>
+      <c r="J42" s="14"/>
+      <c r="K42" s="14"/>
+      <c r="L42" s="14"/>
+      <c r="M42" s="14"/>
+    </row>
+    <row r="43" spans="6:13">
+      <c r="F43" s="15"/>
+      <c r="G43" s="15"/>
+      <c r="H43" s="14"/>
+      <c r="I43" s="14"/>
+      <c r="J43" s="14"/>
+      <c r="K43" s="14"/>
+      <c r="L43" s="14"/>
+      <c r="M43" s="14"/>
+    </row>
+    <row r="44" spans="6:13">
+      <c r="F44" s="15"/>
+      <c r="G44" s="15"/>
+      <c r="H44" s="14"/>
+      <c r="I44" s="14"/>
+      <c r="J44" s="14"/>
+      <c r="K44" s="14"/>
+      <c r="L44" s="14"/>
+      <c r="M44" s="14"/>
+    </row>
+    <row r="45" spans="6:13">
+      <c r="F45" s="15"/>
+      <c r="G45" s="15"/>
+      <c r="H45" s="14"/>
+      <c r="I45" s="14"/>
+      <c r="J45" s="14"/>
+      <c r="K45" s="14"/>
+      <c r="L45" s="14"/>
+      <c r="M45" s="14"/>
+    </row>
+    <row r="46" spans="6:13">
+      <c r="F46" s="15"/>
+      <c r="G46" s="15"/>
+      <c r="H46" s="14"/>
+      <c r="I46" s="14"/>
+      <c r="J46" s="14"/>
+      <c r="K46" s="14"/>
+      <c r="L46" s="14"/>
+      <c r="M46" s="14"/>
+    </row>
+    <row r="47" spans="6:13">
+      <c r="F47" s="15"/>
+      <c r="G47" s="15"/>
+      <c r="H47" s="14"/>
+      <c r="I47" s="14"/>
+      <c r="J47" s="14"/>
+      <c r="K47" s="14"/>
+      <c r="L47" s="14"/>
+      <c r="M47" s="14"/>
+    </row>
+    <row r="48" spans="6:13">
+      <c r="F48" s="15"/>
+      <c r="G48" s="15"/>
+      <c r="H48" s="14"/>
+      <c r="I48" s="14"/>
+      <c r="J48" s="14"/>
+      <c r="K48" s="14"/>
+      <c r="L48" s="14"/>
+      <c r="M48" s="14"/>
+    </row>
+    <row r="49" spans="6:13">
+      <c r="F49" s="15"/>
+      <c r="G49" s="15"/>
+      <c r="H49" s="14"/>
+      <c r="I49" s="14"/>
+      <c r="J49" s="14"/>
+      <c r="K49" s="14"/>
+      <c r="L49" s="14"/>
+      <c r="M49" s="14"/>
+    </row>
+    <row r="50" spans="6:13">
+      <c r="F50" s="15"/>
+      <c r="G50" s="15"/>
+      <c r="H50" s="14"/>
+      <c r="I50" s="14"/>
+      <c r="J50" s="14"/>
+      <c r="K50" s="14"/>
+      <c r="L50" s="14"/>
+      <c r="M50" s="14"/>
+    </row>
+    <row r="51" spans="6:13">
+      <c r="F51" s="15"/>
+      <c r="G51" s="15"/>
+      <c r="H51" s="14"/>
+      <c r="I51" s="14"/>
+      <c r="J51" s="14"/>
+      <c r="K51" s="14"/>
+      <c r="L51" s="14"/>
+      <c r="M51" s="14"/>
+    </row>
+    <row r="52" spans="6:13">
+      <c r="F52" s="15"/>
+      <c r="G52" s="15"/>
+      <c r="H52" s="14"/>
+      <c r="I52" s="14"/>
+      <c r="J52" s="14"/>
+      <c r="K52" s="14"/>
+      <c r="L52" s="14"/>
+      <c r="M52" s="14"/>
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:A11">
@@ -5366,2084 +8616,4 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{638C2691-F153-42DD-AE26-EE64F03BC3A1}">
-  <dimension ref="A1:Q81"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="13" customWidth="1"/>
-    <col min="10" max="10" width="11.5703125" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A1" s="13" t="s">
-        <v>134</v>
-      </c>
-      <c r="B1" s="15" t="s">
-        <v>135</v>
-      </c>
-      <c r="C1" s="15" t="s">
-        <v>136</v>
-      </c>
-      <c r="D1" s="15" t="s">
-        <v>137</v>
-      </c>
-      <c r="E1" s="15" t="s">
-        <v>138</v>
-      </c>
-      <c r="F1" s="15" t="s">
-        <v>4</v>
-      </c>
-      <c r="G1" s="15" t="s">
-        <v>139</v>
-      </c>
-      <c r="H1" s="15" t="s">
-        <v>140</v>
-      </c>
-      <c r="O1" s="13"/>
-      <c r="P1" s="13"/>
-      <c r="Q1" s="13"/>
-    </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A2" s="16" t="s">
-        <v>11</v>
-      </c>
-      <c r="B2" s="14">
-        <v>6</v>
-      </c>
-      <c r="C2" s="14">
-        <v>2</v>
-      </c>
-      <c r="D2" s="14">
-        <v>2</v>
-      </c>
-      <c r="E2" s="14">
-        <v>3</v>
-      </c>
-      <c r="F2" s="14">
-        <v>14</v>
-      </c>
-      <c r="G2" s="14">
-        <v>6</v>
-      </c>
-      <c r="H2" s="14">
-        <v>1</v>
-      </c>
-      <c r="I2">
-        <v>20</v>
-      </c>
-      <c r="J2" s="20">
-        <f>K14*L2</f>
-        <v>8.5116279069767433</v>
-      </c>
-      <c r="K2">
-        <f>(I2/5)*2-1</f>
-        <v>7</v>
-      </c>
-      <c r="L2" s="19">
-        <f t="shared" ref="L2:L12" si="0">G2/$G$14</f>
-        <v>0.83720930232558133</v>
-      </c>
-      <c r="O2" s="16"/>
-      <c r="P2" s="16"/>
-      <c r="Q2" s="16"/>
-    </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A3" s="16" t="s">
-        <v>21</v>
-      </c>
-      <c r="B3" s="14">
-        <v>5</v>
-      </c>
-      <c r="C3" s="14">
-        <v>3</v>
-      </c>
-      <c r="D3" s="14">
-        <v>2</v>
-      </c>
-      <c r="E3" s="14">
-        <v>3</v>
-      </c>
-      <c r="F3" s="14">
-        <v>14</v>
-      </c>
-      <c r="G3" s="14">
-        <v>6</v>
-      </c>
-      <c r="H3" s="14">
-        <v>2</v>
-      </c>
-      <c r="I3">
-        <v>20</v>
-      </c>
-      <c r="J3" s="20">
-        <f t="shared" ref="J2:J12" si="1">K3*L3</f>
-        <v>5.8604651162790695</v>
-      </c>
-      <c r="K3">
-        <f t="shared" ref="K3:K55" si="2">(I3/5)*2-1</f>
-        <v>7</v>
-      </c>
-      <c r="L3" s="19">
-        <f t="shared" si="0"/>
-        <v>0.83720930232558133</v>
-      </c>
-      <c r="O3" s="16"/>
-      <c r="P3" s="16"/>
-      <c r="Q3" s="16"/>
-    </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A4" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="B4" s="14">
-        <v>5</v>
-      </c>
-      <c r="C4" s="14">
-        <v>3</v>
-      </c>
-      <c r="D4" s="14">
-        <v>2</v>
-      </c>
-      <c r="E4" s="14">
-        <v>3</v>
-      </c>
-      <c r="F4" s="14">
-        <v>14</v>
-      </c>
-      <c r="G4" s="14">
-        <v>6</v>
-      </c>
-      <c r="H4" s="14">
-        <v>2</v>
-      </c>
-      <c r="I4">
-        <v>20</v>
-      </c>
-      <c r="J4" s="20">
-        <f t="shared" si="1"/>
-        <v>5.8604651162790695</v>
-      </c>
-      <c r="K4">
-        <f t="shared" si="2"/>
-        <v>7</v>
-      </c>
-      <c r="L4" s="19">
-        <f t="shared" si="0"/>
-        <v>0.83720930232558133</v>
-      </c>
-      <c r="O4" s="16"/>
-      <c r="P4" s="16"/>
-      <c r="Q4" s="16"/>
-    </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A5" s="16" t="s">
-        <v>24</v>
-      </c>
-      <c r="B5" s="14">
-        <v>5</v>
-      </c>
-      <c r="C5" s="14">
-        <v>2</v>
-      </c>
-      <c r="D5" s="14">
-        <v>3</v>
-      </c>
-      <c r="E5" s="14">
-        <v>3</v>
-      </c>
-      <c r="F5" s="14">
-        <v>16</v>
-      </c>
-      <c r="G5" s="14">
-        <v>7</v>
-      </c>
-      <c r="H5" s="14">
-        <v>2</v>
-      </c>
-      <c r="I5">
-        <v>25</v>
-      </c>
-      <c r="J5" s="20">
-        <f t="shared" si="1"/>
-        <v>8.7906976744186043</v>
-      </c>
-      <c r="K5">
-        <f t="shared" si="2"/>
-        <v>9</v>
-      </c>
-      <c r="L5" s="19">
-        <f t="shared" si="0"/>
-        <v>0.97674418604651159</v>
-      </c>
-      <c r="O5" s="16"/>
-      <c r="P5" s="16"/>
-      <c r="Q5" s="16"/>
-    </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A6" s="16" t="s">
-        <v>51</v>
-      </c>
-      <c r="B6" s="14">
-        <v>6</v>
-      </c>
-      <c r="C6" s="14">
-        <v>4</v>
-      </c>
-      <c r="D6" s="14">
-        <v>3</v>
-      </c>
-      <c r="E6" s="14">
-        <v>3</v>
-      </c>
-      <c r="F6" s="14">
-        <v>15</v>
-      </c>
-      <c r="G6" s="14">
-        <v>7</v>
-      </c>
-      <c r="H6" s="14">
-        <v>2</v>
-      </c>
-      <c r="I6">
-        <v>25</v>
-      </c>
-      <c r="J6" s="20">
-        <f t="shared" si="1"/>
-        <v>8.7906976744186043</v>
-      </c>
-      <c r="K6">
-        <f t="shared" si="2"/>
-        <v>9</v>
-      </c>
-      <c r="L6" s="19">
-        <f t="shared" si="0"/>
-        <v>0.97674418604651159</v>
-      </c>
-      <c r="O6" s="16"/>
-      <c r="P6" s="16"/>
-      <c r="Q6" s="16"/>
-    </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A7" s="16" t="s">
-        <v>26</v>
-      </c>
-      <c r="B7" s="14">
-        <v>4</v>
-      </c>
-      <c r="C7" s="14">
-        <v>3</v>
-      </c>
-      <c r="D7" s="14">
-        <v>3</v>
-      </c>
-      <c r="E7" s="14">
-        <v>3</v>
-      </c>
-      <c r="F7" s="14">
-        <v>18</v>
-      </c>
-      <c r="G7" s="14">
-        <v>8</v>
-      </c>
-      <c r="H7" s="14">
-        <v>2</v>
-      </c>
-      <c r="I7">
-        <v>30</v>
-      </c>
-      <c r="J7" s="20">
-        <f t="shared" si="1"/>
-        <v>12.279069767441861</v>
-      </c>
-      <c r="K7">
-        <f t="shared" si="2"/>
-        <v>11</v>
-      </c>
-      <c r="L7" s="19">
-        <f t="shared" si="0"/>
-        <v>1.1162790697674418</v>
-      </c>
-      <c r="O7" s="16"/>
-      <c r="P7" s="16"/>
-      <c r="Q7" s="16"/>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A8" s="16" t="s">
-        <v>39</v>
-      </c>
-      <c r="B8" s="14">
-        <v>6</v>
-      </c>
-      <c r="C8" s="14">
-        <v>2</v>
-      </c>
-      <c r="D8" s="14">
-        <v>2</v>
-      </c>
-      <c r="E8" s="14">
-        <v>3</v>
-      </c>
-      <c r="F8" s="14">
-        <v>15</v>
-      </c>
-      <c r="G8" s="14">
-        <v>6</v>
-      </c>
-      <c r="H8" s="14">
-        <v>2</v>
-      </c>
-      <c r="I8">
-        <v>30</v>
-      </c>
-      <c r="J8" s="20">
-        <f t="shared" si="1"/>
-        <v>9.2093023255813939</v>
-      </c>
-      <c r="K8">
-        <f t="shared" si="2"/>
-        <v>11</v>
-      </c>
-      <c r="L8" s="19">
-        <f t="shared" si="0"/>
-        <v>0.83720930232558133</v>
-      </c>
-      <c r="O8" s="16"/>
-      <c r="P8" s="16"/>
-      <c r="Q8" s="16"/>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A9" s="16" t="s">
-        <v>40</v>
-      </c>
-      <c r="B9" s="14">
-        <v>5</v>
-      </c>
-      <c r="C9" s="14">
-        <v>2</v>
-      </c>
-      <c r="D9" s="14">
-        <v>2</v>
-      </c>
-      <c r="E9" s="14">
-        <v>3</v>
-      </c>
-      <c r="F9" s="14">
-        <v>16</v>
-      </c>
-      <c r="G9" s="14">
-        <v>6</v>
-      </c>
-      <c r="H9" s="14">
-        <v>2</v>
-      </c>
-      <c r="I9">
-        <v>30</v>
-      </c>
-      <c r="J9" s="20">
-        <f t="shared" si="1"/>
-        <v>9.2093023255813939</v>
-      </c>
-      <c r="K9">
-        <f t="shared" si="2"/>
-        <v>11</v>
-      </c>
-      <c r="L9" s="19">
-        <f t="shared" si="0"/>
-        <v>0.83720930232558133</v>
-      </c>
-      <c r="O9" s="16"/>
-      <c r="P9" s="16"/>
-      <c r="Q9" s="16"/>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A10" s="16" t="s">
-        <v>41</v>
-      </c>
-      <c r="B10" s="14">
-        <v>6</v>
-      </c>
-      <c r="C10" s="14">
-        <v>3</v>
-      </c>
-      <c r="D10" s="14">
-        <v>3</v>
-      </c>
-      <c r="E10" s="14">
-        <v>3</v>
-      </c>
-      <c r="F10" s="14">
-        <v>14</v>
-      </c>
-      <c r="G10" s="14">
-        <v>7</v>
-      </c>
-      <c r="H10" s="14">
-        <v>2</v>
-      </c>
-      <c r="I10">
-        <v>30</v>
-      </c>
-      <c r="J10" s="20">
-        <f t="shared" si="1"/>
-        <v>10.744186046511627</v>
-      </c>
-      <c r="K10">
-        <f t="shared" si="2"/>
-        <v>11</v>
-      </c>
-      <c r="L10" s="19">
-        <f t="shared" si="0"/>
-        <v>0.97674418604651159</v>
-      </c>
-      <c r="O10" s="16"/>
-      <c r="P10" s="16"/>
-      <c r="Q10" s="16"/>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A11" s="16" t="s">
-        <v>42</v>
-      </c>
-      <c r="B11" s="14">
-        <v>3</v>
-      </c>
-      <c r="C11" s="14">
-        <v>4</v>
-      </c>
-      <c r="D11" s="14">
-        <v>4</v>
-      </c>
-      <c r="E11" s="14">
-        <v>3</v>
-      </c>
-      <c r="F11" s="14">
-        <v>20</v>
-      </c>
-      <c r="G11" s="14">
-        <v>9</v>
-      </c>
-      <c r="H11" s="14">
-        <v>3</v>
-      </c>
-      <c r="I11">
-        <v>35</v>
-      </c>
-      <c r="J11" s="20">
-        <f t="shared" si="1"/>
-        <v>16.325581395348838</v>
-      </c>
-      <c r="K11">
-        <f t="shared" si="2"/>
-        <v>13</v>
-      </c>
-      <c r="L11" s="19">
-        <f t="shared" si="0"/>
-        <v>1.2558139534883721</v>
-      </c>
-      <c r="O11" s="16"/>
-      <c r="P11" s="16"/>
-      <c r="Q11" s="16"/>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A12" s="16" t="s">
-        <v>43</v>
-      </c>
-      <c r="B12" s="14">
-        <v>4</v>
-      </c>
-      <c r="C12" s="14">
-        <v>6</v>
-      </c>
-      <c r="D12" s="14">
-        <v>3</v>
-      </c>
-      <c r="E12" s="14">
-        <v>3</v>
-      </c>
-      <c r="F12" s="14">
-        <v>18</v>
-      </c>
-      <c r="G12" s="14">
-        <v>8</v>
-      </c>
-      <c r="H12" s="14">
-        <v>2</v>
-      </c>
-      <c r="I12">
-        <v>35</v>
-      </c>
-      <c r="J12" s="20">
-        <f t="shared" si="1"/>
-        <v>14.511627906976743</v>
-      </c>
-      <c r="K12">
-        <f t="shared" si="2"/>
-        <v>13</v>
-      </c>
-      <c r="L12" s="19">
-        <f t="shared" si="0"/>
-        <v>1.1162790697674418</v>
-      </c>
-      <c r="O12" s="16"/>
-      <c r="P12" s="16"/>
-      <c r="Q12" s="16"/>
-    </row>
-    <row r="13" spans="1:17" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="16" t="s">
-        <v>44</v>
-      </c>
-      <c r="B13" s="14">
-        <v>4</v>
-      </c>
-      <c r="C13" s="14">
-        <v>4</v>
-      </c>
-      <c r="D13" s="14">
-        <v>5</v>
-      </c>
-      <c r="E13" s="14">
-        <v>3</v>
-      </c>
-      <c r="F13" s="14">
-        <v>22</v>
-      </c>
-      <c r="G13" s="14">
-        <v>10</v>
-      </c>
-      <c r="H13" s="14">
-        <v>3</v>
-      </c>
-      <c r="I13">
-        <v>35</v>
-      </c>
-      <c r="J13" s="20">
-        <f>K13*L13</f>
-        <v>18.13953488372093</v>
-      </c>
-      <c r="K13">
-        <f t="shared" si="2"/>
-        <v>13</v>
-      </c>
-      <c r="L13" s="19">
-        <f>G13/$G$14</f>
-        <v>1.3953488372093024</v>
-      </c>
-      <c r="O13" s="16"/>
-      <c r="P13" s="16"/>
-      <c r="Q13" s="16"/>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="G14" s="17">
-        <f>AVERAGE(G2:G13)</f>
-        <v>7.166666666666667</v>
-      </c>
-      <c r="J14" s="20">
-        <f t="shared" ref="J14:J27" si="3">K14*L14</f>
-        <v>0</v>
-      </c>
-      <c r="K14">
-        <f>AVERAGE(K2:K13)</f>
-        <v>10.166666666666666</v>
-      </c>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A15" s="13" t="s">
-        <v>134</v>
-      </c>
-      <c r="B15" s="15" t="s">
-        <v>135</v>
-      </c>
-      <c r="C15" s="15" t="s">
-        <v>136</v>
-      </c>
-      <c r="D15" s="15" t="s">
-        <v>137</v>
-      </c>
-      <c r="E15" s="15" t="s">
-        <v>138</v>
-      </c>
-      <c r="F15" s="15" t="s">
-        <v>4</v>
-      </c>
-      <c r="G15" s="15" t="s">
-        <v>139</v>
-      </c>
-      <c r="H15" s="15" t="s">
-        <v>140</v>
-      </c>
-      <c r="J15" s="20">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A16" s="16" t="s">
-        <v>53</v>
-      </c>
-      <c r="B16" s="14">
-        <v>6</v>
-      </c>
-      <c r="C16" s="14">
-        <v>2</v>
-      </c>
-      <c r="D16" s="14">
-        <v>2</v>
-      </c>
-      <c r="E16" s="14">
-        <v>4</v>
-      </c>
-      <c r="F16" s="14">
-        <v>18</v>
-      </c>
-      <c r="G16" s="14">
-        <v>8</v>
-      </c>
-      <c r="H16" s="14">
-        <v>2</v>
-      </c>
-      <c r="I16">
-        <v>40</v>
-      </c>
-      <c r="J16" s="20">
-        <f>K28*L16</f>
-        <v>12.753623188405795</v>
-      </c>
-      <c r="K16">
-        <f t="shared" si="2"/>
-        <v>15</v>
-      </c>
-      <c r="L16" s="18">
-        <f>G16/$G$28</f>
-        <v>0.69565217391304346</v>
-      </c>
-    </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A17" s="16" t="s">
-        <v>55</v>
-      </c>
-      <c r="B17" s="14">
-        <v>5</v>
-      </c>
-      <c r="C17" s="14">
-        <v>2</v>
-      </c>
-      <c r="D17" s="14">
-        <v>3</v>
-      </c>
-      <c r="E17" s="14">
-        <v>4</v>
-      </c>
-      <c r="F17" s="14">
-        <v>20</v>
-      </c>
-      <c r="G17" s="14">
-        <v>9</v>
-      </c>
-      <c r="H17" s="14">
-        <v>2</v>
-      </c>
-      <c r="I17">
-        <v>40</v>
-      </c>
-      <c r="J17" s="20">
-        <f t="shared" si="3"/>
-        <v>11.739130434782609</v>
-      </c>
-      <c r="K17">
-        <f t="shared" si="2"/>
-        <v>15</v>
-      </c>
-      <c r="L17" s="18">
-        <f t="shared" ref="L17:L27" si="4">G17/$G$28</f>
-        <v>0.78260869565217395</v>
-      </c>
-    </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A18" s="16" t="s">
-        <v>56</v>
-      </c>
-      <c r="B18" s="14">
-        <v>3</v>
-      </c>
-      <c r="C18" s="14">
-        <v>4</v>
-      </c>
-      <c r="D18" s="14">
-        <v>3</v>
-      </c>
-      <c r="E18" s="14">
-        <v>4</v>
-      </c>
-      <c r="F18" s="14">
-        <v>24</v>
-      </c>
-      <c r="G18" s="14">
-        <v>11</v>
-      </c>
-      <c r="H18" s="14">
-        <v>2</v>
-      </c>
-      <c r="I18">
-        <v>45</v>
-      </c>
-      <c r="J18" s="20">
-        <f t="shared" si="3"/>
-        <v>16.260869565217391</v>
-      </c>
-      <c r="K18">
-        <f t="shared" si="2"/>
-        <v>17</v>
-      </c>
-      <c r="L18" s="18">
-        <f t="shared" si="4"/>
-        <v>0.95652173913043481</v>
-      </c>
-    </row>
-    <row r="19" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="16" t="s">
-        <v>28</v>
-      </c>
-      <c r="B19" s="14">
-        <v>6</v>
-      </c>
-      <c r="C19" s="14">
-        <v>4</v>
-      </c>
-      <c r="D19" s="14">
-        <v>3</v>
-      </c>
-      <c r="E19" s="14">
-        <v>4</v>
-      </c>
-      <c r="F19" s="14">
-        <v>25</v>
-      </c>
-      <c r="G19" s="14">
-        <v>11</v>
-      </c>
-      <c r="H19" s="14">
-        <v>3</v>
-      </c>
-      <c r="I19">
-        <v>45</v>
-      </c>
-      <c r="J19" s="20">
-        <f t="shared" si="3"/>
-        <v>16.260869565217391</v>
-      </c>
-      <c r="K19">
-        <f t="shared" si="2"/>
-        <v>17</v>
-      </c>
-      <c r="L19" s="18">
-        <f t="shared" si="4"/>
-        <v>0.95652173913043481</v>
-      </c>
-    </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A20" s="16" t="s">
-        <v>59</v>
-      </c>
-      <c r="B20" s="14">
-        <v>4</v>
-      </c>
-      <c r="C20" s="14">
-        <v>4</v>
-      </c>
-      <c r="D20" s="14">
-        <v>5</v>
-      </c>
-      <c r="E20" s="14">
-        <v>4</v>
-      </c>
-      <c r="F20" s="14">
-        <v>26</v>
-      </c>
-      <c r="G20" s="14">
-        <v>12</v>
-      </c>
-      <c r="H20" s="14">
-        <v>3</v>
-      </c>
-      <c r="I20">
-        <v>45</v>
-      </c>
-      <c r="J20" s="20">
-        <f t="shared" si="3"/>
-        <v>17.739130434782609</v>
-      </c>
-      <c r="K20">
-        <f t="shared" si="2"/>
-        <v>17</v>
-      </c>
-      <c r="L20" s="18">
-        <f t="shared" si="4"/>
-        <v>1.0434782608695652</v>
-      </c>
-    </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A21" s="16" t="s">
-        <v>36</v>
-      </c>
-      <c r="B21" s="14">
-        <v>4</v>
-      </c>
-      <c r="C21" s="14">
-        <v>3</v>
-      </c>
-      <c r="D21" s="14">
-        <v>5</v>
-      </c>
-      <c r="E21" s="14">
-        <v>4</v>
-      </c>
-      <c r="F21" s="14">
-        <v>28</v>
-      </c>
-      <c r="G21" s="14">
-        <v>13</v>
-      </c>
-      <c r="H21" s="14">
-        <v>2</v>
-      </c>
-      <c r="I21">
-        <v>50</v>
-      </c>
-      <c r="J21" s="20">
-        <f t="shared" si="3"/>
-        <v>21.478260869565215</v>
-      </c>
-      <c r="K21">
-        <f t="shared" si="2"/>
-        <v>19</v>
-      </c>
-      <c r="L21" s="18">
-        <f t="shared" si="4"/>
-        <v>1.1304347826086956</v>
-      </c>
-    </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A22" s="16" t="s">
-        <v>35</v>
-      </c>
-      <c r="B22" s="14">
-        <v>3</v>
-      </c>
-      <c r="C22" s="14">
-        <v>2</v>
-      </c>
-      <c r="D22" s="14">
-        <v>5</v>
-      </c>
-      <c r="E22" s="14">
-        <v>4</v>
-      </c>
-      <c r="F22" s="14">
-        <v>31</v>
-      </c>
-      <c r="G22" s="14">
-        <v>14</v>
-      </c>
-      <c r="H22" s="14">
-        <v>2</v>
-      </c>
-      <c r="I22">
-        <v>50</v>
-      </c>
-      <c r="J22" s="20">
-        <f t="shared" si="3"/>
-        <v>23.130434782608695</v>
-      </c>
-      <c r="K22">
-        <f t="shared" si="2"/>
-        <v>19</v>
-      </c>
-      <c r="L22" s="18">
-        <f t="shared" si="4"/>
-        <v>1.2173913043478262</v>
-      </c>
-    </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A23" s="16" t="s">
-        <v>60</v>
-      </c>
-      <c r="B23" s="14">
-        <v>5</v>
-      </c>
-      <c r="C23" s="14">
-        <v>5</v>
-      </c>
-      <c r="D23" s="14">
-        <v>3</v>
-      </c>
-      <c r="E23" s="14">
-        <v>4</v>
-      </c>
-      <c r="F23" s="14">
-        <v>24</v>
-      </c>
-      <c r="G23" s="14">
-        <v>11</v>
-      </c>
-      <c r="H23" s="14">
-        <v>3</v>
-      </c>
-      <c r="I23">
-        <v>50</v>
-      </c>
-      <c r="J23" s="20">
-        <f t="shared" si="3"/>
-        <v>18.173913043478262</v>
-      </c>
-      <c r="K23">
-        <f t="shared" si="2"/>
-        <v>19</v>
-      </c>
-      <c r="L23" s="18">
-        <f t="shared" si="4"/>
-        <v>0.95652173913043481</v>
-      </c>
-    </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A24" s="16" t="s">
-        <v>77</v>
-      </c>
-      <c r="B24" s="14">
-        <v>5</v>
-      </c>
-      <c r="C24" s="14">
-        <v>5</v>
-      </c>
-      <c r="D24" s="14">
-        <v>3</v>
-      </c>
-      <c r="E24" s="14">
-        <v>4</v>
-      </c>
-      <c r="F24" s="14">
-        <v>25</v>
-      </c>
-      <c r="G24" s="14">
-        <v>11</v>
-      </c>
-      <c r="H24" s="14">
-        <v>3</v>
-      </c>
-      <c r="I24">
-        <v>50</v>
-      </c>
-      <c r="J24" s="20">
-        <f t="shared" si="3"/>
-        <v>18.173913043478262</v>
-      </c>
-      <c r="K24">
-        <f t="shared" si="2"/>
-        <v>19</v>
-      </c>
-      <c r="L24" s="18">
-        <f t="shared" si="4"/>
-        <v>0.95652173913043481</v>
-      </c>
-    </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A25" s="16" t="s">
-        <v>31</v>
-      </c>
-      <c r="B25" s="14">
-        <v>4</v>
-      </c>
-      <c r="C25" s="14">
-        <v>4</v>
-      </c>
-      <c r="D25" s="14">
-        <v>5</v>
-      </c>
-      <c r="E25" s="14">
-        <v>4</v>
-      </c>
-      <c r="F25" s="14">
-        <v>27</v>
-      </c>
-      <c r="G25" s="14">
-        <v>12</v>
-      </c>
-      <c r="H25" s="14">
-        <v>3</v>
-      </c>
-      <c r="I25">
-        <v>55</v>
-      </c>
-      <c r="J25" s="20">
-        <f t="shared" si="3"/>
-        <v>21.913043478260867</v>
-      </c>
-      <c r="K25">
-        <f t="shared" si="2"/>
-        <v>21</v>
-      </c>
-      <c r="L25" s="18">
-        <f t="shared" si="4"/>
-        <v>1.0434782608695652</v>
-      </c>
-    </row>
-    <row r="26" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="16" t="s">
-        <v>32</v>
-      </c>
-      <c r="B26" s="14">
-        <v>5</v>
-      </c>
-      <c r="C26" s="14">
-        <v>4</v>
-      </c>
-      <c r="D26" s="14">
-        <v>5</v>
-      </c>
-      <c r="E26" s="14">
-        <v>4</v>
-      </c>
-      <c r="F26" s="14">
-        <v>31</v>
-      </c>
-      <c r="G26" s="14">
-        <v>13</v>
-      </c>
-      <c r="H26" s="14">
-        <v>2</v>
-      </c>
-      <c r="I26">
-        <v>55</v>
-      </c>
-      <c r="J26" s="20">
-        <f t="shared" si="3"/>
-        <v>23.739130434782606</v>
-      </c>
-      <c r="K26">
-        <f t="shared" si="2"/>
-        <v>21</v>
-      </c>
-      <c r="L26" s="18">
-        <f t="shared" si="4"/>
-        <v>1.1304347826086956</v>
-      </c>
-    </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A27" s="16" t="s">
-        <v>34</v>
-      </c>
-      <c r="B27" s="14">
-        <v>5</v>
-      </c>
-      <c r="C27" s="14">
-        <v>4</v>
-      </c>
-      <c r="D27" s="14">
-        <v>6</v>
-      </c>
-      <c r="E27" s="14">
-        <v>4</v>
-      </c>
-      <c r="F27" s="14">
-        <v>30</v>
-      </c>
-      <c r="G27" s="14">
-        <v>13</v>
-      </c>
-      <c r="H27" s="14">
-        <v>3</v>
-      </c>
-      <c r="I27">
-        <v>55</v>
-      </c>
-      <c r="J27" s="20">
-        <f t="shared" si="3"/>
-        <v>23.739130434782606</v>
-      </c>
-      <c r="K27">
-        <f t="shared" si="2"/>
-        <v>21</v>
-      </c>
-      <c r="L27" s="18">
-        <f t="shared" si="4"/>
-        <v>1.1304347826086956</v>
-      </c>
-    </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="G28" s="17">
-        <f>AVERAGE(G16:G27)</f>
-        <v>11.5</v>
-      </c>
-      <c r="K28">
-        <f>AVERAGE(K16:K27)</f>
-        <v>18.333333333333332</v>
-      </c>
-    </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A29" s="13" t="s">
-        <v>134</v>
-      </c>
-      <c r="B29" s="15" t="s">
-        <v>135</v>
-      </c>
-      <c r="C29" s="15" t="s">
-        <v>136</v>
-      </c>
-      <c r="D29" s="15" t="s">
-        <v>137</v>
-      </c>
-      <c r="E29" s="15" t="s">
-        <v>138</v>
-      </c>
-      <c r="F29" s="15" t="s">
-        <v>4</v>
-      </c>
-      <c r="G29" s="15" t="s">
-        <v>139</v>
-      </c>
-      <c r="H29" s="15" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A30" s="16" t="s">
-        <v>99</v>
-      </c>
-      <c r="B30" s="14">
-        <v>3</v>
-      </c>
-      <c r="C30" s="14">
-        <v>3</v>
-      </c>
-      <c r="D30" s="14">
-        <v>3</v>
-      </c>
-      <c r="E30" s="14">
-        <v>5</v>
-      </c>
-      <c r="F30" s="14">
-        <v>33</v>
-      </c>
-      <c r="G30" s="14">
-        <v>15</v>
-      </c>
-      <c r="H30" s="14">
-        <v>2</v>
-      </c>
-      <c r="I30">
-        <v>60</v>
-      </c>
-      <c r="J30" s="14">
-        <v>23</v>
-      </c>
-      <c r="K30">
-        <f t="shared" si="2"/>
-        <v>23</v>
-      </c>
-    </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A31" s="16" t="s">
-        <v>79</v>
-      </c>
-      <c r="B31" s="14">
-        <v>5</v>
-      </c>
-      <c r="C31" s="14">
-        <v>2</v>
-      </c>
-      <c r="D31" s="14">
-        <v>3</v>
-      </c>
-      <c r="E31" s="14">
-        <v>5</v>
-      </c>
-      <c r="F31" s="14">
-        <v>33</v>
-      </c>
-      <c r="G31" s="14">
-        <v>15</v>
-      </c>
-      <c r="H31" s="14">
-        <v>2</v>
-      </c>
-      <c r="I31">
-        <v>60</v>
-      </c>
-      <c r="J31" s="14">
-        <v>22</v>
-      </c>
-      <c r="K31">
-        <f t="shared" si="2"/>
-        <v>23</v>
-      </c>
-    </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A32" s="16" t="s">
-        <v>81</v>
-      </c>
-      <c r="B32" s="14">
-        <v>3</v>
-      </c>
-      <c r="C32" s="14">
-        <v>5</v>
-      </c>
-      <c r="D32" s="14">
-        <v>2</v>
-      </c>
-      <c r="E32" s="14">
-        <v>5</v>
-      </c>
-      <c r="F32" s="14">
-        <v>30</v>
-      </c>
-      <c r="G32" s="14">
-        <v>14</v>
-      </c>
-      <c r="H32" s="14">
-        <v>1</v>
-      </c>
-      <c r="I32">
-        <v>60</v>
-      </c>
-      <c r="J32" s="14">
-        <v>23</v>
-      </c>
-      <c r="K32">
-        <f t="shared" si="2"/>
-        <v>23</v>
-      </c>
-    </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A33" s="16" t="s">
-        <v>127</v>
-      </c>
-      <c r="B33" s="14">
-        <v>4</v>
-      </c>
-      <c r="C33" s="14">
-        <v>2</v>
-      </c>
-      <c r="D33" s="14">
-        <v>4</v>
-      </c>
-      <c r="E33" s="14">
-        <v>5</v>
-      </c>
-      <c r="F33" s="14">
-        <v>36</v>
-      </c>
-      <c r="G33" s="14">
-        <v>16</v>
-      </c>
-      <c r="H33" s="14">
-        <v>2</v>
-      </c>
-      <c r="I33">
-        <v>65</v>
-      </c>
-      <c r="K33">
-        <f t="shared" si="2"/>
-        <v>25</v>
-      </c>
-    </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A34" s="16" t="s">
-        <v>83</v>
-      </c>
-      <c r="B34" s="14">
-        <v>3</v>
-      </c>
-      <c r="C34" s="14">
-        <v>3</v>
-      </c>
-      <c r="D34" s="14">
-        <v>6</v>
-      </c>
-      <c r="E34" s="14">
-        <v>5</v>
-      </c>
-      <c r="F34" s="14">
-        <v>38</v>
-      </c>
-      <c r="G34" s="14">
-        <v>17</v>
-      </c>
-      <c r="H34" s="14">
-        <v>3</v>
-      </c>
-      <c r="I34">
-        <v>65</v>
-      </c>
-      <c r="K34">
-        <f t="shared" si="2"/>
-        <v>25</v>
-      </c>
-    </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A35" s="16" t="s">
-        <v>85</v>
-      </c>
-      <c r="B35" s="14">
-        <v>3</v>
-      </c>
-      <c r="C35" s="14">
-        <v>4</v>
-      </c>
-      <c r="D35" s="14">
-        <v>5</v>
-      </c>
-      <c r="E35" s="14">
-        <v>5</v>
-      </c>
-      <c r="F35" s="14">
-        <v>34</v>
-      </c>
-      <c r="G35" s="14">
-        <v>16</v>
-      </c>
-      <c r="H35" s="14">
-        <v>3</v>
-      </c>
-      <c r="I35">
-        <v>65</v>
-      </c>
-      <c r="K35">
-        <f t="shared" si="2"/>
-        <v>25</v>
-      </c>
-    </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A36" s="16" t="s">
-        <v>87</v>
-      </c>
-      <c r="B36" s="14">
-        <v>3</v>
-      </c>
-      <c r="C36" s="14">
-        <v>4</v>
-      </c>
-      <c r="D36" s="14">
-        <v>5</v>
-      </c>
-      <c r="E36" s="14">
-        <v>5</v>
-      </c>
-      <c r="F36" s="14">
-        <v>36</v>
-      </c>
-      <c r="G36" s="14">
-        <v>16</v>
-      </c>
-      <c r="H36" s="14">
-        <v>3</v>
-      </c>
-      <c r="I36">
-        <v>70</v>
-      </c>
-      <c r="K36">
-        <f t="shared" si="2"/>
-        <v>27</v>
-      </c>
-    </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A37" s="16" t="s">
-        <v>101</v>
-      </c>
-      <c r="B37" s="14">
-        <v>5</v>
-      </c>
-      <c r="C37" s="14">
-        <v>4</v>
-      </c>
-      <c r="D37" s="14">
-        <v>6</v>
-      </c>
-      <c r="E37" s="14">
-        <v>5</v>
-      </c>
-      <c r="F37" s="14">
-        <v>36</v>
-      </c>
-      <c r="G37" s="14">
-        <v>16</v>
-      </c>
-      <c r="H37" s="14">
-        <v>4</v>
-      </c>
-      <c r="I37">
-        <v>70</v>
-      </c>
-      <c r="K37">
-        <f t="shared" si="2"/>
-        <v>27</v>
-      </c>
-    </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A38" s="16" t="s">
-        <v>89</v>
-      </c>
-      <c r="B38" s="14">
-        <v>3</v>
-      </c>
-      <c r="C38" s="14">
-        <v>5</v>
-      </c>
-      <c r="D38" s="14">
-        <v>3</v>
-      </c>
-      <c r="E38" s="14">
-        <v>5</v>
-      </c>
-      <c r="F38" s="14">
-        <v>37</v>
-      </c>
-      <c r="G38" s="14">
-        <v>16</v>
-      </c>
-      <c r="H38" s="14">
-        <v>2</v>
-      </c>
-      <c r="I38">
-        <v>70</v>
-      </c>
-      <c r="K38">
-        <f t="shared" si="2"/>
-        <v>27</v>
-      </c>
-    </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A39" s="16" t="s">
-        <v>100</v>
-      </c>
-      <c r="B39" s="14">
-        <v>3</v>
-      </c>
-      <c r="C39" s="14">
-        <v>5</v>
-      </c>
-      <c r="D39" s="14">
-        <v>6</v>
-      </c>
-      <c r="E39" s="14">
-        <v>5</v>
-      </c>
-      <c r="F39" s="14">
-        <v>39</v>
-      </c>
-      <c r="G39" s="14">
-        <v>17</v>
-      </c>
-      <c r="H39" s="14">
-        <v>4</v>
-      </c>
-      <c r="I39">
-        <v>75</v>
-      </c>
-      <c r="K39">
-        <f t="shared" si="2"/>
-        <v>29</v>
-      </c>
-    </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A40" s="16" t="s">
-        <v>91</v>
-      </c>
-      <c r="B40" s="14">
-        <v>4</v>
-      </c>
-      <c r="C40" s="14">
-        <v>5</v>
-      </c>
-      <c r="D40" s="14">
-        <v>5</v>
-      </c>
-      <c r="E40" s="14">
-        <v>5</v>
-      </c>
-      <c r="F40" s="14">
-        <v>41</v>
-      </c>
-      <c r="G40" s="14">
-        <v>17</v>
-      </c>
-      <c r="H40" s="14">
-        <v>3</v>
-      </c>
-      <c r="I40">
-        <v>75</v>
-      </c>
-      <c r="K40">
-        <f t="shared" si="2"/>
-        <v>29</v>
-      </c>
-    </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A41" s="16" t="s">
-        <v>105</v>
-      </c>
-      <c r="B41" s="14">
-        <v>3</v>
-      </c>
-      <c r="C41" s="14">
-        <v>3</v>
-      </c>
-      <c r="D41" s="14">
-        <v>5</v>
-      </c>
-      <c r="E41" s="14">
-        <v>5</v>
-      </c>
-      <c r="F41" s="14">
-        <v>39</v>
-      </c>
-      <c r="G41" s="14">
-        <v>18</v>
-      </c>
-      <c r="H41" s="14">
-        <v>3</v>
-      </c>
-      <c r="I41">
-        <v>75</v>
-      </c>
-      <c r="K41">
-        <f t="shared" si="2"/>
-        <v>29</v>
-      </c>
-    </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A43" s="13" t="s">
-        <v>134</v>
-      </c>
-      <c r="B43" s="15" t="s">
-        <v>135</v>
-      </c>
-      <c r="C43" s="15" t="s">
-        <v>136</v>
-      </c>
-      <c r="D43" s="15" t="s">
-        <v>137</v>
-      </c>
-      <c r="E43" s="15" t="s">
-        <v>138</v>
-      </c>
-      <c r="F43" s="15" t="s">
-        <v>4</v>
-      </c>
-      <c r="G43" s="15" t="s">
-        <v>139</v>
-      </c>
-      <c r="H43" s="15" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A44" s="16" t="s">
-        <v>93</v>
-      </c>
-      <c r="B44" s="14">
-        <v>2</v>
-      </c>
-      <c r="C44" s="14">
-        <v>4</v>
-      </c>
-      <c r="D44" s="14">
-        <v>6</v>
-      </c>
-      <c r="E44" s="14">
-        <v>6</v>
-      </c>
-      <c r="F44" s="14">
-        <v>51</v>
-      </c>
-      <c r="G44" s="14">
-        <v>22</v>
-      </c>
-      <c r="H44" s="14">
-        <v>5</v>
-      </c>
-      <c r="I44">
-        <v>80</v>
-      </c>
-      <c r="K44">
-        <f t="shared" si="2"/>
-        <v>31</v>
-      </c>
-    </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A45" s="16" t="s">
-        <v>109</v>
-      </c>
-      <c r="B45" s="14">
-        <v>3</v>
-      </c>
-      <c r="C45" s="14">
-        <v>3</v>
-      </c>
-      <c r="D45" s="14">
-        <v>5</v>
-      </c>
-      <c r="E45" s="14">
-        <v>6</v>
-      </c>
-      <c r="F45" s="14">
-        <v>43</v>
-      </c>
-      <c r="G45" s="14">
-        <v>20</v>
-      </c>
-      <c r="H45" s="14">
-        <v>3</v>
-      </c>
-      <c r="I45">
-        <v>80</v>
-      </c>
-      <c r="K45">
-        <f t="shared" si="2"/>
-        <v>31</v>
-      </c>
-    </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A46" s="16" t="s">
-        <v>121</v>
-      </c>
-      <c r="B46" s="14">
-        <v>5</v>
-      </c>
-      <c r="C46" s="14">
-        <v>3</v>
-      </c>
-      <c r="D46" s="14">
-        <v>4</v>
-      </c>
-      <c r="E46" s="14">
-        <v>6</v>
-      </c>
-      <c r="F46" s="14">
-        <v>41</v>
-      </c>
-      <c r="G46" s="14">
-        <v>19</v>
-      </c>
-      <c r="H46" s="14">
-        <v>3</v>
-      </c>
-      <c r="I46">
-        <v>80</v>
-      </c>
-      <c r="K46">
-        <f t="shared" si="2"/>
-        <v>31</v>
-      </c>
-    </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A47" s="16" t="s">
-        <v>95</v>
-      </c>
-      <c r="B47" s="14">
-        <v>4</v>
-      </c>
-      <c r="C47" s="14">
-        <v>4</v>
-      </c>
-      <c r="D47" s="14">
-        <v>5</v>
-      </c>
-      <c r="E47" s="14">
-        <v>6</v>
-      </c>
-      <c r="F47" s="14">
-        <v>45</v>
-      </c>
-      <c r="G47" s="14">
-        <v>20</v>
-      </c>
-      <c r="H47" s="14">
-        <v>4</v>
-      </c>
-      <c r="I47">
-        <v>85</v>
-      </c>
-      <c r="K47">
-        <f t="shared" si="2"/>
-        <v>33</v>
-      </c>
-    </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A48" s="16" t="s">
-        <v>107</v>
-      </c>
-      <c r="B48" s="14">
-        <v>2</v>
-      </c>
-      <c r="C48" s="14">
-        <v>3</v>
-      </c>
-      <c r="D48" s="14">
-        <v>6</v>
-      </c>
-      <c r="E48" s="14">
-        <v>6</v>
-      </c>
-      <c r="F48" s="14">
-        <v>52</v>
-      </c>
-      <c r="G48" s="14">
-        <v>23</v>
-      </c>
-      <c r="H48" s="14">
-        <v>3</v>
-      </c>
-      <c r="I48">
-        <v>85</v>
-      </c>
-      <c r="K48">
-        <f t="shared" si="2"/>
-        <v>33</v>
-      </c>
-    </row>
-    <row r="49" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A49" s="16" t="s">
-        <v>111</v>
-      </c>
-      <c r="B49" s="14">
-        <v>4</v>
-      </c>
-      <c r="C49" s="14">
-        <v>4</v>
-      </c>
-      <c r="D49" s="14">
-        <v>6</v>
-      </c>
-      <c r="E49" s="14">
-        <v>6</v>
-      </c>
-      <c r="F49" s="14">
-        <v>48</v>
-      </c>
-      <c r="G49" s="14">
-        <v>22</v>
-      </c>
-      <c r="H49" s="14">
-        <v>4</v>
-      </c>
-      <c r="I49">
-        <v>90</v>
-      </c>
-      <c r="K49">
-        <f t="shared" si="2"/>
-        <v>35</v>
-      </c>
-    </row>
-    <row r="50" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A50" s="16" t="s">
-        <v>123</v>
-      </c>
-      <c r="B50" s="14">
-        <v>2</v>
-      </c>
-      <c r="C50" s="14">
-        <v>5</v>
-      </c>
-      <c r="D50" s="14">
-        <v>3</v>
-      </c>
-      <c r="E50" s="14">
-        <v>6</v>
-      </c>
-      <c r="F50" s="14">
-        <v>44</v>
-      </c>
-      <c r="G50" s="14">
-        <v>21</v>
-      </c>
-      <c r="H50" s="14">
-        <v>2</v>
-      </c>
-      <c r="I50">
-        <v>90</v>
-      </c>
-      <c r="K50">
-        <f t="shared" si="2"/>
-        <v>35</v>
-      </c>
-    </row>
-    <row r="51" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A51" s="16" t="s">
-        <v>113</v>
-      </c>
-      <c r="B51" s="14">
-        <v>4</v>
-      </c>
-      <c r="C51" s="14">
-        <v>2</v>
-      </c>
-      <c r="D51" s="14">
-        <v>4</v>
-      </c>
-      <c r="E51" s="14">
-        <v>6</v>
-      </c>
-      <c r="F51" s="14">
-        <v>43</v>
-      </c>
-      <c r="G51" s="14">
-        <v>22</v>
-      </c>
-      <c r="H51" s="14">
-        <v>2</v>
-      </c>
-      <c r="I51">
-        <v>95</v>
-      </c>
-      <c r="K51">
-        <f t="shared" si="2"/>
-        <v>37</v>
-      </c>
-    </row>
-    <row r="52" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A52" s="16" t="s">
-        <v>115</v>
-      </c>
-      <c r="B52" s="14">
-        <v>1</v>
-      </c>
-      <c r="C52" s="14">
-        <v>4</v>
-      </c>
-      <c r="D52" s="14">
-        <v>6</v>
-      </c>
-      <c r="E52" s="14">
-        <v>6</v>
-      </c>
-      <c r="F52" s="14">
-        <v>56</v>
-      </c>
-      <c r="G52" s="14">
-        <v>24</v>
-      </c>
-      <c r="H52" s="14">
-        <v>2</v>
-      </c>
-      <c r="I52">
-        <v>100</v>
-      </c>
-      <c r="K52">
-        <f t="shared" si="2"/>
-        <v>39</v>
-      </c>
-    </row>
-    <row r="53" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A53" s="16" t="s">
-        <v>117</v>
-      </c>
-      <c r="B53" s="14">
-        <v>3</v>
-      </c>
-      <c r="C53" s="14">
-        <v>4</v>
-      </c>
-      <c r="D53" s="14">
-        <v>6</v>
-      </c>
-      <c r="E53" s="14">
-        <v>6</v>
-      </c>
-      <c r="F53" s="14">
-        <v>58</v>
-      </c>
-      <c r="G53" s="14">
-        <v>25</v>
-      </c>
-      <c r="H53" s="14">
-        <v>4</v>
-      </c>
-      <c r="I53">
-        <v>100</v>
-      </c>
-      <c r="K53">
-        <f t="shared" si="2"/>
-        <v>39</v>
-      </c>
-    </row>
-    <row r="54" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A54" s="16" t="s">
-        <v>118</v>
-      </c>
-      <c r="B54" s="14">
-        <v>1</v>
-      </c>
-      <c r="C54" s="14">
-        <v>5</v>
-      </c>
-      <c r="D54" s="14">
-        <v>5</v>
-      </c>
-      <c r="E54" s="14">
-        <v>6</v>
-      </c>
-      <c r="F54" s="14">
-        <v>57</v>
-      </c>
-      <c r="G54" s="14">
-        <v>24</v>
-      </c>
-      <c r="H54" s="14">
-        <v>3</v>
-      </c>
-      <c r="I54">
-        <v>100</v>
-      </c>
-      <c r="K54">
-        <f t="shared" si="2"/>
-        <v>39</v>
-      </c>
-    </row>
-    <row r="55" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A55" s="16" t="s">
-        <v>119</v>
-      </c>
-      <c r="B55" s="14">
-        <v>2</v>
-      </c>
-      <c r="C55" s="14">
-        <v>4</v>
-      </c>
-      <c r="D55" s="14">
-        <v>6</v>
-      </c>
-      <c r="E55" s="14">
-        <v>6</v>
-      </c>
-      <c r="F55" s="14">
-        <v>55</v>
-      </c>
-      <c r="G55" s="14">
-        <v>24</v>
-      </c>
-      <c r="H55" s="14">
-        <v>3</v>
-      </c>
-      <c r="I55">
-        <v>100</v>
-      </c>
-      <c r="K55">
-        <f t="shared" si="2"/>
-        <v>39</v>
-      </c>
-    </row>
-    <row r="63" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="F63" s="13"/>
-      <c r="G63" s="13"/>
-      <c r="J63" s="13"/>
-    </row>
-    <row r="64" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="F64" s="21"/>
-      <c r="G64" s="21"/>
-      <c r="J64" s="16"/>
-      <c r="P64" s="13"/>
-    </row>
-    <row r="65" spans="6:16" x14ac:dyDescent="0.25">
-      <c r="F65" s="21"/>
-      <c r="G65" s="21"/>
-      <c r="J65" s="16"/>
-      <c r="P65" s="21"/>
-    </row>
-    <row r="66" spans="6:16" x14ac:dyDescent="0.25">
-      <c r="F66" s="21"/>
-      <c r="G66" s="21"/>
-      <c r="J66" s="16"/>
-      <c r="P66" s="21"/>
-    </row>
-    <row r="67" spans="6:16" x14ac:dyDescent="0.25">
-      <c r="F67" s="21"/>
-      <c r="G67" s="21"/>
-      <c r="J67" s="16"/>
-      <c r="P67" s="21"/>
-    </row>
-    <row r="68" spans="6:16" x14ac:dyDescent="0.25">
-      <c r="F68" s="21"/>
-      <c r="G68" s="21"/>
-      <c r="J68" s="16"/>
-      <c r="P68" s="21"/>
-    </row>
-    <row r="69" spans="6:16" x14ac:dyDescent="0.25">
-      <c r="F69" s="21"/>
-      <c r="G69" s="21"/>
-      <c r="J69" s="16"/>
-      <c r="P69" s="21"/>
-    </row>
-    <row r="70" spans="6:16" x14ac:dyDescent="0.25">
-      <c r="F70" s="21"/>
-      <c r="G70" s="21"/>
-      <c r="J70" s="16"/>
-      <c r="P70" s="21"/>
-    </row>
-    <row r="71" spans="6:16" x14ac:dyDescent="0.25">
-      <c r="F71" s="21"/>
-      <c r="G71" s="21"/>
-      <c r="J71" s="16"/>
-      <c r="P71" s="21"/>
-    </row>
-    <row r="72" spans="6:16" x14ac:dyDescent="0.25">
-      <c r="F72" s="21"/>
-      <c r="G72" s="21"/>
-      <c r="J72" s="16"/>
-      <c r="P72" s="21"/>
-    </row>
-    <row r="73" spans="6:16" x14ac:dyDescent="0.25">
-      <c r="F73" s="21"/>
-      <c r="G73" s="21"/>
-      <c r="J73" s="16"/>
-      <c r="P73" s="21"/>
-    </row>
-    <row r="74" spans="6:16" x14ac:dyDescent="0.25">
-      <c r="F74" s="21"/>
-      <c r="G74" s="21"/>
-      <c r="J74" s="16"/>
-      <c r="P74" s="21"/>
-    </row>
-    <row r="75" spans="6:16" x14ac:dyDescent="0.25">
-      <c r="F75" s="21"/>
-      <c r="G75" s="21"/>
-      <c r="J75" s="16"/>
-      <c r="P75" s="21"/>
-    </row>
-    <row r="76" spans="6:16" x14ac:dyDescent="0.25">
-      <c r="F76" s="21"/>
-      <c r="G76" s="21"/>
-      <c r="J76" s="16"/>
-      <c r="P76" s="21"/>
-    </row>
-    <row r="77" spans="6:16" x14ac:dyDescent="0.25">
-      <c r="F77" s="21"/>
-      <c r="G77" s="21"/>
-      <c r="J77" s="16"/>
-      <c r="P77" s="21"/>
-    </row>
-    <row r="78" spans="6:16" x14ac:dyDescent="0.25">
-      <c r="F78" s="21"/>
-      <c r="G78" s="21"/>
-      <c r="J78" s="16"/>
-      <c r="P78" s="21"/>
-    </row>
-    <row r="79" spans="6:16" x14ac:dyDescent="0.25">
-      <c r="F79" s="21"/>
-      <c r="G79" s="21"/>
-      <c r="J79" s="16"/>
-      <c r="P79" s="21"/>
-    </row>
-    <row r="80" spans="6:16" x14ac:dyDescent="0.25">
-      <c r="F80" s="21"/>
-      <c r="G80" s="21"/>
-      <c r="J80" s="16"/>
-      <c r="P80" s="21"/>
-    </row>
-    <row r="81" spans="16:16" x14ac:dyDescent="0.25">
-      <c r="P81" s="21"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>
--- a/docs/Mech Data.xlsx
+++ b/docs/Mech Data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\FoundryData-Dev\Data\systems\mwd\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10FBC4AF-F6F2-43DD-860F-6EEE9C0A8CED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E516EFF-50DE-4984-80EA-ABC96E607761}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="51480" yWindow="-4995" windowWidth="16440" windowHeight="28320" xr2:uid="{8D44F242-D0B2-4B9E-94CF-33F11494976A}"/>
+    <workbookView xWindow="27240" yWindow="1050" windowWidth="23205" windowHeight="19275" activeTab="2" xr2:uid="{8D44F242-D0B2-4B9E-94CF-33F11494976A}"/>
   </bookViews>
   <sheets>
     <sheet name="Mechs" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="713" uniqueCount="437">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="789" uniqueCount="497">
   <si>
     <t>Chassis</t>
   </si>
@@ -794,12 +794,6 @@
     <t>Reinforced Cockpit</t>
   </si>
   <si>
-    <t>Modules</t>
-  </si>
-  <si>
-    <t>Quirks</t>
-  </si>
-  <si>
     <t>Low Profile</t>
   </si>
   <si>
@@ -887,9 +881,6 @@
     <t>Combat  Electronics</t>
   </si>
   <si>
-    <t>Hardened Structure Components</t>
-  </si>
-  <si>
     <t>Advanced Optics</t>
   </si>
   <si>
@@ -899,6 +890,9 @@
     <t>Jump Booster</t>
   </si>
   <si>
+    <t>Thermal Exchanger</t>
+  </si>
+  <si>
     <t>Thermal Bank</t>
   </si>
   <si>
@@ -935,15 +929,9 @@
     <t>Electronic Protection Array</t>
   </si>
   <si>
-    <t>UAV Integration Compartment</t>
-  </si>
-  <si>
     <t>Hardened Armor</t>
   </si>
   <si>
-    <t>Laser Heat Sink</t>
-  </si>
-  <si>
     <t>Reactive Plating</t>
   </si>
   <si>
@@ -1147,9 +1135,6 @@
     <t>speedBoost, legs, heat</t>
   </si>
   <si>
-    <t>-1 trackingPenalty</t>
-  </si>
-  <si>
     <t>Generates +1 heat when used</t>
   </si>
   <si>
@@ -2800,9 +2785,6 @@
     <t>Targeting/Attack; Mobility Provider</t>
   </si>
   <si>
-    <t>Improved Actuators Mechanics</t>
-  </si>
-  <si>
     <t xml:space="preserve">Packrat </t>
   </si>
   <si>
@@ -2903,6 +2885,609 @@
   </si>
   <si>
     <t>Cruiser</t>
+  </si>
+  <si>
+    <t>Machine Quirks</t>
+  </si>
+  <si>
+    <t>Heat disappation unaffected by environmental factors</t>
+  </si>
+  <si>
+    <t>+1 heatProfile</t>
+  </si>
+  <si>
+    <t>+1 heatDissapation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Armor gains 2 Concussive Resistance </t>
+  </si>
+  <si>
+    <t>Armor gains 2 Energy Resistance</t>
+  </si>
+  <si>
+    <t>Armor gains 2 Penatrating Resistance</t>
+  </si>
+  <si>
+    <t>Asset Modules</t>
+  </si>
+  <si>
+    <t>Anti-Missile System</t>
+  </si>
+  <si>
+    <t>Laser AMS</t>
+  </si>
+  <si>
+    <t>Laser Heat Sinks</t>
+  </si>
+  <si>
+    <t>Hardened Structural Components</t>
+  </si>
+  <si>
+    <t>UAV Control Pod</t>
+  </si>
+  <si>
+    <t>Missile Cluster Dice hit on 6</t>
+  </si>
+  <si>
+    <t>High Emission: Enemies reduce trackingPenalty against this machine by 1, minimum 0. Enemies gain +1 die to acquireTarget against this machine when emissions are relevant.</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>High Emission [Rating]</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Enemies reduce trackingPenalty against this machine by [Rating], minimum 0. Enemies gain +[Rating] die to acquireTarget against this machine when emissions are relevant.</t>
+  </si>
+  <si>
+    <t>High Emission (1)</t>
+  </si>
+  <si>
+    <t>Volatile component or ammo explosion event</t>
+  </si>
+  <si>
+    <t>CASE destroyed/consumed when it prevents a catastrophic event.</t>
+  </si>
+  <si>
+    <t>Prevents full machine destruction and automatic crew death. Local location still suffers severe consequence: condition +1, stress spike, or module destruction.</t>
+  </si>
+  <si>
+    <r>
+      <t>+2 dice</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> to </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>feedReset</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> and other Feed-related remedies. Applies to Jammed Ballistic, Ammo Feed Fault, Weapon Supply Interruption, missile feed failures.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>+2 dice</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> to </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>powerReroute</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>systemReset</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>, and power-routing remedies. Helps reactor instability, power bus outage, shutdown recovery where appropriate.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Increase global machine shock/pressure capacity by </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>+1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Ablative Module:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> drops to Resistance 1 at 50% armor remaining; destroyed at 25% armor remaining.</t>
+    </r>
+  </si>
+  <si>
+    <t>Armor &gt; 0</t>
+  </si>
+  <si>
+    <t>Gains High Emission (1) when Heat Status not SAFE</t>
+  </si>
+  <si>
+    <t>armorResistance</t>
+  </si>
+  <si>
+    <t>heatDissipation</t>
+  </si>
+  <si>
+    <t>heatBuffer</t>
+  </si>
+  <si>
+    <t>structure</t>
+  </si>
+  <si>
+    <t>remediation</t>
+  </si>
+  <si>
+    <t>Ready; not Prone/immobile; charge available</t>
+  </si>
+  <si>
+    <t>Ready; Structure remaining &lt; 100%</t>
+  </si>
+  <si>
+    <t>Immediately reduce heat, -5 heat</t>
+  </si>
+  <si>
+    <t>Consume on use</t>
+  </si>
+  <si>
+    <t>Heat &gt; 0; Coolant systems functional</t>
+  </si>
+  <si>
+    <t>At the start of the activation, recover 2 armor damage</t>
+  </si>
+  <si>
+    <t>10 charges then asset destroyed/consumed</t>
+  </si>
+  <si>
+    <t>Actuator Enhancement System</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">+3 DR; Grants </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Shield Block</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> reaction: Reduce incoming damage by 1</t>
+    </r>
+  </si>
+  <si>
+    <t>-5 AR for limb-mounted weapons; 5 Shield Block charges - asset disabled when out of charges</t>
+  </si>
+  <si>
+    <t>Ready; heat sinks functional</t>
+  </si>
+  <si>
+    <t>Ready</t>
+  </si>
+  <si>
+    <t>10 Charges</t>
+  </si>
+  <si>
+    <t>Incoming missile/cluster attack; charges available</t>
+  </si>
+  <si>
+    <t>Incoming missile/cluster attack</t>
+  </si>
+  <si>
+    <t>consumable</t>
+  </si>
+  <si>
+    <t>autoRepair, consumable</t>
+  </si>
+  <si>
+    <t>Free Action to jump 180 meters (or add +180 meters to a Jump Move)</t>
+  </si>
+  <si>
+    <t>1 charge, 3 turn recovery; Use generates +1 heat</t>
+  </si>
+  <si>
+    <t>High Emission (1) while in use, FA to sustain lock</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Target at </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>contact</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> or better; Line of Sight - successful TAG action</t>
+    </r>
+  </si>
+  <si>
+    <t>Target TAGged - Sensor Locked, generateTargetData against TAGged enemy is a Free Action</t>
+  </si>
+  <si>
+    <t>NARC Attack hits target; beacon attached</t>
+  </si>
+  <si>
+    <t>Attach NARC Beacon - NARCed target counts as Sensor Locked only for compatible guided missile systems., Beacon carrier trackingPenalty reduced by 3</t>
+  </si>
+  <si>
+    <t>UAV Active and not jammed</t>
+  </si>
+  <si>
+    <t>C3 Active</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Friendly C3 units may use the best friendly detection state on a target, capped at </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>track</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> unless the attacker also has direct </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>lock</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>. May use best shared targetingData packet from the network, not stacked.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>network</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>c3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>targetingData</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>sharedSensors</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>network</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>uav</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>remoteSensor</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>eyeInSky</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>network</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>command</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>intelligence</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>initiative</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>coordination</t>
+    </r>
+  </si>
+  <si>
+    <t>Suppressed by IFF Jammer/network disruption</t>
+  </si>
+  <si>
+    <t>All friendly SLIC units have +1 initiative; Grants +1 die to acquireTarget, sensorSweep, holdLink, breakLock, generateTargetData to all friendly units within 500m</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Provides passive battlefield overwatch. Grants </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>+1 die</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> to Acquire Target / Sensor Sweep. Can maintain </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>contact</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> on visible enemies in UAV coverage. Grants +2 dice to Piloting checks to cross hazardous terrain/mine fields . Removes indirect fire penalties for operator.</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -3005,7 +3590,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -3056,17 +3641,15 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="49" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -3075,6 +3658,27 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -6752,58 +7356,58 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="15.75" thickBot="1">
-      <c r="A1" s="31" t="s">
+      <c r="A1" s="29" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="31" t="s">
+      <c r="B1" s="29" t="s">
         <v>9</v>
       </c>
-      <c r="C1" s="31" t="s">
+      <c r="C1" s="29" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="31" t="s">
+      <c r="D1" s="29" t="s">
         <v>72</v>
       </c>
-      <c r="E1" s="31" t="s">
-        <v>270</v>
-      </c>
-      <c r="F1" s="31" t="s">
+      <c r="E1" s="29" t="s">
+        <v>268</v>
+      </c>
+      <c r="F1" s="29" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="31" t="s">
+      <c r="G1" s="29" t="s">
         <v>4</v>
       </c>
-      <c r="H1" s="31" t="s">
+      <c r="H1" s="29" t="s">
         <v>5</v>
       </c>
-      <c r="I1" s="31" t="s">
+      <c r="I1" s="29" t="s">
         <v>7</v>
       </c>
-      <c r="J1" s="31" t="s">
+      <c r="J1" s="29" t="s">
         <v>13</v>
       </c>
-      <c r="K1" s="31" t="s">
+      <c r="K1" s="29" t="s">
         <v>17</v>
       </c>
-      <c r="L1" s="31" t="s">
+      <c r="L1" s="29" t="s">
         <v>18</v>
       </c>
-      <c r="M1" s="31" t="s">
+      <c r="M1" s="29" t="s">
         <v>0</v>
       </c>
-      <c r="N1" s="31" t="s">
+      <c r="N1" s="29" t="s">
         <v>19</v>
       </c>
-      <c r="O1" s="32" t="s">
+      <c r="O1" s="30" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="33" t="s">
+      <c r="P1" s="31" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="2" spans="1:16">
       <c r="B2" t="s">
-        <v>403</v>
+        <v>397</v>
       </c>
       <c r="C2">
         <v>20</v>
@@ -6812,29 +7416,29 @@
         <v>128</v>
       </c>
       <c r="E2" t="s">
-        <v>411</v>
+        <v>405</v>
       </c>
     </row>
     <row r="3" spans="1:16">
       <c r="A3" t="s">
-        <v>404</v>
+        <v>398</v>
       </c>
       <c r="B3" t="s">
-        <v>405</v>
+        <v>399</v>
       </c>
       <c r="C3">
         <v>21</v>
       </c>
       <c r="D3" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="E3" t="s">
-        <v>406</v>
+        <v>400</v>
       </c>
     </row>
     <row r="4" spans="1:16">
       <c r="B4" t="s">
-        <v>407</v>
+        <v>401</v>
       </c>
       <c r="C4">
         <v>25</v>
@@ -6843,26 +7447,26 @@
         <v>130</v>
       </c>
       <c r="E4" t="s">
-        <v>408</v>
+        <v>402</v>
       </c>
     </row>
     <row r="5" spans="1:16">
       <c r="B5" t="s">
-        <v>409</v>
+        <v>403</v>
       </c>
       <c r="C5">
         <v>40</v>
       </c>
       <c r="D5" t="s">
-        <v>410</v>
+        <v>404</v>
       </c>
       <c r="E5" t="s">
-        <v>411</v>
+        <v>405</v>
       </c>
     </row>
     <row r="6" spans="1:16">
       <c r="B6" t="s">
-        <v>412</v>
+        <v>406</v>
       </c>
       <c r="C6">
         <v>50</v>
@@ -6871,26 +7475,26 @@
         <v>132</v>
       </c>
       <c r="E6" t="s">
-        <v>413</v>
+        <v>407</v>
       </c>
     </row>
     <row r="7" spans="1:16">
       <c r="B7" t="s">
-        <v>414</v>
+        <v>408</v>
       </c>
       <c r="C7">
         <v>50</v>
       </c>
       <c r="D7" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="E7" t="s">
-        <v>408</v>
+        <v>402</v>
       </c>
     </row>
     <row r="8" spans="1:16">
       <c r="B8" t="s">
-        <v>415</v>
+        <v>409</v>
       </c>
       <c r="C8">
         <v>65</v>
@@ -6899,12 +7503,12 @@
         <v>131</v>
       </c>
       <c r="E8" t="s">
-        <v>408</v>
+        <v>402</v>
       </c>
     </row>
     <row r="9" spans="1:16">
       <c r="B9" t="s">
-        <v>416</v>
+        <v>410</v>
       </c>
       <c r="C9">
         <v>80</v>
@@ -6913,46 +7517,46 @@
         <v>131</v>
       </c>
       <c r="E9" t="s">
-        <v>408</v>
+        <v>402</v>
       </c>
     </row>
     <row r="10" spans="1:16">
       <c r="A10" t="s">
-        <v>417</v>
+        <v>411</v>
       </c>
       <c r="B10" t="s">
-        <v>418</v>
+        <v>412</v>
       </c>
       <c r="C10">
         <v>25</v>
       </c>
       <c r="D10" t="s">
-        <v>419</v>
+        <v>413</v>
       </c>
       <c r="E10" t="s">
-        <v>420</v>
+        <v>414</v>
       </c>
     </row>
     <row r="11" spans="1:16">
       <c r="B11" t="s">
-        <v>421</v>
+        <v>415</v>
       </c>
       <c r="C11">
         <v>50</v>
       </c>
       <c r="D11" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="E11" t="s">
-        <v>422</v>
+        <v>416</v>
       </c>
     </row>
     <row r="12" spans="1:16">
       <c r="A12" t="s">
-        <v>423</v>
+        <v>417</v>
       </c>
       <c r="B12" t="s">
-        <v>424</v>
+        <v>418</v>
       </c>
       <c r="C12">
         <v>60</v>
@@ -6961,86 +7565,86 @@
         <v>130</v>
       </c>
       <c r="E12" t="s">
-        <v>422</v>
+        <v>416</v>
       </c>
     </row>
     <row r="13" spans="1:16">
       <c r="A13" t="s">
-        <v>425</v>
+        <v>419</v>
       </c>
       <c r="B13" t="s">
-        <v>426</v>
+        <v>420</v>
       </c>
       <c r="C13">
         <v>65</v>
       </c>
       <c r="D13" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="E13" t="s">
-        <v>422</v>
+        <v>416</v>
       </c>
     </row>
     <row r="14" spans="1:16">
       <c r="A14" t="s">
-        <v>428</v>
+        <v>422</v>
       </c>
       <c r="B14" t="s">
-        <v>429</v>
+        <v>423</v>
       </c>
       <c r="C14">
         <v>90</v>
       </c>
       <c r="D14" t="s">
-        <v>430</v>
+        <v>424</v>
       </c>
       <c r="E14" t="s">
-        <v>422</v>
+        <v>416</v>
       </c>
     </row>
     <row r="15" spans="1:16">
       <c r="A15" t="s">
-        <v>433</v>
+        <v>427</v>
       </c>
       <c r="B15" t="s">
-        <v>431</v>
+        <v>425</v>
       </c>
       <c r="C15">
         <v>1.5</v>
       </c>
       <c r="D15" t="s">
-        <v>432</v>
+        <v>426</v>
       </c>
       <c r="E15" t="s">
-        <v>413</v>
+        <v>407</v>
       </c>
     </row>
     <row r="16" spans="1:16">
       <c r="B16" t="s">
-        <v>434</v>
+        <v>428</v>
       </c>
       <c r="C16">
         <v>3</v>
       </c>
       <c r="D16" t="s">
-        <v>432</v>
+        <v>426</v>
       </c>
       <c r="E16" t="s">
-        <v>411</v>
+        <v>405</v>
       </c>
     </row>
     <row r="17" spans="2:5">
       <c r="B17" t="s">
-        <v>435</v>
+        <v>429</v>
       </c>
       <c r="C17">
         <v>10</v>
       </c>
       <c r="D17" t="s">
-        <v>436</v>
+        <v>430</v>
       </c>
       <c r="E17" t="s">
-        <v>411</v>
+        <v>405</v>
       </c>
     </row>
   </sheetData>
@@ -7050,36 +7654,36 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B4614B8F-CA9A-402E-B293-C8FF103E111E}">
-  <dimension ref="A1:G69"/>
+  <dimension ref="A1:G66"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="32.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="32.42578125" customWidth="1"/>
-    <col min="4" max="4" width="50.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="54.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="108.42578125" style="25" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="61.28515625" style="25" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="32.42578125" hidden="1" customWidth="1"/>
+    <col min="4" max="4" width="50.85546875" hidden="1" customWidth="1"/>
+    <col min="5" max="5" width="54.5703125" style="24" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="108.42578125" style="35" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="70.85546875" style="35" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" s="21" t="s">
-        <v>250</v>
+        <v>438</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="E1" t="s">
-        <v>305</v>
-      </c>
-      <c r="F1" s="26" t="s">
-        <v>304</v>
-      </c>
-      <c r="G1" s="26" t="s">
-        <v>311</v>
+      <c r="E1" s="24" t="s">
+        <v>301</v>
+      </c>
+      <c r="F1" s="33" t="s">
+        <v>300</v>
+      </c>
+      <c r="G1" s="33" t="s">
+        <v>307</v>
       </c>
     </row>
     <row r="2" spans="1:7">
@@ -7089,216 +7693,216 @@
       <c r="B2" s="28"/>
       <c r="C2" s="28"/>
       <c r="D2" s="28"/>
-      <c r="E2" s="29"/>
-      <c r="F2" s="29"/>
-      <c r="G2" s="29"/>
+      <c r="E2" s="37"/>
+      <c r="F2" s="34"/>
+      <c r="G2" s="34"/>
     </row>
     <row r="3" spans="1:7">
       <c r="B3" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="C3" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
       <c r="D3" t="s">
-        <v>330</v>
-      </c>
-      <c r="E3" s="25" t="s">
+        <v>326</v>
+      </c>
+      <c r="E3" s="38" t="s">
+        <v>312</v>
+      </c>
+      <c r="F3" s="27" t="s">
         <v>316</v>
       </c>
-      <c r="F3" s="27" t="s">
-        <v>320</v>
-      </c>
-      <c r="G3" s="25" t="s">
-        <v>312</v>
+      <c r="G3" s="35" t="s">
+        <v>308</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="B4" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="C4" t="s">
-        <v>337</v>
+        <v>333</v>
       </c>
       <c r="D4" t="s">
-        <v>331</v>
-      </c>
-      <c r="E4" s="25" t="s">
-        <v>317</v>
-      </c>
-      <c r="F4" s="25" t="s">
-        <v>309</v>
-      </c>
-      <c r="G4" s="25" t="s">
-        <v>312</v>
+        <v>327</v>
+      </c>
+      <c r="E4" s="38" t="s">
+        <v>313</v>
+      </c>
+      <c r="F4" s="35" t="s">
+        <v>305</v>
+      </c>
+      <c r="G4" s="35" t="s">
+        <v>308</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="B5" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="C5" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="D5" t="s">
-        <v>332</v>
-      </c>
-      <c r="E5" s="25" t="s">
-        <v>318</v>
-      </c>
-      <c r="F5" s="25" t="s">
-        <v>307</v>
-      </c>
-      <c r="G5" s="25" t="s">
-        <v>312</v>
+        <v>328</v>
+      </c>
+      <c r="E5" s="38" t="s">
+        <v>314</v>
+      </c>
+      <c r="F5" s="35" t="s">
+        <v>303</v>
+      </c>
+      <c r="G5" s="35" t="s">
+        <v>308</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="B6" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="C6" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="D6" t="s">
-        <v>333</v>
-      </c>
-      <c r="E6" s="25" t="s">
-        <v>319</v>
-      </c>
-      <c r="F6" s="25" t="s">
+        <v>329</v>
+      </c>
+      <c r="E6" s="38" t="s">
+        <v>315</v>
+      </c>
+      <c r="F6" s="35" t="s">
+        <v>304</v>
+      </c>
+      <c r="G6" s="35" t="s">
         <v>308</v>
-      </c>
-      <c r="G6" s="25" t="s">
-        <v>312</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7" s="28" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="B7" s="28"/>
       <c r="C7" s="28"/>
       <c r="D7" s="28"/>
-      <c r="E7" s="29"/>
-      <c r="F7" s="29"/>
-      <c r="G7" s="29"/>
+      <c r="E7" s="37"/>
+      <c r="F7" s="34"/>
+      <c r="G7" s="34"/>
     </row>
     <row r="8" spans="1:7">
       <c r="B8" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="C8" t="s">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="D8" t="s">
-        <v>334</v>
-      </c>
-      <c r="E8" s="25" t="s">
-        <v>312</v>
-      </c>
-      <c r="F8" s="25" t="s">
-        <v>314</v>
-      </c>
-      <c r="G8" s="25" t="s">
-        <v>313</v>
+        <v>330</v>
+      </c>
+      <c r="E8" s="38" t="s">
+        <v>308</v>
+      </c>
+      <c r="F8" s="35" t="s">
+        <v>310</v>
+      </c>
+      <c r="G8" s="35" t="s">
+        <v>309</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="B9" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="C9" t="s">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="D9" t="s">
-        <v>334</v>
-      </c>
-      <c r="E9" s="25" t="s">
-        <v>312</v>
-      </c>
-      <c r="F9" s="25" t="s">
-        <v>315</v>
-      </c>
-      <c r="G9" s="25" t="s">
-        <v>313</v>
+        <v>330</v>
+      </c>
+      <c r="E9" s="38" t="s">
+        <v>308</v>
+      </c>
+      <c r="F9" s="35" t="s">
+        <v>311</v>
+      </c>
+      <c r="G9" s="35" t="s">
+        <v>309</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="B10" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="C10" t="s">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="D10" t="s">
-        <v>340</v>
-      </c>
-      <c r="E10" s="25" t="s">
-        <v>306</v>
-      </c>
-      <c r="F10" s="30" t="s">
-        <v>321</v>
-      </c>
-      <c r="G10" t="s">
-        <v>327</v>
+        <v>336</v>
+      </c>
+      <c r="E10" s="38" t="s">
+        <v>302</v>
+      </c>
+      <c r="F10" s="36" t="s">
+        <v>317</v>
+      </c>
+      <c r="G10" s="14" t="s">
+        <v>323</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="B11" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="C11" t="s">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="D11" t="s">
-        <v>335</v>
-      </c>
-      <c r="E11" s="25" t="s">
-        <v>310</v>
-      </c>
-      <c r="F11" s="25" t="s">
+        <v>331</v>
+      </c>
+      <c r="E11" s="38" t="s">
+        <v>306</v>
+      </c>
+      <c r="F11" s="35" t="s">
+        <v>318</v>
+      </c>
+      <c r="G11" s="14" t="s">
         <v>322</v>
-      </c>
-      <c r="G11" t="s">
-        <v>326</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="B12" t="s">
-        <v>402</v>
+        <v>471</v>
       </c>
       <c r="C12" t="s">
-        <v>339</v>
-      </c>
-      <c r="E12" s="25" t="s">
-        <v>350</v>
-      </c>
-      <c r="F12" s="30" t="s">
-        <v>323</v>
-      </c>
-      <c r="G12" s="25" t="s">
-        <v>312</v>
+        <v>335</v>
+      </c>
+      <c r="E12" s="38" t="s">
+        <v>345</v>
+      </c>
+      <c r="F12" s="36" t="s">
+        <v>319</v>
+      </c>
+      <c r="G12" s="35" t="s">
+        <v>308</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="B13" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="C13" t="s">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="D13" t="s">
-        <v>342</v>
-      </c>
-      <c r="E13" s="25" t="s">
-        <v>310</v>
-      </c>
-      <c r="F13" s="30" t="s">
-        <v>324</v>
-      </c>
-      <c r="G13" t="s">
-        <v>325</v>
+        <v>338</v>
+      </c>
+      <c r="E13" s="38" t="s">
+        <v>306</v>
+      </c>
+      <c r="F13" s="36" t="s">
+        <v>320</v>
+      </c>
+      <c r="G13" s="14" t="s">
+        <v>321</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -7308,239 +7912,239 @@
       <c r="B14" s="28"/>
       <c r="C14" s="28"/>
       <c r="D14" s="28"/>
-      <c r="E14" s="29"/>
-      <c r="F14" s="29"/>
-      <c r="G14" s="29"/>
-    </row>
-    <row r="15" spans="1:7">
+      <c r="E14" s="37"/>
+      <c r="F14" s="34"/>
+      <c r="G14" s="34"/>
+    </row>
+    <row r="15" spans="1:7" ht="30">
       <c r="B15" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="C15" t="s">
-        <v>345</v>
-      </c>
-      <c r="D15" s="27" t="s">
-        <v>354</v>
-      </c>
-      <c r="E15" s="25" t="s">
-        <v>348</v>
-      </c>
-      <c r="F15" s="25" t="s">
-        <v>356</v>
-      </c>
-      <c r="G15" s="25" t="s">
+        <v>340</v>
+      </c>
+      <c r="D15" s="26" t="s">
+        <v>349</v>
+      </c>
+      <c r="E15" s="38" t="s">
         <v>343</v>
       </c>
-    </row>
-    <row r="16" spans="1:7">
+      <c r="F15" s="35" t="s">
+        <v>351</v>
+      </c>
+      <c r="G15" s="35" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="30">
       <c r="B16" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="C16" t="s">
-        <v>345</v>
-      </c>
-      <c r="D16" s="27" t="s">
-        <v>355</v>
-      </c>
-      <c r="E16" s="25" t="s">
-        <v>348</v>
-      </c>
-      <c r="F16" s="25" t="s">
-        <v>357</v>
-      </c>
-      <c r="G16" s="25" t="s">
+        <v>340</v>
+      </c>
+      <c r="D16" s="26" t="s">
+        <v>350</v>
+      </c>
+      <c r="E16" s="38" t="s">
         <v>343</v>
+      </c>
+      <c r="F16" s="35" t="s">
+        <v>352</v>
+      </c>
+      <c r="G16" s="35" t="s">
+        <v>449</v>
       </c>
     </row>
     <row r="17" spans="1:7">
       <c r="B17" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="C17" t="s">
-        <v>345</v>
+        <v>340</v>
       </c>
       <c r="D17" t="s">
+        <v>342</v>
+      </c>
+      <c r="E17" s="24" t="s">
+        <v>346</v>
+      </c>
+      <c r="F17" s="35" t="s">
+        <v>348</v>
+      </c>
+      <c r="G17" s="35" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="30">
+      <c r="B18" t="s">
+        <v>291</v>
+      </c>
+      <c r="C18" t="s">
+        <v>340</v>
+      </c>
+      <c r="D18" s="26" t="s">
         <v>347</v>
       </c>
-      <c r="E17" t="s">
-        <v>351</v>
-      </c>
-      <c r="F17" s="25" t="s">
-        <v>353</v>
-      </c>
-      <c r="G17" s="25" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="B18" t="s">
-        <v>293</v>
-      </c>
-      <c r="C18" t="s">
-        <v>345</v>
-      </c>
-      <c r="D18" s="27" t="s">
-        <v>352</v>
-      </c>
-      <c r="E18" s="25" t="s">
-        <v>348</v>
-      </c>
-      <c r="F18" s="25" t="s">
-        <v>373</v>
-      </c>
-      <c r="G18" s="25" t="s">
-        <v>312</v>
+      <c r="E18" s="38" t="s">
+        <v>343</v>
+      </c>
+      <c r="F18" s="35" t="s">
+        <v>368</v>
+      </c>
+      <c r="G18" s="35" t="s">
+        <v>308</v>
       </c>
     </row>
     <row r="19" spans="1:7">
       <c r="B19" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="C19" t="s">
-        <v>345</v>
+        <v>340</v>
       </c>
       <c r="D19" t="s">
-        <v>349</v>
-      </c>
-      <c r="E19" s="25" t="s">
-        <v>348</v>
-      </c>
-      <c r="F19" s="25" t="s">
-        <v>358</v>
-      </c>
-      <c r="G19" s="25" t="s">
-        <v>359</v>
+        <v>344</v>
+      </c>
+      <c r="E19" s="38" t="s">
+        <v>343</v>
+      </c>
+      <c r="F19" s="35" t="s">
+        <v>353</v>
+      </c>
+      <c r="G19" s="35" t="s">
+        <v>354</v>
       </c>
     </row>
     <row r="20" spans="1:7">
       <c r="A20" s="28" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="B20" s="28"/>
       <c r="C20" s="28"/>
       <c r="D20" s="28"/>
-      <c r="E20" s="29"/>
-      <c r="F20" s="29"/>
-      <c r="G20" s="29"/>
-    </row>
-    <row r="21" spans="1:7">
+      <c r="E20" s="37"/>
+      <c r="F20" s="34"/>
+      <c r="G20" s="34"/>
+    </row>
+    <row r="21" spans="1:7" ht="45">
       <c r="B21" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="C21" t="s">
-        <v>346</v>
-      </c>
-      <c r="D21" s="27" t="s">
+        <v>341</v>
+      </c>
+      <c r="D21" s="26" t="s">
+        <v>355</v>
+      </c>
+      <c r="E21" s="38" t="s">
+        <v>369</v>
+      </c>
+      <c r="F21" s="35" t="s">
+        <v>359</v>
+      </c>
+      <c r="G21" s="35" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="30">
+      <c r="B22" t="s">
+        <v>292</v>
+      </c>
+      <c r="C22" t="s">
+        <v>341</v>
+      </c>
+      <c r="D22" s="26" t="s">
+        <v>356</v>
+      </c>
+      <c r="E22" s="38" t="s">
+        <v>369</v>
+      </c>
+      <c r="F22" s="35" t="s">
         <v>360</v>
       </c>
-      <c r="E21" s="25" t="s">
-        <v>374</v>
-      </c>
-      <c r="F21" s="25" t="s">
+      <c r="G22" s="35" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" ht="30">
+      <c r="B23" t="s">
+        <v>276</v>
+      </c>
+      <c r="C23" t="s">
+        <v>341</v>
+      </c>
+      <c r="D23" s="26" t="s">
+        <v>357</v>
+      </c>
+      <c r="E23" s="38" t="s">
+        <v>370</v>
+      </c>
+      <c r="F23" s="35" t="s">
+        <v>362</v>
+      </c>
+      <c r="G23" s="35" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="30">
+      <c r="B24" t="s">
+        <v>294</v>
+      </c>
+      <c r="C24" t="s">
+        <v>341</v>
+      </c>
+      <c r="D24" s="26" t="s">
+        <v>358</v>
+      </c>
+      <c r="E24" s="38" t="s">
+        <v>371</v>
+      </c>
+      <c r="F24" s="35" t="s">
+        <v>363</v>
+      </c>
+      <c r="G24" s="35" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="30">
+      <c r="B25" t="s">
+        <v>280</v>
+      </c>
+      <c r="C25" t="s">
+        <v>341</v>
+      </c>
+      <c r="D25" s="26" t="s">
+        <v>366</v>
+      </c>
+      <c r="E25" s="24" t="s">
+        <v>372</v>
+      </c>
+      <c r="F25" s="35" t="s">
         <v>364</v>
       </c>
-      <c r="G21" s="25" t="s">
-        <v>343</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7">
-      <c r="B22" t="s">
-        <v>294</v>
-      </c>
-      <c r="C22" t="s">
-        <v>346</v>
-      </c>
-      <c r="D22" s="27" t="s">
-        <v>361</v>
-      </c>
-      <c r="E22" s="25" t="s">
-        <v>374</v>
-      </c>
-      <c r="F22" s="25" t="s">
-        <v>365</v>
-      </c>
-      <c r="G22" s="25" t="s">
-        <v>366</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7">
-      <c r="B23" t="s">
-        <v>278</v>
-      </c>
-      <c r="C23" t="s">
-        <v>346</v>
-      </c>
-      <c r="D23" s="27" t="s">
-        <v>362</v>
-      </c>
-      <c r="E23" s="25" t="s">
-        <v>375</v>
-      </c>
-      <c r="F23" s="25" t="s">
-        <v>367</v>
-      </c>
-      <c r="G23" s="25" t="s">
-        <v>366</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7">
-      <c r="B24" t="s">
-        <v>296</v>
-      </c>
-      <c r="C24" t="s">
-        <v>346</v>
-      </c>
-      <c r="D24" s="27" t="s">
-        <v>363</v>
-      </c>
-      <c r="E24" s="25" t="s">
-        <v>376</v>
-      </c>
-      <c r="F24" s="25" t="s">
-        <v>368</v>
-      </c>
-      <c r="G24" s="25" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7">
-      <c r="B25" t="s">
-        <v>283</v>
-      </c>
-      <c r="C25" t="s">
-        <v>346</v>
-      </c>
-      <c r="D25" s="27" t="s">
-        <v>371</v>
-      </c>
-      <c r="E25" t="s">
-        <v>377</v>
-      </c>
-      <c r="F25" s="25" t="s">
-        <v>369</v>
-      </c>
-      <c r="G25" s="25" t="s">
-        <v>312</v>
+      <c r="G25" s="35" t="s">
+        <v>308</v>
       </c>
     </row>
     <row r="26" spans="1:7">
       <c r="B26" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="C26" t="s">
-        <v>346</v>
-      </c>
-      <c r="D26" s="27" t="s">
-        <v>370</v>
-      </c>
-      <c r="E26" s="25" t="s">
-        <v>378</v>
-      </c>
-      <c r="F26" s="25" t="s">
-        <v>372</v>
-      </c>
-      <c r="G26" s="25" t="s">
-        <v>344</v>
+        <v>341</v>
+      </c>
+      <c r="D26" s="26" t="s">
+        <v>365</v>
+      </c>
+      <c r="E26" s="38" t="s">
+        <v>373</v>
+      </c>
+      <c r="F26" s="35" t="s">
+        <v>367</v>
+      </c>
+      <c r="G26" s="35" t="s">
+        <v>339</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -7550,317 +8154,527 @@
       <c r="B27" s="28"/>
       <c r="C27" s="28"/>
       <c r="D27" s="28"/>
-      <c r="E27" s="29"/>
-      <c r="F27" s="29"/>
-      <c r="G27" s="29"/>
-    </row>
-    <row r="28" spans="1:7">
+      <c r="E27" s="37"/>
+      <c r="F27" s="34"/>
+      <c r="G27" s="34"/>
+    </row>
+    <row r="28" spans="1:7" ht="30">
       <c r="B28" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="C28" t="s">
-        <v>399</v>
-      </c>
-      <c r="D28" s="27" t="s">
-        <v>382</v>
-      </c>
-      <c r="E28" t="s">
-        <v>380</v>
-      </c>
-      <c r="F28" s="25" t="s">
-        <v>386</v>
-      </c>
-      <c r="G28" t="s">
+        <v>394</v>
+      </c>
+      <c r="D28" s="26" t="s">
+        <v>377</v>
+      </c>
+      <c r="E28" s="24" t="s">
+        <v>375</v>
+      </c>
+      <c r="F28" s="35" t="s">
         <v>381</v>
+      </c>
+      <c r="G28" s="14" t="s">
+        <v>376</v>
       </c>
     </row>
     <row r="29" spans="1:7">
       <c r="B29" t="s">
+        <v>374</v>
+      </c>
+      <c r="C29" t="s">
+        <v>394</v>
+      </c>
+      <c r="D29" s="26" t="s">
+        <v>378</v>
+      </c>
+      <c r="E29" s="24" t="s">
         <v>379</v>
       </c>
-      <c r="C29" t="s">
-        <v>399</v>
-      </c>
-      <c r="D29" s="27" t="s">
-        <v>383</v>
-      </c>
-      <c r="E29" t="s">
-        <v>384</v>
-      </c>
-      <c r="F29" s="25" t="s">
-        <v>385</v>
-      </c>
-      <c r="G29" s="25" t="s">
-        <v>312</v>
+      <c r="F29" s="35" t="s">
+        <v>380</v>
+      </c>
+      <c r="G29" s="35" t="s">
+        <v>308</v>
       </c>
     </row>
     <row r="30" spans="1:7">
       <c r="A30" s="28" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="B30" s="28"/>
       <c r="C30" s="28"/>
       <c r="D30" s="28"/>
-      <c r="E30" s="29"/>
-      <c r="F30" s="29"/>
-      <c r="G30" s="29"/>
-    </row>
-    <row r="31" spans="1:7">
+      <c r="E30" s="37"/>
+      <c r="F30" s="34"/>
+      <c r="G30" s="34"/>
+    </row>
+    <row r="31" spans="1:7" ht="30">
       <c r="B31" t="s">
+        <v>387</v>
+      </c>
+      <c r="C31" t="s">
+        <v>395</v>
+      </c>
+      <c r="D31" s="26" t="s">
+        <v>382</v>
+      </c>
+      <c r="E31" s="24" t="s">
+        <v>385</v>
+      </c>
+      <c r="F31" s="35" t="s">
         <v>392</v>
       </c>
-      <c r="C31" t="s">
-        <v>400</v>
-      </c>
-      <c r="D31" s="27" t="s">
-        <v>387</v>
-      </c>
-      <c r="E31" t="s">
+      <c r="G31" s="14" t="s">
         <v>390</v>
-      </c>
-      <c r="F31" s="25" t="s">
-        <v>397</v>
-      </c>
-      <c r="G31" t="s">
-        <v>395</v>
       </c>
     </row>
     <row r="32" spans="1:7">
       <c r="B32" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="C32" t="s">
-        <v>400</v>
-      </c>
-      <c r="D32" s="27" t="s">
+        <v>395</v>
+      </c>
+      <c r="D32" s="26" t="s">
+        <v>384</v>
+      </c>
+      <c r="E32" s="24" t="s">
+        <v>385</v>
+      </c>
+      <c r="F32" s="35" t="s">
+        <v>388</v>
+      </c>
+      <c r="G32" s="14" t="s">
         <v>389</v>
       </c>
-      <c r="E32" t="s">
-        <v>390</v>
-      </c>
-      <c r="F32" s="25" t="s">
+    </row>
+    <row r="33" spans="1:7" ht="45">
+      <c r="B33" t="s">
+        <v>287</v>
+      </c>
+      <c r="C33" t="s">
+        <v>396</v>
+      </c>
+      <c r="D33" s="26" t="s">
+        <v>383</v>
+      </c>
+      <c r="E33" s="24" t="s">
+        <v>386</v>
+      </c>
+      <c r="F33" s="36" t="s">
         <v>393</v>
       </c>
-      <c r="G32" t="s">
-        <v>394</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7">
-      <c r="B33" t="s">
-        <v>289</v>
-      </c>
-      <c r="C33" t="s">
-        <v>401</v>
-      </c>
-      <c r="D33" s="27" t="s">
-        <v>388</v>
-      </c>
-      <c r="E33" t="s">
+      <c r="G33" s="14" t="s">
         <v>391</v>
-      </c>
-      <c r="F33" s="30" t="s">
-        <v>398</v>
-      </c>
-      <c r="G33" t="s">
-        <v>396</v>
       </c>
     </row>
     <row r="34" spans="1:7">
       <c r="A34" s="28" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="B34" s="28"/>
       <c r="C34" s="28"/>
       <c r="D34" s="28"/>
-      <c r="E34" s="29"/>
-      <c r="F34" s="29"/>
-      <c r="G34" s="29"/>
-    </row>
-    <row r="35" spans="1:7">
+      <c r="E34" s="37"/>
+      <c r="F34" s="34"/>
+      <c r="G34" s="34"/>
+    </row>
+    <row r="35" spans="1:7" ht="30">
       <c r="B35" t="s">
-        <v>261</v>
-      </c>
-      <c r="E35" s="25"/>
-    </row>
-    <row r="36" spans="1:7">
+        <v>259</v>
+      </c>
+      <c r="D35" s="26" t="s">
+        <v>491</v>
+      </c>
+      <c r="E35" s="38" t="s">
+        <v>489</v>
+      </c>
+      <c r="F35" s="14" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" ht="45">
       <c r="B36" t="s">
-        <v>297</v>
-      </c>
-      <c r="E36" s="25"/>
-    </row>
-    <row r="37" spans="1:7">
+        <v>443</v>
+      </c>
+      <c r="D36" s="26" t="s">
+        <v>492</v>
+      </c>
+      <c r="E36" s="38" t="s">
+        <v>488</v>
+      </c>
+      <c r="F36" s="14" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" ht="30">
       <c r="B37" t="s">
-        <v>292</v>
-      </c>
-      <c r="E37" s="25"/>
+        <v>290</v>
+      </c>
+      <c r="D37" s="26" t="s">
+        <v>493</v>
+      </c>
+      <c r="E37" s="38"/>
+      <c r="F37" s="35" t="s">
+        <v>495</v>
+      </c>
+      <c r="G37" s="24" t="s">
+        <v>494</v>
+      </c>
     </row>
     <row r="38" spans="1:7">
       <c r="A38" s="28" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="B38" s="28"/>
       <c r="C38" s="28"/>
       <c r="D38" s="28"/>
-      <c r="E38" s="29"/>
-      <c r="F38" s="29"/>
-      <c r="G38" s="29"/>
-    </row>
-    <row r="39" spans="1:7">
+      <c r="E38" s="37"/>
+      <c r="F38" s="34"/>
+      <c r="G38" s="34"/>
+    </row>
+    <row r="39" spans="1:7" ht="30">
       <c r="B39" t="s">
-        <v>266</v>
-      </c>
-      <c r="E39" s="25"/>
-    </row>
-    <row r="40" spans="1:7">
+        <v>264</v>
+      </c>
+      <c r="D39" t="s">
+        <v>479</v>
+      </c>
+      <c r="E39" s="24" t="s">
+        <v>450</v>
+      </c>
+      <c r="F39" s="14" t="s">
+        <v>452</v>
+      </c>
+      <c r="G39" s="14" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" ht="30">
       <c r="B40" t="s">
+        <v>265</v>
+      </c>
+      <c r="D40" t="s">
+        <v>463</v>
+      </c>
+      <c r="E40" s="38"/>
+      <c r="F40" s="27" t="s">
+        <v>453</v>
+      </c>
+      <c r="G40" s="35" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" ht="30">
+      <c r="B41" t="s">
         <v>267</v>
       </c>
-      <c r="E40" s="25"/>
-    </row>
-    <row r="41" spans="1:7">
-      <c r="B41" t="s">
-        <v>269</v>
-      </c>
-      <c r="E41" s="25"/>
+      <c r="D41" t="s">
+        <v>463</v>
+      </c>
+      <c r="E41" s="38"/>
+      <c r="F41" s="27" t="s">
+        <v>454</v>
+      </c>
+      <c r="G41" s="35" t="s">
+        <v>308</v>
+      </c>
     </row>
     <row r="42" spans="1:7">
       <c r="B42" t="s">
-        <v>281</v>
-      </c>
-      <c r="E42" s="25"/>
+        <v>442</v>
+      </c>
+      <c r="D42" t="s">
+        <v>462</v>
+      </c>
+      <c r="E42" s="38"/>
+      <c r="F42" s="14" t="s">
+        <v>455</v>
+      </c>
+      <c r="G42" s="35" t="s">
+        <v>308</v>
+      </c>
     </row>
     <row r="43" spans="1:7">
       <c r="B43" t="s">
-        <v>285</v>
-      </c>
-      <c r="E43" s="25"/>
+        <v>283</v>
+      </c>
+      <c r="D43" t="s">
+        <v>461</v>
+      </c>
+      <c r="E43" s="38"/>
+      <c r="F43" s="35" t="s">
+        <v>433</v>
+      </c>
+      <c r="G43" s="35" t="s">
+        <v>458</v>
+      </c>
     </row>
     <row r="44" spans="1:7">
       <c r="B44" t="s">
-        <v>300</v>
-      </c>
-      <c r="E44" s="25"/>
-    </row>
-    <row r="45" spans="1:7">
+        <v>282</v>
+      </c>
+      <c r="D44" t="s">
+        <v>460</v>
+      </c>
+      <c r="E44" s="38"/>
+      <c r="F44" s="35" t="s">
+        <v>434</v>
+      </c>
+      <c r="G44" s="35" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" ht="30">
       <c r="B45" t="s">
-        <v>303</v>
-      </c>
-      <c r="E45" s="25"/>
-    </row>
-    <row r="46" spans="1:7">
+        <v>296</v>
+      </c>
+      <c r="D45" t="s">
+        <v>459</v>
+      </c>
+      <c r="E45" s="24" t="s">
+        <v>457</v>
+      </c>
+      <c r="F45" s="35" t="s">
+        <v>435</v>
+      </c>
+      <c r="G45" s="15" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" ht="30">
       <c r="B46" t="s">
-        <v>298</v>
-      </c>
-      <c r="E46" s="25"/>
-    </row>
-    <row r="47" spans="1:7">
+        <v>299</v>
+      </c>
+      <c r="D46" t="s">
+        <v>459</v>
+      </c>
+      <c r="E46" s="24" t="s">
+        <v>457</v>
+      </c>
+      <c r="F46" s="35" t="s">
+        <v>436</v>
+      </c>
+      <c r="G46" s="15" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" ht="30">
       <c r="B47" t="s">
-        <v>299</v>
-      </c>
-      <c r="E47" s="25"/>
+        <v>295</v>
+      </c>
+      <c r="D47" t="s">
+        <v>459</v>
+      </c>
+      <c r="E47" s="24" t="s">
+        <v>457</v>
+      </c>
+      <c r="F47" s="35" t="s">
+        <v>437</v>
+      </c>
+      <c r="G47" s="15" t="s">
+        <v>456</v>
+      </c>
     </row>
     <row r="48" spans="1:7">
-      <c r="E48" s="25"/>
-    </row>
-    <row r="49" spans="1:5">
-      <c r="A49" s="21" t="s">
+      <c r="B48" t="s">
+        <v>297</v>
+      </c>
+      <c r="D48" t="s">
+        <v>480</v>
+      </c>
+      <c r="E48" s="24" t="s">
+        <v>465</v>
+      </c>
+      <c r="F48" s="35" t="s">
+        <v>469</v>
+      </c>
+      <c r="G48" s="35" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7">
+      <c r="A49" s="32" t="s">
+        <v>255</v>
+      </c>
+      <c r="B49" s="28"/>
+      <c r="C49" s="28"/>
+      <c r="D49" s="28"/>
+      <c r="E49" s="37"/>
+      <c r="F49" s="34"/>
+      <c r="G49" s="34"/>
+    </row>
+    <row r="50" spans="1:7">
+      <c r="B50" t="s">
+        <v>274</v>
+      </c>
+      <c r="D50" s="25"/>
+      <c r="E50" s="24" t="s">
+        <v>484</v>
+      </c>
+      <c r="F50" s="35" t="s">
+        <v>485</v>
+      </c>
+      <c r="G50" s="35" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" ht="30">
+      <c r="B51" t="s">
+        <v>275</v>
+      </c>
+      <c r="D51" s="25" t="s">
+        <v>479</v>
+      </c>
+      <c r="E51" s="24" t="s">
+        <v>486</v>
+      </c>
+      <c r="F51" s="35" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7">
+      <c r="B52" t="s">
+        <v>281</v>
+      </c>
+      <c r="D52" s="25" t="s">
+        <v>479</v>
+      </c>
+      <c r="E52" s="24" t="s">
+        <v>464</v>
+      </c>
+      <c r="F52" s="35" t="s">
+        <v>481</v>
+      </c>
+      <c r="G52" s="35" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7">
+      <c r="B53" t="s">
+        <v>266</v>
+      </c>
+      <c r="D53" s="25" t="s">
+        <v>479</v>
+      </c>
+      <c r="E53" s="24" t="s">
+        <v>468</v>
+      </c>
+      <c r="F53" s="35" t="s">
+        <v>466</v>
+      </c>
+      <c r="G53" s="35" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" ht="30">
+      <c r="B54" t="s">
+        <v>289</v>
+      </c>
+      <c r="D54" s="25"/>
+      <c r="E54" s="24" t="s">
+        <v>475</v>
+      </c>
+      <c r="F54" s="35" t="s">
+        <v>472</v>
+      </c>
+      <c r="G54" s="35" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7">
+      <c r="B55" t="s">
+        <v>441</v>
+      </c>
+      <c r="E55" s="24" t="s">
+        <v>474</v>
+      </c>
+      <c r="F55" s="35" t="s">
+        <v>432</v>
+      </c>
+      <c r="G55" s="35" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7">
+      <c r="B56" t="s">
+        <v>439</v>
+      </c>
+      <c r="D56" s="25"/>
+      <c r="E56" s="24" t="s">
+        <v>477</v>
+      </c>
+      <c r="F56" s="35" t="s">
+        <v>444</v>
+      </c>
+      <c r="G56" s="35" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7">
+      <c r="B57" t="s">
+        <v>440</v>
+      </c>
+      <c r="E57" s="24" t="s">
+        <v>478</v>
+      </c>
+      <c r="F57" s="35" t="s">
+        <v>444</v>
+      </c>
+      <c r="G57" s="35" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7">
+      <c r="D58" s="25"/>
+      <c r="E58" s="38"/>
+    </row>
+    <row r="59" spans="1:7">
+      <c r="D59" s="25"/>
+      <c r="E59" s="38"/>
+    </row>
+    <row r="60" spans="1:7">
+      <c r="E60" s="38"/>
+    </row>
+    <row r="61" spans="1:7">
+      <c r="A61" s="21" t="s">
+        <v>431</v>
+      </c>
+      <c r="E61" s="38"/>
+    </row>
+    <row r="62" spans="1:7">
+      <c r="B62" t="s">
+        <v>250</v>
+      </c>
+      <c r="F62" s="14"/>
+    </row>
+    <row r="63" spans="1:7">
+      <c r="B63" t="s">
         <v>251</v>
       </c>
-      <c r="E49" s="25"/>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="A50" t="s">
+      <c r="E63" s="38"/>
+    </row>
+    <row r="64" spans="1:7">
+      <c r="B64" t="s">
         <v>252</v>
       </c>
-      <c r="E50" s="25"/>
-    </row>
-    <row r="51" spans="1:5">
-      <c r="A51" t="s">
+      <c r="E64" s="38"/>
+    </row>
+    <row r="65" spans="2:5">
+      <c r="B65" t="s">
         <v>253</v>
       </c>
-      <c r="E51" s="25"/>
-    </row>
-    <row r="52" spans="1:5">
-      <c r="A52" t="s">
+      <c r="E65" s="38"/>
+    </row>
+    <row r="66" spans="2:5">
+      <c r="B66" t="s">
         <v>254</v>
       </c>
-      <c r="E52" s="25"/>
-    </row>
-    <row r="53" spans="1:5">
-      <c r="A53" t="s">
-        <v>255</v>
-      </c>
-      <c r="E53" s="25"/>
-    </row>
-    <row r="54" spans="1:5">
-      <c r="A54" t="s">
-        <v>256</v>
-      </c>
-      <c r="E54" s="25"/>
-    </row>
-    <row r="55" spans="1:5">
-      <c r="E55" s="25"/>
-    </row>
-    <row r="56" spans="1:5">
-      <c r="E56" s="25"/>
-    </row>
-    <row r="57" spans="1:5">
-      <c r="E57" s="25"/>
-    </row>
-    <row r="58" spans="1:5">
-      <c r="E58" s="25"/>
-    </row>
-    <row r="59" spans="1:5">
-      <c r="E59" s="25"/>
-    </row>
-    <row r="60" spans="1:5">
-      <c r="E60" s="25"/>
-    </row>
-    <row r="61" spans="1:5">
-      <c r="E61" s="25"/>
-    </row>
-    <row r="62" spans="1:5">
-      <c r="E62" s="25"/>
-    </row>
-    <row r="63" spans="1:5">
-      <c r="A63" s="24" t="s">
-        <v>257</v>
-      </c>
-      <c r="E63" s="25"/>
-    </row>
-    <row r="64" spans="1:5">
-      <c r="A64" t="s">
-        <v>276</v>
-      </c>
-      <c r="E64" s="25"/>
-    </row>
-    <row r="65" spans="1:5">
-      <c r="A65" t="s">
-        <v>277</v>
-      </c>
-      <c r="E65" s="25"/>
-    </row>
-    <row r="66" spans="1:5">
-      <c r="A66" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5">
-      <c r="A67" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5">
-      <c r="A68" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5">
-      <c r="A69" t="s">
-        <v>301</v>
-      </c>
+      <c r="E66" s="38"/>
     </row>
   </sheetData>
+  <dataConsolidate/>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -8301,8 +9115,11 @@
       <c r="C16" s="22" t="s">
         <v>235</v>
       </c>
-    </row>
-    <row r="17" spans="1:11">
+      <c r="K16" s="14" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12">
       <c r="A17" t="s">
         <v>236</v>
       </c>
@@ -8312,8 +9129,14 @@
       <c r="C17" t="s">
         <v>245</v>
       </c>
-    </row>
-    <row r="18" spans="1:11">
+      <c r="K17" s="11" t="s">
+        <v>447</v>
+      </c>
+      <c r="L17" s="25" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12">
       <c r="A18" t="s">
         <v>237</v>
       </c>
@@ -8324,7 +9147,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="19" spans="1:11">
+    <row r="19" spans="1:12">
       <c r="B19" t="s">
         <v>241</v>
       </c>
@@ -8332,7 +9155,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="20" spans="1:11">
+    <row r="20" spans="1:12">
       <c r="A20" t="s">
         <v>240</v>
       </c>
@@ -8351,7 +9174,7 @@
       <c r="J20" s="13"/>
       <c r="K20" s="13"/>
     </row>
-    <row r="21" spans="1:11">
+    <row r="21" spans="1:12">
       <c r="B21" t="s">
         <v>241</v>
       </c>
@@ -8367,7 +9190,7 @@
       <c r="J21" s="14"/>
       <c r="K21" s="14"/>
     </row>
-    <row r="22" spans="1:11">
+    <row r="22" spans="1:12">
       <c r="D22" s="15"/>
       <c r="E22" s="15"/>
       <c r="F22" s="14"/>
@@ -8377,7 +9200,7 @@
       <c r="J22" s="14"/>
       <c r="K22" s="14"/>
     </row>
-    <row r="23" spans="1:11">
+    <row r="23" spans="1:12">
       <c r="D23" s="15"/>
       <c r="E23" s="15"/>
       <c r="F23" s="14"/>
@@ -8387,7 +9210,7 @@
       <c r="J23" s="14"/>
       <c r="K23" s="14"/>
     </row>
-    <row r="24" spans="1:11">
+    <row r="24" spans="1:12">
       <c r="D24" s="15"/>
       <c r="E24" s="15"/>
       <c r="F24" s="14"/>
@@ -8397,7 +9220,7 @@
       <c r="J24" s="14"/>
       <c r="K24" s="14"/>
     </row>
-    <row r="25" spans="1:11">
+    <row r="25" spans="1:12">
       <c r="D25" s="15"/>
       <c r="E25" s="15"/>
       <c r="F25" s="14"/>
@@ -8407,7 +9230,7 @@
       <c r="J25" s="14"/>
       <c r="K25" s="14"/>
     </row>
-    <row r="26" spans="1:11">
+    <row r="26" spans="1:12">
       <c r="D26" s="15"/>
       <c r="E26" s="15"/>
       <c r="F26" s="14"/>
@@ -8417,7 +9240,7 @@
       <c r="J26" s="14"/>
       <c r="K26" s="14"/>
     </row>
-    <row r="27" spans="1:11">
+    <row r="27" spans="1:12">
       <c r="D27" s="15"/>
       <c r="E27" s="15"/>
       <c r="F27" s="14"/>
@@ -8427,7 +9250,7 @@
       <c r="J27" s="14"/>
       <c r="K27" s="14"/>
     </row>
-    <row r="28" spans="1:11">
+    <row r="28" spans="1:12">
       <c r="D28" s="15"/>
       <c r="E28" s="15"/>
       <c r="F28" s="14"/>
@@ -8437,7 +9260,7 @@
       <c r="J28" s="14"/>
       <c r="K28" s="14"/>
     </row>
-    <row r="29" spans="1:11">
+    <row r="29" spans="1:12">
       <c r="D29" s="15"/>
       <c r="E29" s="15"/>
       <c r="F29" s="14"/>
@@ -8447,7 +9270,7 @@
       <c r="J29" s="14"/>
       <c r="K29" s="14"/>
     </row>
-    <row r="30" spans="1:11">
+    <row r="30" spans="1:12">
       <c r="D30" s="15"/>
       <c r="E30" s="15"/>
       <c r="F30" s="14"/>
@@ -8457,7 +9280,7 @@
       <c r="J30" s="14"/>
       <c r="K30" s="14"/>
     </row>
-    <row r="31" spans="1:11">
+    <row r="31" spans="1:12">
       <c r="D31" s="15"/>
       <c r="E31" s="15"/>
       <c r="F31" s="14"/>
@@ -8467,7 +9290,7 @@
       <c r="J31" s="14"/>
       <c r="K31" s="14"/>
     </row>
-    <row r="32" spans="1:11">
+    <row r="32" spans="1:12">
       <c r="D32" s="15"/>
       <c r="E32" s="15"/>
       <c r="F32" s="14"/>

--- a/docs/Mech Data.xlsx
+++ b/docs/Mech Data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\FoundryData-Dev\Data\systems\mwd\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E516EFF-50DE-4984-80EA-ABC96E607761}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D4FB945-F4DD-4396-B3F6-6A0FA50FD83B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="27240" yWindow="1050" windowWidth="23205" windowHeight="19275" activeTab="2" xr2:uid="{8D44F242-D0B2-4B9E-94CF-33F11494976A}"/>
+    <workbookView xWindow="2400" yWindow="630" windowWidth="23205" windowHeight="19275" xr2:uid="{8D44F242-D0B2-4B9E-94CF-33F11494976A}"/>
   </bookViews>
   <sheets>
     <sheet name="Mechs" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="789" uniqueCount="497">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="793" uniqueCount="501">
   <si>
     <t>Chassis</t>
   </si>
@@ -3488,6 +3488,18 @@
       </rPr>
       <t xml:space="preserve"> on visible enemies in UAV coverage. Grants +2 dice to Piloting checks to cross hazardous terrain/mine fields . Removes indirect fire penalties for operator.</t>
     </r>
+  </si>
+  <si>
+    <t>Tag Marked</t>
+  </si>
+  <si>
+    <t>Narc Attached</t>
+  </si>
+  <si>
+    <t>Blackout</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tier 3 sensor jamming </t>
   </si>
 </sst>
 </file>
@@ -3590,7 +3602,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -3638,9 +3650,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -3659,7 +3668,7 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -3679,6 +3688,12 @@
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -7356,52 +7371,52 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="15.75" thickBot="1">
-      <c r="A1" s="29" t="s">
+      <c r="A1" s="28" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="29" t="s">
+      <c r="B1" s="28" t="s">
         <v>9</v>
       </c>
-      <c r="C1" s="29" t="s">
+      <c r="C1" s="28" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="29" t="s">
+      <c r="D1" s="28" t="s">
         <v>72</v>
       </c>
-      <c r="E1" s="29" t="s">
+      <c r="E1" s="28" t="s">
         <v>268</v>
       </c>
-      <c r="F1" s="29" t="s">
+      <c r="F1" s="28" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="29" t="s">
+      <c r="G1" s="28" t="s">
         <v>4</v>
       </c>
-      <c r="H1" s="29" t="s">
+      <c r="H1" s="28" t="s">
         <v>5</v>
       </c>
-      <c r="I1" s="29" t="s">
+      <c r="I1" s="28" t="s">
         <v>7</v>
       </c>
-      <c r="J1" s="29" t="s">
+      <c r="J1" s="28" t="s">
         <v>13</v>
       </c>
-      <c r="K1" s="29" t="s">
+      <c r="K1" s="28" t="s">
         <v>17</v>
       </c>
-      <c r="L1" s="29" t="s">
+      <c r="L1" s="28" t="s">
         <v>18</v>
       </c>
-      <c r="M1" s="29" t="s">
+      <c r="M1" s="28" t="s">
         <v>0</v>
       </c>
-      <c r="N1" s="29" t="s">
+      <c r="N1" s="28" t="s">
         <v>19</v>
       </c>
-      <c r="O1" s="30" t="s">
+      <c r="O1" s="29" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="31" t="s">
+      <c r="P1" s="30" t="s">
         <v>15</v>
       </c>
     </row>
@@ -7661,9 +7676,9 @@
     <col min="2" max="2" width="32.42578125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="32.42578125" hidden="1" customWidth="1"/>
     <col min="4" max="4" width="50.85546875" hidden="1" customWidth="1"/>
-    <col min="5" max="5" width="54.5703125" style="24" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="108.42578125" style="35" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="70.85546875" style="35" customWidth="1"/>
+    <col min="5" max="5" width="54.5703125" style="23" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="108.42578125" style="34" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="70.85546875" style="34" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
@@ -7676,26 +7691,26 @@
       <c r="D1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="E1" s="24" t="s">
+      <c r="E1" s="23" t="s">
         <v>301</v>
       </c>
-      <c r="F1" s="33" t="s">
+      <c r="F1" s="32" t="s">
         <v>300</v>
       </c>
-      <c r="G1" s="33" t="s">
+      <c r="G1" s="32" t="s">
         <v>307</v>
       </c>
     </row>
     <row r="2" spans="1:7">
-      <c r="A2" s="28" t="s">
+      <c r="A2" s="27" t="s">
         <v>247</v>
       </c>
-      <c r="B2" s="28"/>
-      <c r="C2" s="28"/>
-      <c r="D2" s="28"/>
-      <c r="E2" s="37"/>
-      <c r="F2" s="34"/>
-      <c r="G2" s="34"/>
+      <c r="B2" s="27"/>
+      <c r="C2" s="27"/>
+      <c r="D2" s="27"/>
+      <c r="E2" s="36"/>
+      <c r="F2" s="33"/>
+      <c r="G2" s="33"/>
     </row>
     <row r="3" spans="1:7">
       <c r="B3" t="s">
@@ -7707,13 +7722,13 @@
       <c r="D3" t="s">
         <v>326</v>
       </c>
-      <c r="E3" s="38" t="s">
+      <c r="E3" s="37" t="s">
         <v>312</v>
       </c>
-      <c r="F3" s="27" t="s">
+      <c r="F3" s="26" t="s">
         <v>316</v>
       </c>
-      <c r="G3" s="35" t="s">
+      <c r="G3" s="34" t="s">
         <v>308</v>
       </c>
     </row>
@@ -7727,13 +7742,13 @@
       <c r="D4" t="s">
         <v>327</v>
       </c>
-      <c r="E4" s="38" t="s">
+      <c r="E4" s="37" t="s">
         <v>313</v>
       </c>
-      <c r="F4" s="35" t="s">
+      <c r="F4" s="34" t="s">
         <v>305</v>
       </c>
-      <c r="G4" s="35" t="s">
+      <c r="G4" s="34" t="s">
         <v>308</v>
       </c>
     </row>
@@ -7747,13 +7762,13 @@
       <c r="D5" t="s">
         <v>328</v>
       </c>
-      <c r="E5" s="38" t="s">
+      <c r="E5" s="37" t="s">
         <v>314</v>
       </c>
-      <c r="F5" s="35" t="s">
+      <c r="F5" s="34" t="s">
         <v>303</v>
       </c>
-      <c r="G5" s="35" t="s">
+      <c r="G5" s="34" t="s">
         <v>308</v>
       </c>
     </row>
@@ -7767,26 +7782,26 @@
       <c r="D6" t="s">
         <v>329</v>
       </c>
-      <c r="E6" s="38" t="s">
+      <c r="E6" s="37" t="s">
         <v>315</v>
       </c>
-      <c r="F6" s="35" t="s">
+      <c r="F6" s="34" t="s">
         <v>304</v>
       </c>
-      <c r="G6" s="35" t="s">
+      <c r="G6" s="34" t="s">
         <v>308</v>
       </c>
     </row>
     <row r="7" spans="1:7">
-      <c r="A7" s="28" t="s">
+      <c r="A7" s="27" t="s">
         <v>268</v>
       </c>
-      <c r="B7" s="28"/>
-      <c r="C7" s="28"/>
-      <c r="D7" s="28"/>
-      <c r="E7" s="37"/>
-      <c r="F7" s="34"/>
-      <c r="G7" s="34"/>
+      <c r="B7" s="27"/>
+      <c r="C7" s="27"/>
+      <c r="D7" s="27"/>
+      <c r="E7" s="36"/>
+      <c r="F7" s="33"/>
+      <c r="G7" s="33"/>
     </row>
     <row r="8" spans="1:7">
       <c r="B8" t="s">
@@ -7798,13 +7813,13 @@
       <c r="D8" t="s">
         <v>330</v>
       </c>
-      <c r="E8" s="38" t="s">
+      <c r="E8" s="37" t="s">
         <v>308</v>
       </c>
-      <c r="F8" s="35" t="s">
+      <c r="F8" s="34" t="s">
         <v>310</v>
       </c>
-      <c r="G8" s="35" t="s">
+      <c r="G8" s="34" t="s">
         <v>309</v>
       </c>
     </row>
@@ -7818,13 +7833,13 @@
       <c r="D9" t="s">
         <v>330</v>
       </c>
-      <c r="E9" s="38" t="s">
+      <c r="E9" s="37" t="s">
         <v>308</v>
       </c>
-      <c r="F9" s="35" t="s">
+      <c r="F9" s="34" t="s">
         <v>311</v>
       </c>
-      <c r="G9" s="35" t="s">
+      <c r="G9" s="34" t="s">
         <v>309</v>
       </c>
     </row>
@@ -7838,10 +7853,10 @@
       <c r="D10" t="s">
         <v>336</v>
       </c>
-      <c r="E10" s="38" t="s">
+      <c r="E10" s="37" t="s">
         <v>302</v>
       </c>
-      <c r="F10" s="36" t="s">
+      <c r="F10" s="35" t="s">
         <v>317</v>
       </c>
       <c r="G10" s="14" t="s">
@@ -7858,10 +7873,10 @@
       <c r="D11" t="s">
         <v>331</v>
       </c>
-      <c r="E11" s="38" t="s">
+      <c r="E11" s="37" t="s">
         <v>306</v>
       </c>
-      <c r="F11" s="35" t="s">
+      <c r="F11" s="34" t="s">
         <v>318</v>
       </c>
       <c r="G11" s="14" t="s">
@@ -7875,13 +7890,13 @@
       <c r="C12" t="s">
         <v>335</v>
       </c>
-      <c r="E12" s="38" t="s">
+      <c r="E12" s="37" t="s">
         <v>345</v>
       </c>
-      <c r="F12" s="36" t="s">
+      <c r="F12" s="35" t="s">
         <v>319</v>
       </c>
-      <c r="G12" s="35" t="s">
+      <c r="G12" s="34" t="s">
         <v>308</v>
       </c>
     </row>
@@ -7895,10 +7910,10 @@
       <c r="D13" t="s">
         <v>338</v>
       </c>
-      <c r="E13" s="38" t="s">
+      <c r="E13" s="37" t="s">
         <v>306</v>
       </c>
-      <c r="F13" s="36" t="s">
+      <c r="F13" s="35" t="s">
         <v>320</v>
       </c>
       <c r="G13" s="14" t="s">
@@ -7906,15 +7921,15 @@
       </c>
     </row>
     <row r="14" spans="1:7">
-      <c r="A14" s="28" t="s">
+      <c r="A14" s="27" t="s">
         <v>248</v>
       </c>
-      <c r="B14" s="28"/>
-      <c r="C14" s="28"/>
-      <c r="D14" s="28"/>
-      <c r="E14" s="37"/>
-      <c r="F14" s="34"/>
-      <c r="G14" s="34"/>
+      <c r="B14" s="27"/>
+      <c r="C14" s="27"/>
+      <c r="D14" s="27"/>
+      <c r="E14" s="36"/>
+      <c r="F14" s="33"/>
+      <c r="G14" s="33"/>
     </row>
     <row r="15" spans="1:7" ht="30">
       <c r="B15" t="s">
@@ -7923,16 +7938,16 @@
       <c r="C15" t="s">
         <v>340</v>
       </c>
-      <c r="D15" s="26" t="s">
+      <c r="D15" s="25" t="s">
         <v>349</v>
       </c>
-      <c r="E15" s="38" t="s">
+      <c r="E15" s="37" t="s">
         <v>343</v>
       </c>
-      <c r="F15" s="35" t="s">
+      <c r="F15" s="34" t="s">
         <v>351</v>
       </c>
-      <c r="G15" s="35" t="s">
+      <c r="G15" s="34" t="s">
         <v>449</v>
       </c>
     </row>
@@ -7943,16 +7958,16 @@
       <c r="C16" t="s">
         <v>340</v>
       </c>
-      <c r="D16" s="26" t="s">
+      <c r="D16" s="25" t="s">
         <v>350</v>
       </c>
-      <c r="E16" s="38" t="s">
+      <c r="E16" s="37" t="s">
         <v>343</v>
       </c>
-      <c r="F16" s="35" t="s">
+      <c r="F16" s="34" t="s">
         <v>352</v>
       </c>
-      <c r="G16" s="35" t="s">
+      <c r="G16" s="34" t="s">
         <v>449</v>
       </c>
     </row>
@@ -7966,13 +7981,13 @@
       <c r="D17" t="s">
         <v>342</v>
       </c>
-      <c r="E17" s="24" t="s">
+      <c r="E17" s="23" t="s">
         <v>346</v>
       </c>
-      <c r="F17" s="35" t="s">
+      <c r="F17" s="34" t="s">
         <v>348</v>
       </c>
-      <c r="G17" s="35" t="s">
+      <c r="G17" s="34" t="s">
         <v>308</v>
       </c>
     </row>
@@ -7983,16 +7998,16 @@
       <c r="C18" t="s">
         <v>340</v>
       </c>
-      <c r="D18" s="26" t="s">
+      <c r="D18" s="25" t="s">
         <v>347</v>
       </c>
-      <c r="E18" s="38" t="s">
+      <c r="E18" s="37" t="s">
         <v>343</v>
       </c>
-      <c r="F18" s="35" t="s">
+      <c r="F18" s="34" t="s">
         <v>368</v>
       </c>
-      <c r="G18" s="35" t="s">
+      <c r="G18" s="34" t="s">
         <v>308</v>
       </c>
     </row>
@@ -8006,26 +8021,26 @@
       <c r="D19" t="s">
         <v>344</v>
       </c>
-      <c r="E19" s="38" t="s">
+      <c r="E19" s="37" t="s">
         <v>343</v>
       </c>
-      <c r="F19" s="35" t="s">
+      <c r="F19" s="34" t="s">
         <v>353</v>
       </c>
-      <c r="G19" s="35" t="s">
+      <c r="G19" s="34" t="s">
         <v>354</v>
       </c>
     </row>
     <row r="20" spans="1:7">
-      <c r="A20" s="28" t="s">
+      <c r="A20" s="27" t="s">
         <v>278</v>
       </c>
-      <c r="B20" s="28"/>
-      <c r="C20" s="28"/>
-      <c r="D20" s="28"/>
-      <c r="E20" s="37"/>
-      <c r="F20" s="34"/>
-      <c r="G20" s="34"/>
+      <c r="B20" s="27"/>
+      <c r="C20" s="27"/>
+      <c r="D20" s="27"/>
+      <c r="E20" s="36"/>
+      <c r="F20" s="33"/>
+      <c r="G20" s="33"/>
     </row>
     <row r="21" spans="1:7" ht="45">
       <c r="B21" t="s">
@@ -8034,16 +8049,16 @@
       <c r="C21" t="s">
         <v>341</v>
       </c>
-      <c r="D21" s="26" t="s">
+      <c r="D21" s="25" t="s">
         <v>355</v>
       </c>
-      <c r="E21" s="38" t="s">
+      <c r="E21" s="37" t="s">
         <v>369</v>
       </c>
-      <c r="F21" s="35" t="s">
+      <c r="F21" s="34" t="s">
         <v>359</v>
       </c>
-      <c r="G21" s="35" t="s">
+      <c r="G21" s="34" t="s">
         <v>445</v>
       </c>
     </row>
@@ -8054,16 +8069,16 @@
       <c r="C22" t="s">
         <v>341</v>
       </c>
-      <c r="D22" s="26" t="s">
+      <c r="D22" s="25" t="s">
         <v>356</v>
       </c>
-      <c r="E22" s="38" t="s">
+      <c r="E22" s="37" t="s">
         <v>369</v>
       </c>
-      <c r="F22" s="35" t="s">
+      <c r="F22" s="34" t="s">
         <v>360</v>
       </c>
-      <c r="G22" s="35" t="s">
+      <c r="G22" s="34" t="s">
         <v>361</v>
       </c>
     </row>
@@ -8074,16 +8089,16 @@
       <c r="C23" t="s">
         <v>341</v>
       </c>
-      <c r="D23" s="26" t="s">
+      <c r="D23" s="25" t="s">
         <v>357</v>
       </c>
-      <c r="E23" s="38" t="s">
+      <c r="E23" s="37" t="s">
         <v>370</v>
       </c>
-      <c r="F23" s="35" t="s">
+      <c r="F23" s="34" t="s">
         <v>362</v>
       </c>
-      <c r="G23" s="35" t="s">
+      <c r="G23" s="34" t="s">
         <v>361</v>
       </c>
     </row>
@@ -8094,16 +8109,16 @@
       <c r="C24" t="s">
         <v>341</v>
       </c>
-      <c r="D24" s="26" t="s">
+      <c r="D24" s="25" t="s">
         <v>358</v>
       </c>
-      <c r="E24" s="38" t="s">
+      <c r="E24" s="37" t="s">
         <v>371</v>
       </c>
-      <c r="F24" s="35" t="s">
+      <c r="F24" s="34" t="s">
         <v>363</v>
       </c>
-      <c r="G24" s="35" t="s">
+      <c r="G24" s="34" t="s">
         <v>308</v>
       </c>
     </row>
@@ -8114,16 +8129,16 @@
       <c r="C25" t="s">
         <v>341</v>
       </c>
-      <c r="D25" s="26" t="s">
+      <c r="D25" s="25" t="s">
         <v>366</v>
       </c>
-      <c r="E25" s="24" t="s">
+      <c r="E25" s="23" t="s">
         <v>372</v>
       </c>
-      <c r="F25" s="35" t="s">
+      <c r="F25" s="34" t="s">
         <v>364</v>
       </c>
-      <c r="G25" s="35" t="s">
+      <c r="G25" s="34" t="s">
         <v>308</v>
       </c>
     </row>
@@ -8134,29 +8149,29 @@
       <c r="C26" t="s">
         <v>341</v>
       </c>
-      <c r="D26" s="26" t="s">
+      <c r="D26" s="25" t="s">
         <v>365</v>
       </c>
-      <c r="E26" s="38" t="s">
+      <c r="E26" s="37" t="s">
         <v>373</v>
       </c>
-      <c r="F26" s="35" t="s">
+      <c r="F26" s="34" t="s">
         <v>367</v>
       </c>
-      <c r="G26" s="35" t="s">
+      <c r="G26" s="34" t="s">
         <v>339</v>
       </c>
     </row>
     <row r="27" spans="1:7">
-      <c r="A27" s="28" t="s">
+      <c r="A27" s="27" t="s">
         <v>249</v>
       </c>
-      <c r="B27" s="28"/>
-      <c r="C27" s="28"/>
-      <c r="D27" s="28"/>
-      <c r="E27" s="37"/>
-      <c r="F27" s="34"/>
-      <c r="G27" s="34"/>
+      <c r="B27" s="27"/>
+      <c r="C27" s="27"/>
+      <c r="D27" s="27"/>
+      <c r="E27" s="36"/>
+      <c r="F27" s="33"/>
+      <c r="G27" s="33"/>
     </row>
     <row r="28" spans="1:7" ht="30">
       <c r="B28" t="s">
@@ -8165,13 +8180,13 @@
       <c r="C28" t="s">
         <v>394</v>
       </c>
-      <c r="D28" s="26" t="s">
+      <c r="D28" s="25" t="s">
         <v>377</v>
       </c>
-      <c r="E28" s="24" t="s">
+      <c r="E28" s="23" t="s">
         <v>375</v>
       </c>
-      <c r="F28" s="35" t="s">
+      <c r="F28" s="34" t="s">
         <v>381</v>
       </c>
       <c r="G28" s="14" t="s">
@@ -8185,29 +8200,29 @@
       <c r="C29" t="s">
         <v>394</v>
       </c>
-      <c r="D29" s="26" t="s">
+      <c r="D29" s="25" t="s">
         <v>378</v>
       </c>
-      <c r="E29" s="24" t="s">
+      <c r="E29" s="23" t="s">
         <v>379</v>
       </c>
-      <c r="F29" s="35" t="s">
+      <c r="F29" s="34" t="s">
         <v>380</v>
       </c>
-      <c r="G29" s="35" t="s">
+      <c r="G29" s="34" t="s">
         <v>308</v>
       </c>
     </row>
     <row r="30" spans="1:7">
-      <c r="A30" s="28" t="s">
+      <c r="A30" s="27" t="s">
         <v>256</v>
       </c>
-      <c r="B30" s="28"/>
-      <c r="C30" s="28"/>
-      <c r="D30" s="28"/>
-      <c r="E30" s="37"/>
-      <c r="F30" s="34"/>
-      <c r="G30" s="34"/>
+      <c r="B30" s="27"/>
+      <c r="C30" s="27"/>
+      <c r="D30" s="27"/>
+      <c r="E30" s="36"/>
+      <c r="F30" s="33"/>
+      <c r="G30" s="33"/>
     </row>
     <row r="31" spans="1:7" ht="30">
       <c r="B31" t="s">
@@ -8216,13 +8231,13 @@
       <c r="C31" t="s">
         <v>395</v>
       </c>
-      <c r="D31" s="26" t="s">
+      <c r="D31" s="25" t="s">
         <v>382</v>
       </c>
-      <c r="E31" s="24" t="s">
+      <c r="E31" s="23" t="s">
         <v>385</v>
       </c>
-      <c r="F31" s="35" t="s">
+      <c r="F31" s="34" t="s">
         <v>392</v>
       </c>
       <c r="G31" s="14" t="s">
@@ -8236,13 +8251,13 @@
       <c r="C32" t="s">
         <v>395</v>
       </c>
-      <c r="D32" s="26" t="s">
+      <c r="D32" s="25" t="s">
         <v>384</v>
       </c>
-      <c r="E32" s="24" t="s">
+      <c r="E32" s="23" t="s">
         <v>385</v>
       </c>
-      <c r="F32" s="35" t="s">
+      <c r="F32" s="34" t="s">
         <v>388</v>
       </c>
       <c r="G32" s="14" t="s">
@@ -8256,13 +8271,13 @@
       <c r="C33" t="s">
         <v>396</v>
       </c>
-      <c r="D33" s="26" t="s">
+      <c r="D33" s="25" t="s">
         <v>383</v>
       </c>
-      <c r="E33" s="24" t="s">
+      <c r="E33" s="23" t="s">
         <v>386</v>
       </c>
-      <c r="F33" s="36" t="s">
+      <c r="F33" s="35" t="s">
         <v>393</v>
       </c>
       <c r="G33" s="14" t="s">
@@ -8270,24 +8285,24 @@
       </c>
     </row>
     <row r="34" spans="1:7">
-      <c r="A34" s="28" t="s">
+      <c r="A34" s="27" t="s">
         <v>258</v>
       </c>
-      <c r="B34" s="28"/>
-      <c r="C34" s="28"/>
-      <c r="D34" s="28"/>
-      <c r="E34" s="37"/>
-      <c r="F34" s="34"/>
-      <c r="G34" s="34"/>
+      <c r="B34" s="27"/>
+      <c r="C34" s="27"/>
+      <c r="D34" s="27"/>
+      <c r="E34" s="36"/>
+      <c r="F34" s="33"/>
+      <c r="G34" s="33"/>
     </row>
     <row r="35" spans="1:7" ht="30">
       <c r="B35" t="s">
         <v>259</v>
       </c>
-      <c r="D35" s="26" t="s">
+      <c r="D35" s="25" t="s">
         <v>491</v>
       </c>
-      <c r="E35" s="38" t="s">
+      <c r="E35" s="37" t="s">
         <v>489</v>
       </c>
       <c r="F35" s="14" t="s">
@@ -8298,10 +8313,10 @@
       <c r="B36" t="s">
         <v>443</v>
       </c>
-      <c r="D36" s="26" t="s">
+      <c r="D36" s="25" t="s">
         <v>492</v>
       </c>
-      <c r="E36" s="38" t="s">
+      <c r="E36" s="37" t="s">
         <v>488</v>
       </c>
       <c r="F36" s="14" t="s">
@@ -8312,27 +8327,27 @@
       <c r="B37" t="s">
         <v>290</v>
       </c>
-      <c r="D37" s="26" t="s">
+      <c r="D37" s="25" t="s">
         <v>493</v>
       </c>
-      <c r="E37" s="38"/>
-      <c r="F37" s="35" t="s">
+      <c r="E37" s="37"/>
+      <c r="F37" s="34" t="s">
         <v>495</v>
       </c>
-      <c r="G37" s="24" t="s">
+      <c r="G37" s="23" t="s">
         <v>494</v>
       </c>
     </row>
     <row r="38" spans="1:7">
-      <c r="A38" s="28" t="s">
+      <c r="A38" s="27" t="s">
         <v>263</v>
       </c>
-      <c r="B38" s="28"/>
-      <c r="C38" s="28"/>
-      <c r="D38" s="28"/>
-      <c r="E38" s="37"/>
-      <c r="F38" s="34"/>
-      <c r="G38" s="34"/>
+      <c r="B38" s="27"/>
+      <c r="C38" s="27"/>
+      <c r="D38" s="27"/>
+      <c r="E38" s="36"/>
+      <c r="F38" s="33"/>
+      <c r="G38" s="33"/>
     </row>
     <row r="39" spans="1:7" ht="30">
       <c r="B39" t="s">
@@ -8341,7 +8356,7 @@
       <c r="D39" t="s">
         <v>479</v>
       </c>
-      <c r="E39" s="24" t="s">
+      <c r="E39" s="23" t="s">
         <v>450</v>
       </c>
       <c r="F39" s="14" t="s">
@@ -8358,11 +8373,11 @@
       <c r="D40" t="s">
         <v>463</v>
       </c>
-      <c r="E40" s="38"/>
-      <c r="F40" s="27" t="s">
+      <c r="E40" s="37"/>
+      <c r="F40" s="26" t="s">
         <v>453</v>
       </c>
-      <c r="G40" s="35" t="s">
+      <c r="G40" s="34" t="s">
         <v>308</v>
       </c>
     </row>
@@ -8373,11 +8388,11 @@
       <c r="D41" t="s">
         <v>463</v>
       </c>
-      <c r="E41" s="38"/>
-      <c r="F41" s="27" t="s">
+      <c r="E41" s="37"/>
+      <c r="F41" s="26" t="s">
         <v>454</v>
       </c>
-      <c r="G41" s="35" t="s">
+      <c r="G41" s="34" t="s">
         <v>308</v>
       </c>
     </row>
@@ -8388,11 +8403,11 @@
       <c r="D42" t="s">
         <v>462</v>
       </c>
-      <c r="E42" s="38"/>
+      <c r="E42" s="37"/>
       <c r="F42" s="14" t="s">
         <v>455</v>
       </c>
-      <c r="G42" s="35" t="s">
+      <c r="G42" s="34" t="s">
         <v>308</v>
       </c>
     </row>
@@ -8403,11 +8418,11 @@
       <c r="D43" t="s">
         <v>461</v>
       </c>
-      <c r="E43" s="38"/>
-      <c r="F43" s="35" t="s">
+      <c r="E43" s="37"/>
+      <c r="F43" s="34" t="s">
         <v>433</v>
       </c>
-      <c r="G43" s="35" t="s">
+      <c r="G43" s="34" t="s">
         <v>458</v>
       </c>
     </row>
@@ -8418,11 +8433,11 @@
       <c r="D44" t="s">
         <v>460</v>
       </c>
-      <c r="E44" s="38"/>
-      <c r="F44" s="35" t="s">
+      <c r="E44" s="37"/>
+      <c r="F44" s="34" t="s">
         <v>434</v>
       </c>
-      <c r="G44" s="35" t="s">
+      <c r="G44" s="34" t="s">
         <v>458</v>
       </c>
     </row>
@@ -8433,10 +8448,10 @@
       <c r="D45" t="s">
         <v>459</v>
       </c>
-      <c r="E45" s="24" t="s">
+      <c r="E45" s="23" t="s">
         <v>457</v>
       </c>
-      <c r="F45" s="35" t="s">
+      <c r="F45" s="34" t="s">
         <v>435</v>
       </c>
       <c r="G45" s="15" t="s">
@@ -8450,10 +8465,10 @@
       <c r="D46" t="s">
         <v>459</v>
       </c>
-      <c r="E46" s="24" t="s">
+      <c r="E46" s="23" t="s">
         <v>457</v>
       </c>
-      <c r="F46" s="35" t="s">
+      <c r="F46" s="34" t="s">
         <v>436</v>
       </c>
       <c r="G46" s="15" t="s">
@@ -8467,10 +8482,10 @@
       <c r="D47" t="s">
         <v>459</v>
       </c>
-      <c r="E47" s="24" t="s">
+      <c r="E47" s="23" t="s">
         <v>457</v>
       </c>
-      <c r="F47" s="35" t="s">
+      <c r="F47" s="34" t="s">
         <v>437</v>
       </c>
       <c r="G47" s="15" t="s">
@@ -8484,39 +8499,39 @@
       <c r="D48" t="s">
         <v>480</v>
       </c>
-      <c r="E48" s="24" t="s">
+      <c r="E48" s="23" t="s">
         <v>465</v>
       </c>
-      <c r="F48" s="35" t="s">
+      <c r="F48" s="34" t="s">
         <v>469</v>
       </c>
-      <c r="G48" s="35" t="s">
+      <c r="G48" s="34" t="s">
         <v>470</v>
       </c>
     </row>
     <row r="49" spans="1:7">
-      <c r="A49" s="32" t="s">
+      <c r="A49" s="31" t="s">
         <v>255</v>
       </c>
-      <c r="B49" s="28"/>
-      <c r="C49" s="28"/>
-      <c r="D49" s="28"/>
-      <c r="E49" s="37"/>
-      <c r="F49" s="34"/>
-      <c r="G49" s="34"/>
+      <c r="B49" s="27"/>
+      <c r="C49" s="27"/>
+      <c r="D49" s="27"/>
+      <c r="E49" s="36"/>
+      <c r="F49" s="33"/>
+      <c r="G49" s="33"/>
     </row>
     <row r="50" spans="1:7">
       <c r="B50" t="s">
         <v>274</v>
       </c>
-      <c r="D50" s="25"/>
-      <c r="E50" s="24" t="s">
+      <c r="D50" s="24"/>
+      <c r="E50" s="23" t="s">
         <v>484</v>
       </c>
-      <c r="F50" s="35" t="s">
+      <c r="F50" s="34" t="s">
         <v>485</v>
       </c>
-      <c r="G50" s="35" t="s">
+      <c r="G50" s="34" t="s">
         <v>483</v>
       </c>
     </row>
@@ -8524,13 +8539,13 @@
       <c r="B51" t="s">
         <v>275</v>
       </c>
-      <c r="D51" s="25" t="s">
+      <c r="D51" s="24" t="s">
         <v>479</v>
       </c>
-      <c r="E51" s="24" t="s">
+      <c r="E51" s="23" t="s">
         <v>486</v>
       </c>
-      <c r="F51" s="35" t="s">
+      <c r="F51" s="34" t="s">
         <v>487</v>
       </c>
     </row>
@@ -8538,16 +8553,16 @@
       <c r="B52" t="s">
         <v>281</v>
       </c>
-      <c r="D52" s="25" t="s">
+      <c r="D52" s="24" t="s">
         <v>479</v>
       </c>
-      <c r="E52" s="24" t="s">
+      <c r="E52" s="23" t="s">
         <v>464</v>
       </c>
-      <c r="F52" s="35" t="s">
+      <c r="F52" s="34" t="s">
         <v>481</v>
       </c>
-      <c r="G52" s="35" t="s">
+      <c r="G52" s="34" t="s">
         <v>482</v>
       </c>
     </row>
@@ -8555,16 +8570,16 @@
       <c r="B53" t="s">
         <v>266</v>
       </c>
-      <c r="D53" s="25" t="s">
+      <c r="D53" s="24" t="s">
         <v>479</v>
       </c>
-      <c r="E53" s="24" t="s">
+      <c r="E53" s="23" t="s">
         <v>468</v>
       </c>
-      <c r="F53" s="35" t="s">
+      <c r="F53" s="34" t="s">
         <v>466</v>
       </c>
-      <c r="G53" s="35" t="s">
+      <c r="G53" s="34" t="s">
         <v>467</v>
       </c>
     </row>
@@ -8572,14 +8587,14 @@
       <c r="B54" t="s">
         <v>289</v>
       </c>
-      <c r="D54" s="25"/>
-      <c r="E54" s="24" t="s">
+      <c r="D54" s="24"/>
+      <c r="E54" s="23" t="s">
         <v>475</v>
       </c>
-      <c r="F54" s="35" t="s">
+      <c r="F54" s="34" t="s">
         <v>472</v>
       </c>
-      <c r="G54" s="35" t="s">
+      <c r="G54" s="34" t="s">
         <v>473</v>
       </c>
     </row>
@@ -8587,13 +8602,13 @@
       <c r="B55" t="s">
         <v>441</v>
       </c>
-      <c r="E55" s="24" t="s">
+      <c r="E55" s="23" t="s">
         <v>474</v>
       </c>
-      <c r="F55" s="35" t="s">
+      <c r="F55" s="34" t="s">
         <v>432</v>
       </c>
-      <c r="G55" s="35" t="s">
+      <c r="G55" s="34" t="s">
         <v>458</v>
       </c>
     </row>
@@ -8601,14 +8616,14 @@
       <c r="B56" t="s">
         <v>439</v>
       </c>
-      <c r="D56" s="25"/>
-      <c r="E56" s="24" t="s">
+      <c r="D56" s="24"/>
+      <c r="E56" s="23" t="s">
         <v>477</v>
       </c>
-      <c r="F56" s="35" t="s">
+      <c r="F56" s="34" t="s">
         <v>444</v>
       </c>
-      <c r="G56" s="35" t="s">
+      <c r="G56" s="34" t="s">
         <v>476</v>
       </c>
     </row>
@@ -8616,32 +8631,32 @@
       <c r="B57" t="s">
         <v>440</v>
       </c>
-      <c r="E57" s="24" t="s">
+      <c r="E57" s="23" t="s">
         <v>478</v>
       </c>
-      <c r="F57" s="35" t="s">
+      <c r="F57" s="34" t="s">
         <v>444</v>
       </c>
-      <c r="G57" s="35" t="s">
+      <c r="G57" s="34" t="s">
         <v>339</v>
       </c>
     </row>
     <row r="58" spans="1:7">
-      <c r="D58" s="25"/>
-      <c r="E58" s="38"/>
+      <c r="D58" s="24"/>
+      <c r="E58" s="37"/>
     </row>
     <row r="59" spans="1:7">
-      <c r="D59" s="25"/>
-      <c r="E59" s="38"/>
+      <c r="D59" s="24"/>
+      <c r="E59" s="37"/>
     </row>
     <row r="60" spans="1:7">
-      <c r="E60" s="38"/>
+      <c r="E60" s="37"/>
     </row>
     <row r="61" spans="1:7">
       <c r="A61" s="21" t="s">
         <v>431</v>
       </c>
-      <c r="E61" s="38"/>
+      <c r="E61" s="37"/>
     </row>
     <row r="62" spans="1:7">
       <c r="B62" t="s">
@@ -8653,25 +8668,25 @@
       <c r="B63" t="s">
         <v>251</v>
       </c>
-      <c r="E63" s="38"/>
+      <c r="E63" s="37"/>
     </row>
     <row r="64" spans="1:7">
       <c r="B64" t="s">
         <v>252</v>
       </c>
-      <c r="E64" s="38"/>
+      <c r="E64" s="37"/>
     </row>
     <row r="65" spans="2:5">
       <c r="B65" t="s">
         <v>253</v>
       </c>
-      <c r="E65" s="38"/>
+      <c r="E65" s="37"/>
     </row>
     <row r="66" spans="2:5">
       <c r="B66" t="s">
         <v>254</v>
       </c>
-      <c r="E66" s="38"/>
+      <c r="E66" s="37"/>
     </row>
   </sheetData>
   <dataConsolidate/>
@@ -9099,11 +9114,11 @@
       <c r="L13" s="15"/>
     </row>
     <row r="15" spans="1:12">
-      <c r="A15" s="23" t="s">
+      <c r="A15" s="38" t="s">
         <v>233</v>
       </c>
-      <c r="B15" s="23"/>
-      <c r="C15" s="23"/>
+      <c r="B15" s="38"/>
+      <c r="C15" s="38"/>
     </row>
     <row r="16" spans="1:12">
       <c r="A16" s="22" t="s">
@@ -9132,7 +9147,7 @@
       <c r="K17" s="11" t="s">
         <v>447</v>
       </c>
-      <c r="L17" s="25" t="s">
+      <c r="L17" s="24" t="s">
         <v>448</v>
       </c>
     </row>
@@ -9146,6 +9161,9 @@
       <c r="C18" t="s">
         <v>243</v>
       </c>
+      <c r="K18" t="s">
+        <v>497</v>
+      </c>
     </row>
     <row r="19" spans="1:12">
       <c r="B19" t="s">
@@ -9153,6 +9171,9 @@
       </c>
       <c r="C19" t="s">
         <v>246</v>
+      </c>
+      <c r="K19" t="s">
+        <v>498</v>
       </c>
     </row>
     <row r="20" spans="1:12">
@@ -9172,7 +9193,12 @@
       <c r="H20" s="13"/>
       <c r="I20" s="13"/>
       <c r="J20" s="13"/>
-      <c r="K20" s="13"/>
+      <c r="K20" s="39" t="s">
+        <v>499</v>
+      </c>
+      <c r="L20" t="s">
+        <v>500</v>
+      </c>
     </row>
     <row r="21" spans="1:12">
       <c r="B21" t="s">
